--- a/Family_Income_Statement_2026_v5_FIRE.xlsx
+++ b/Family_Income_Statement_2026_v5_FIRE.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Rules" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Pension - Sue" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="FIRE Dashboard" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Amazon Reconciliation" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -244,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -395,11 +396,18 @@
     <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="11" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="16" fillId="13" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="16" fillId="11" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <font>
         <b val="1"/>
@@ -419,6 +427,16 @@
         <patternFill/>
       </fill>
       <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <colors>
@@ -12814,12 +12832,17 @@
     <row r="43" ht="15.75" customHeight="1" s="39">
       <c r="A43" s="38" t="inlineStr">
         <is>
-          <t>AMAZON MKTPL|AMZN|Amazon.com*RT85D8PV3|AMAZON PRIME*B40RT9363</t>
+          <t>AMZN|AMAZON</t>
         </is>
       </c>
       <c r="B43" s="38" t="inlineStr">
         <is>
           <t>Amazon (misc)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Catch-all Amazon → reconcile on 'Amazon Reconciliation' tab</t>
         </is>
       </c>
     </row>
@@ -15536,6 +15559,969 @@
     <mergeCell ref="A69:C70"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" style="39" min="1" max="1"/>
+    <col width="34" customWidth="1" style="39" min="2" max="2"/>
+    <col width="9" customWidth="1" style="39" min="3" max="3"/>
+    <col width="9" customWidth="1" style="39" min="4" max="4"/>
+    <col width="9" customWidth="1" style="39" min="5" max="5"/>
+    <col width="9" customWidth="1" style="39" min="6" max="6"/>
+    <col width="9" customWidth="1" style="39" min="7" max="7"/>
+    <col width="9" customWidth="1" style="39" min="8" max="8"/>
+    <col width="9" customWidth="1" style="39" min="9" max="9"/>
+    <col width="9" customWidth="1" style="39" min="10" max="10"/>
+    <col width="9" customWidth="1" style="39" min="11" max="11"/>
+    <col width="9" customWidth="1" style="39" min="12" max="12"/>
+    <col width="9" customWidth="1" style="39" min="13" max="13"/>
+    <col width="11" customWidth="1" style="39" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>Amazon — Monthly Reconciliation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1" s="39">
+      <c r="A2" s="41" t="inlineStr">
+        <is>
+          <t>All Amazon spend now lands in ONE bucket — 'Amazon (misc)', CC Detail row 14 — via a single regex rule (AMZN|AMAZON). Each month, split that total into real categories below. ORANGE = you enter $. The reference list at the bottom shows the actual Amazon transactions to guide the split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>① AMAZON TOTAL TO RECONCILE  (auto — from CC Detail)</t>
+        </is>
+      </c>
+      <c r="B4" s="43" t="n"/>
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="43" t="n"/>
+      <c r="E4" s="43" t="n"/>
+      <c r="F4" s="43" t="n"/>
+      <c r="G4" s="43" t="n"/>
+      <c r="H4" s="43" t="n"/>
+      <c r="I4" s="43" t="n"/>
+      <c r="J4" s="43" t="n"/>
+      <c r="K4" s="43" t="n"/>
+      <c r="L4" s="43" t="n"/>
+      <c r="M4" s="43" t="n"/>
+      <c r="N4" s="43" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="78" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C5" s="51" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D5" s="51" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E5" s="51" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F5" s="51" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G5" s="51" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H5" s="51" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I5" s="51" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J5" s="51" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K5" s="51" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L5" s="51" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M5" s="51" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N5" s="51" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="79" t="inlineStr">
+        <is>
+          <t>Amazon (misc) — to reconcile</t>
+        </is>
+      </c>
+      <c r="B6" s="80">
+        <f>'CC Detail'!B14</f>
+        <v/>
+      </c>
+      <c r="C6" s="80">
+        <f>'CC Detail'!C14</f>
+        <v/>
+      </c>
+      <c r="D6" s="80">
+        <f>'CC Detail'!D14</f>
+        <v/>
+      </c>
+      <c r="E6" s="80">
+        <f>'CC Detail'!E14</f>
+        <v/>
+      </c>
+      <c r="F6" s="80">
+        <f>'CC Detail'!F14</f>
+        <v/>
+      </c>
+      <c r="G6" s="80">
+        <f>'CC Detail'!G14</f>
+        <v/>
+      </c>
+      <c r="H6" s="80">
+        <f>'CC Detail'!H14</f>
+        <v/>
+      </c>
+      <c r="I6" s="80">
+        <f>'CC Detail'!I14</f>
+        <v/>
+      </c>
+      <c r="J6" s="80">
+        <f>'CC Detail'!J14</f>
+        <v/>
+      </c>
+      <c r="K6" s="80">
+        <f>'CC Detail'!K14</f>
+        <v/>
+      </c>
+      <c r="L6" s="80">
+        <f>'CC Detail'!L14</f>
+        <v/>
+      </c>
+      <c r="M6" s="80">
+        <f>'CC Detail'!M14</f>
+        <v/>
+      </c>
+      <c r="N6" s="81">
+        <f>SUM(B6:M6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>② ALLOCATE INTO CATEGORIES  (enter $ per month)</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="n"/>
+      <c r="C8" s="43" t="n"/>
+      <c r="D8" s="43" t="n"/>
+      <c r="E8" s="43" t="n"/>
+      <c r="F8" s="43" t="n"/>
+      <c r="G8" s="43" t="n"/>
+      <c r="H8" s="43" t="n"/>
+      <c r="I8" s="43" t="n"/>
+      <c r="J8" s="43" t="n"/>
+      <c r="K8" s="43" t="n"/>
+      <c r="L8" s="43" t="n"/>
+      <c r="M8" s="43" t="n"/>
+      <c r="N8" s="43" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="78" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B9" s="51" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E9" s="51" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F9" s="51" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G9" s="51" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H9" s="51" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I9" s="51" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J9" s="51" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K9" s="51" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L9" s="51" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M9" s="51" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N9" s="51" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="82" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="B10" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="80">
+        <f>SUM(B10:M10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="82" t="inlineStr">
+        <is>
+          <t>Kids / Activities</t>
+        </is>
+      </c>
+      <c r="B11" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="80">
+        <f>SUM(B11:M11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="82" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="B12" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="80">
+        <f>SUM(B12:M12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="82" t="inlineStr">
+        <is>
+          <t>Pharmacy / Health</t>
+        </is>
+      </c>
+      <c r="B13" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="80">
+        <f>SUM(B13:M13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="82" t="inlineStr">
+        <is>
+          <t>Home / Hardware</t>
+        </is>
+      </c>
+      <c r="B14" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="80">
+        <f>SUM(B14:M14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="82" t="inlineStr">
+        <is>
+          <t>Subscriptions (Prime/Kindle/Audible)</t>
+        </is>
+      </c>
+      <c r="B15" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="80">
+        <f>SUM(B15:M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="82" t="inlineStr">
+        <is>
+          <t>Other / gifts</t>
+        </is>
+      </c>
+      <c r="B16" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="80">
+        <f>SUM(B16:M16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="79" t="inlineStr">
+        <is>
+          <t>Allocated total</t>
+        </is>
+      </c>
+      <c r="B17" s="84">
+        <f>SUM(B10:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="84">
+        <f>SUM(C10:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="84">
+        <f>SUM(D10:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="84">
+        <f>SUM(E10:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="84">
+        <f>SUM(F10:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="84">
+        <f>SUM(G10:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="84">
+        <f>SUM(H10:H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="84">
+        <f>SUM(I10:I16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="84">
+        <f>SUM(J10:J16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="84">
+        <f>SUM(K10:K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="84">
+        <f>SUM(L10:L16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="84">
+        <f>SUM(M10:M16)</f>
+        <v/>
+      </c>
+      <c r="N17" s="84">
+        <f>SUM(N10:N16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="79" t="inlineStr">
+        <is>
+          <t>Unallocated remaining</t>
+        </is>
+      </c>
+      <c r="B18" s="81">
+        <f>B6-B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="81">
+        <f>C6-C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="81">
+        <f>D6-D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="81">
+        <f>E6-E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="81">
+        <f>F6-F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="81">
+        <f>G6-G17</f>
+        <v/>
+      </c>
+      <c r="H18" s="81">
+        <f>H6-H17</f>
+        <v/>
+      </c>
+      <c r="I18" s="81">
+        <f>I6-I17</f>
+        <v/>
+      </c>
+      <c r="J18" s="81">
+        <f>J6-J17</f>
+        <v/>
+      </c>
+      <c r="K18" s="81">
+        <f>K6-K17</f>
+        <v/>
+      </c>
+      <c r="L18" s="81">
+        <f>L6-L17</f>
+        <v/>
+      </c>
+      <c r="M18" s="81">
+        <f>M6-M17</f>
+        <v/>
+      </c>
+      <c r="N18" s="81">
+        <f>N6-N17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>③ RECONCILED CATEGORY TOTALS (YTD) — the un-muddied picture</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="n"/>
+      <c r="C20" s="43" t="n"/>
+      <c r="D20" s="43" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="78" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B21" s="51" t="inlineStr">
+        <is>
+          <t>Native (CC Detail)</t>
+        </is>
+      </c>
+      <c r="C21" s="51" t="inlineStr">
+        <is>
+          <t>+ Amazon</t>
+        </is>
+      </c>
+      <c r="D21" s="51">
+        <f> True total (YTD)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="82" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="B22" s="80">
+        <f>'CC Detail'!N5</f>
+        <v/>
+      </c>
+      <c r="C22" s="80">
+        <f>N10</f>
+        <v/>
+      </c>
+      <c r="D22" s="81">
+        <f>B22+C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="82" t="inlineStr">
+        <is>
+          <t>Kids / Activities</t>
+        </is>
+      </c>
+      <c r="B23" s="80">
+        <f>'CC Detail'!N9</f>
+        <v/>
+      </c>
+      <c r="C23" s="80">
+        <f>N11</f>
+        <v/>
+      </c>
+      <c r="D23" s="81">
+        <f>B23+C23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="82" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="B24" s="80">
+        <f>'CC Detail'!N11</f>
+        <v/>
+      </c>
+      <c r="C24" s="80">
+        <f>N12</f>
+        <v/>
+      </c>
+      <c r="D24" s="81">
+        <f>B24+C24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="82" t="inlineStr">
+        <is>
+          <t>Pharmacy / Health</t>
+        </is>
+      </c>
+      <c r="B25" s="80">
+        <f>'CC Detail'!N12</f>
+        <v/>
+      </c>
+      <c r="C25" s="80">
+        <f>N13</f>
+        <v/>
+      </c>
+      <c r="D25" s="81">
+        <f>B25+C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="82" t="inlineStr">
+        <is>
+          <t>Home / Hardware</t>
+        </is>
+      </c>
+      <c r="B26" s="80">
+        <f>'CC Detail'!N13</f>
+        <v/>
+      </c>
+      <c r="C26" s="80">
+        <f>N14</f>
+        <v/>
+      </c>
+      <c r="D26" s="81">
+        <f>B26+C26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="82" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
+        </is>
+      </c>
+      <c r="B27" s="80">
+        <f>'CC Detail'!N8</f>
+        <v/>
+      </c>
+      <c r="C27" s="80">
+        <f>N15</f>
+        <v/>
+      </c>
+      <c r="D27" s="81">
+        <f>B27+C27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="82" t="inlineStr">
+        <is>
+          <t>Other / gifts</t>
+        </is>
+      </c>
+      <c r="B28" s="80">
+        <f>'CC Detail'!N17</f>
+        <v/>
+      </c>
+      <c r="C28" s="80">
+        <f>N16</f>
+        <v/>
+      </c>
+      <c r="D28" s="81">
+        <f>B28+C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="68" t="inlineStr">
+        <is>
+          <t>Note: once split, these 'true totals' show real spend per category — Amazon no longer hides hardware, hygiene, and kids' purchases in one lump. Feed these into the guardrail when it's built.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="32">
+      <c r="A32" s="42" t="inlineStr">
+        <is>
+          <t>④ REFERENCE — current Amazon transactions  (auto, read-only)</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="n"/>
+      <c r="C32" s="43" t="n"/>
+      <c r="D32" s="43" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="68" t="inlineStr">
+        <is>
+          <t>Pulls Amazon rows from your Barclay import so you can see what to split. Refreshes when you paste new data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="78" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B34" s="78" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C34" s="51" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D34" s="51" t="inlineStr">
+        <is>
+          <t>Purchased by</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <f>IFERROR(FILTER({'Imports - Barclay'!A5:A,'Imports - Barclay'!B5:B,'Imports - Barclay'!D5:D,'Imports - Barclay'!F5:F},REGEXMATCH(UPPER('Imports - Barclay'!B5:B),"AMZN|AMAZON")),"No Amazon rows in current Barclay import")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A29:D30"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A33:D33"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B18:N18">
+    <cfRule type="cellIs" priority="1" operator="notBetween" dxfId="2">
+      <formula>-1</formula>
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Family_Income_Statement_2026_v5_FIRE.xlsx
+++ b/Family_Income_Statement_2026_v5_FIRE.xlsx
@@ -18,6 +18,8 @@
     <sheet name="Pension - Sue" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="FIRE Dashboard" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Amazon Reconciliation" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Solar Reinvestment" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="HSA Election Planner" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,12 +28,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="168" formatCode="$#,##0"/>
+    <numFmt numFmtId="169" formatCode="$0.000"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -245,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -306,6 +309,10 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -370,9 +377,6 @@
     <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -403,6 +407,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="16" fillId="11" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="11" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="16" fillId="11" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="16" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13842,27 +13856,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>Sue — MTRS Pension Calculator (Massachusetts Teachers' Retirement System)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" s="39">
-      <c r="A2" s="41" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Membership Tier 1 confirmed — both 2003 and 2010 predate the 4/2/2012 Tier 2 cutoff. YELLOW = confirm in MyTRS  •  ORANGE = scenario inputs  •  Not affiliated with MTRS; verify against the official MTRS estimator before relying on any figure.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>① CONFIRM IN MyTRS  (mtrs.state.ma.us)</t>
         </is>
       </c>
-      <c r="B4" s="43" t="n"/>
-      <c r="C4" s="43" t="n"/>
+      <c r="B4" s="45" t="n"/>
+      <c r="C4" s="45" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13870,10 +13884,10 @@
           <t>Effective membership date (year)</t>
         </is>
       </c>
-      <c r="B5" s="44" t="n">
+      <c r="B5" s="46" t="n">
         <v>2003</v>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="47" t="inlineStr">
         <is>
           <t>2003 if funds left on account; 2010 if she took a refund &amp; rejoined. Either way = Tier 1.</t>
         </is>
@@ -13885,10 +13899,10 @@
           <t>Current creditable service (yrs, today)</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n">
+      <c r="B6" s="48" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="45" t="inlineStr">
+      <c r="C6" s="47" t="inlineStr">
         <is>
           <t>~16 if she refunded the 2003–07 years; ~20 if that service is still on account. MyTRS shows the exact figure.</t>
         </is>
@@ -13900,12 +13914,12 @@
           <t>RetirementPlus participant? (Y/N)</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C7" s="45" t="inlineStr">
+      <c r="C7" s="47" t="inlineStr">
         <is>
           <t>Auto-YES: joined post-7/1/2001 → mandatory R+ at 11%. A flat 11% on her paystub confirms it.</t>
         </is>
@@ -13917,23 +13931,23 @@
           <t>Years as MTRS teacher (R+ 20-yr test)</t>
         </is>
       </c>
-      <c r="B8" s="46" t="n">
+      <c r="B8" s="48" t="n">
         <v>16</v>
       </c>
-      <c r="C8" s="45" t="inlineStr">
+      <c r="C8" s="47" t="inlineStr">
         <is>
           <t>Almost all her creditable service is teacher service; used only for the R+ 20-year test.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="42" t="inlineStr">
+      <c r="A10" s="44" t="inlineStr">
         <is>
           <t>② SCENARIO INPUTS</t>
         </is>
       </c>
-      <c r="B10" s="43" t="n"/>
-      <c r="C10" s="43" t="n"/>
+      <c r="B10" s="45" t="n"/>
+      <c r="C10" s="45" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13941,7 +13955,7 @@
           <t>Sue's current age</t>
         </is>
       </c>
-      <c r="B11" s="47" t="n">
+      <c r="B11" s="49" t="n">
         <v>45</v>
       </c>
     </row>
@@ -13951,7 +13965,7 @@
           <t>Current calendar year</t>
         </is>
       </c>
-      <c r="B12" s="47" t="n">
+      <c r="B12" s="49" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13961,10 +13975,10 @@
           <t>Current annual salary ($)</t>
         </is>
       </c>
-      <c r="B13" s="48" t="n">
+      <c r="B13" s="50" t="n">
         <v>85000</v>
       </c>
-      <c r="C13" s="45" t="inlineStr">
+      <c r="C13" s="47" t="inlineStr">
         <is>
           <t>Enter Sue's actual salary.</t>
         </is>
@@ -13976,7 +13990,7 @@
           <t>Expected annual raise (%)</t>
         </is>
       </c>
-      <c r="B14" s="49" t="n">
+      <c r="B14" s="51" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -13986,7 +14000,7 @@
           <t>Planned retirement age (scenario)</t>
         </is>
       </c>
-      <c r="B15" s="47" t="n">
+      <c r="B15" s="49" t="n">
         <v>60</v>
       </c>
     </row>
@@ -13996,29 +14010,29 @@
           <t>Buy-back: early years to restore</t>
         </is>
       </c>
-      <c r="B16" s="50" t="n">
+      <c r="B16" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="45" t="inlineStr">
+      <c r="C16" s="47" t="inlineStr">
         <is>
           <t>If she refunded 2003–07, she can repay to restore ~4–5 yrs. Try 4 to see the effect.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="42" t="inlineStr">
+      <c r="A18" s="44" t="inlineStr">
         <is>
           <t>③ TIER 1 RULES  (reference — do not edit)</t>
         </is>
       </c>
-      <c r="B18" s="43" t="n"/>
-      <c r="C18" s="43" t="n"/>
-      <c r="E18" s="51" t="inlineStr">
+      <c r="B18" s="45" t="n"/>
+      <c r="C18" s="45" t="n"/>
+      <c r="E18" s="53" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="F18" s="51" t="inlineStr">
+      <c r="F18" s="53" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
@@ -14030,15 +14044,15 @@
           <t>Membership tier</t>
         </is>
       </c>
-      <c r="B19" s="52" t="inlineStr">
+      <c r="B19" s="54" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="E19" s="53" t="n">
+      <c r="E19" s="55" t="n">
         <v>55</v>
       </c>
-      <c r="F19" s="54" t="n">
+      <c r="F19" s="56" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -14048,15 +14062,15 @@
           <t>Salary average period</t>
         </is>
       </c>
-      <c r="B20" s="52" t="inlineStr">
+      <c r="B20" s="54" t="inlineStr">
         <is>
           <t>Highest 3 yrs</t>
         </is>
       </c>
-      <c r="E20" s="53" t="n">
+      <c r="E20" s="55" t="n">
         <v>56</v>
       </c>
-      <c r="F20" s="54" t="n">
+      <c r="F20" s="56" t="n">
         <v>0.016</v>
       </c>
     </row>
@@ -14066,13 +14080,13 @@
           <t>Maximum benefit cap</t>
         </is>
       </c>
-      <c r="B21" s="55" t="n">
+      <c r="B21" s="57" t="n">
         <v>0.8</v>
       </c>
-      <c r="E21" s="53" t="n">
+      <c r="E21" s="55" t="n">
         <v>57</v>
       </c>
-      <c r="F21" s="54" t="n">
+      <c r="F21" s="56" t="n">
         <v>0.017</v>
       </c>
     </row>
@@ -14082,20 +14096,20 @@
           <t>R+ enhancement</t>
         </is>
       </c>
-      <c r="B22" s="52" t="inlineStr">
+      <c r="B22" s="54" t="inlineStr">
         <is>
           <t>+2%/yr over 24 yrs</t>
         </is>
       </c>
-      <c r="C22" s="45" t="inlineStr">
+      <c r="C22" s="47" t="inlineStr">
         <is>
           <t>Requires ≥30 yrs creditable, ≥20 as teacher, 11% for 5+ yrs.</t>
         </is>
       </c>
-      <c r="E22" s="53" t="n">
+      <c r="E22" s="55" t="n">
         <v>58</v>
       </c>
-      <c r="F22" s="54" t="n">
+      <c r="F22" s="56" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -14105,36 +14119,36 @@
           <t>Min retirement age (Tier 1)</t>
         </is>
       </c>
-      <c r="B23" s="52" t="n">
+      <c r="B23" s="54" t="n">
         <v>55</v>
       </c>
-      <c r="E23" s="53" t="n">
+      <c r="E23" s="55" t="n">
         <v>59</v>
       </c>
-      <c r="F23" s="54" t="n">
+      <c r="F23" s="56" t="n">
         <v>0.019</v>
       </c>
     </row>
     <row r="24">
-      <c r="E24" s="53" t="n">
+      <c r="E24" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="F24" s="54" t="n">
+      <c r="F24" s="56" t="n">
         <v>0.02</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="42" t="inlineStr">
+      <c r="A25" s="44" t="inlineStr">
         <is>
           <t>④ RESULT AT PLANNED RETIREMENT AGE</t>
         </is>
       </c>
-      <c r="B25" s="43" t="n"/>
-      <c r="C25" s="43" t="n"/>
-      <c r="E25" s="53" t="n">
+      <c r="B25" s="45" t="n"/>
+      <c r="C25" s="45" t="n"/>
+      <c r="E25" s="55" t="n">
         <v>61</v>
       </c>
-      <c r="F25" s="54" t="n">
+      <c r="F25" s="56" t="n">
         <v>0.021</v>
       </c>
     </row>
@@ -14144,14 +14158,14 @@
           <t>Creditable service at retirement</t>
         </is>
       </c>
-      <c r="B26" s="56">
+      <c r="B26" s="58">
         <f>B6+(B15-B11)+B16</f>
         <v/>
       </c>
-      <c r="E26" s="53" t="n">
+      <c r="E26" s="55" t="n">
         <v>62</v>
       </c>
-      <c r="F26" s="54" t="n">
+      <c r="F26" s="56" t="n">
         <v>0.022</v>
       </c>
     </row>
@@ -14161,14 +14175,14 @@
           <t>Age factor at retirement</t>
         </is>
       </c>
-      <c r="B27" s="57">
+      <c r="B27" s="59">
         <f>IF(B15&lt;55,0,IF(B15&gt;=65,0.025,0.015+(B15-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E27" s="53" t="n">
+      <c r="E27" s="55" t="n">
         <v>63</v>
       </c>
-      <c r="F27" s="54" t="n">
+      <c r="F27" s="56" t="n">
         <v>0.023</v>
       </c>
     </row>
@@ -14178,14 +14192,14 @@
           <t>Salary average (3-yr, est.) $</t>
         </is>
       </c>
-      <c r="B28" s="58">
+      <c r="B28" s="60">
         <f>B13*((1+B14)^(B15-B11)+(1+B14)^(B15-B11-1)+(1+B14)^(B15-B11-2))/3</f>
         <v/>
       </c>
-      <c r="E28" s="53" t="n">
+      <c r="E28" s="55" t="n">
         <v>64</v>
       </c>
-      <c r="F28" s="54" t="n">
+      <c r="F28" s="56" t="n">
         <v>0.024</v>
       </c>
     </row>
@@ -14195,14 +14209,14 @@
           <t>Regular formula benefit %</t>
         </is>
       </c>
-      <c r="B29" s="57">
+      <c r="B29" s="59">
         <f>MIN($B$21,B27*B26)</f>
         <v/>
       </c>
-      <c r="E29" s="53" t="n">
+      <c r="E29" s="55" t="n">
         <v>65</v>
       </c>
-      <c r="F29" s="54" t="n">
+      <c r="F29" s="56" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -14212,7 +14226,7 @@
           <t>R+ eligible?</t>
         </is>
       </c>
-      <c r="B30" s="59">
+      <c r="B30" s="61">
         <f>IF(AND($B$7="Y",B26&gt;=30,B8+(B15-B11)&gt;=20),"Yes","No")</f>
         <v/>
       </c>
@@ -14223,7 +14237,7 @@
           <t>R+ formula benefit %</t>
         </is>
       </c>
-      <c r="B31" s="57">
+      <c r="B31" s="59">
         <f>MIN($B$21,B27*B26+0.02*MAX(0,B26-24))</f>
         <v/>
       </c>
@@ -14234,18 +14248,18 @@
           <t>Applied benefit %</t>
         </is>
       </c>
-      <c r="B32" s="60">
+      <c r="B32" s="62">
         <f>IF(B30="Yes",B31,B29)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="61" t="inlineStr">
+      <c r="A33" s="63" t="inlineStr">
         <is>
           <t>ANNUAL PENSION ($)</t>
         </is>
       </c>
-      <c r="B33" s="62">
+      <c r="B33" s="64">
         <f>B32*B28</f>
         <v/>
       </c>
@@ -14256,636 +14270,636 @@
           <t>Monthly pension ($)</t>
         </is>
       </c>
-      <c r="B34" s="58">
+      <c r="B34" s="60">
         <f>B33/12</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="42" t="inlineStr">
+      <c r="A36" s="44" t="inlineStr">
         <is>
           <t>⑤ PROJECTION BY RETIREMENT AGE  (finds the earliest 80% cap)</t>
         </is>
       </c>
-      <c r="B36" s="43" t="n"/>
-      <c r="C36" s="43" t="n"/>
-      <c r="D36" s="43" t="n"/>
-      <c r="E36" s="43" t="n"/>
-      <c r="F36" s="43" t="n"/>
-      <c r="G36" s="43" t="n"/>
-      <c r="H36" s="43" t="n"/>
-      <c r="I36" s="43" t="n"/>
-      <c r="J36" s="43" t="n"/>
+      <c r="B36" s="45" t="n"/>
+      <c r="C36" s="45" t="n"/>
+      <c r="D36" s="45" t="n"/>
+      <c r="E36" s="45" t="n"/>
+      <c r="F36" s="45" t="n"/>
+      <c r="G36" s="45" t="n"/>
+      <c r="H36" s="45" t="n"/>
+      <c r="I36" s="45" t="n"/>
+      <c r="J36" s="45" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1" s="39">
-      <c r="A37" s="63" t="inlineStr">
+      <c r="A37" s="65" t="inlineStr">
         <is>
           <t>Retire age</t>
         </is>
       </c>
-      <c r="B37" s="63" t="inlineStr">
+      <c r="B37" s="65" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C37" s="63" t="inlineStr">
+      <c r="C37" s="65" t="inlineStr">
         <is>
           <t>Cred. svc</t>
         </is>
       </c>
-      <c r="D37" s="63" t="inlineStr">
+      <c r="D37" s="65" t="inlineStr">
         <is>
           <t>Age factor</t>
         </is>
       </c>
-      <c r="E37" s="63" t="inlineStr">
+      <c r="E37" s="65" t="inlineStr">
         <is>
           <t>Regular %</t>
         </is>
       </c>
-      <c r="F37" s="63" t="inlineStr">
+      <c r="F37" s="65" t="inlineStr">
         <is>
           <t>R+ elig?</t>
         </is>
       </c>
-      <c r="G37" s="63" t="inlineStr">
+      <c r="G37" s="65" t="inlineStr">
         <is>
           <t>R+ %</t>
         </is>
       </c>
-      <c r="H37" s="63" t="inlineStr">
+      <c r="H37" s="65" t="inlineStr">
         <is>
           <t>Applied %</t>
         </is>
       </c>
-      <c r="I37" s="63" t="inlineStr">
+      <c r="I37" s="65" t="inlineStr">
         <is>
           <t>Annual pension $</t>
         </is>
       </c>
-      <c r="J37" s="63" t="inlineStr">
+      <c r="J37" s="65" t="inlineStr">
         <is>
           <t>80% cap?</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="53" t="n">
+      <c r="A38" s="55" t="n">
         <v>55</v>
       </c>
-      <c r="B38" s="53">
+      <c r="B38" s="55">
         <f>$B$12+(A38-$B$11)</f>
         <v/>
       </c>
-      <c r="C38" s="64">
+      <c r="C38" s="66">
         <f>$B$6+(A38-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D38" s="54">
+      <c r="D38" s="56">
         <f>IF(A38&lt;55,0,IF(A38&gt;=65,0.025,0.015+(A38-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E38" s="54">
+      <c r="E38" s="56">
         <f>MIN($B$21,D38*C38)</f>
         <v/>
       </c>
-      <c r="F38" s="53">
+      <c r="F38" s="55">
         <f>IF(AND($B$7="Y",C38&gt;=30,$B$8+(A38-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G38" s="54">
+      <c r="G38" s="56">
         <f>MIN($B$21,D38*C38+0.02*MAX(0,C38-24))</f>
         <v/>
       </c>
-      <c r="H38" s="65">
+      <c r="H38" s="67">
         <f>IF(F38="Y",G38,E38)</f>
         <v/>
       </c>
-      <c r="I38" s="66">
+      <c r="I38" s="68">
         <f>H38*($B$13*((1+$B$14)^(A38-$B$11)+(1+$B$14)^(A38-$B$11-1)+(1+$B$14)^(A38-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J38" s="53">
+      <c r="J38" s="55">
         <f>IF(H38&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="53" t="n">
+      <c r="A39" s="55" t="n">
         <v>56</v>
       </c>
-      <c r="B39" s="53">
+      <c r="B39" s="55">
         <f>$B$12+(A39-$B$11)</f>
         <v/>
       </c>
-      <c r="C39" s="64">
+      <c r="C39" s="66">
         <f>$B$6+(A39-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D39" s="54">
+      <c r="D39" s="56">
         <f>IF(A39&lt;55,0,IF(A39&gt;=65,0.025,0.015+(A39-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E39" s="54">
+      <c r="E39" s="56">
         <f>MIN($B$21,D39*C39)</f>
         <v/>
       </c>
-      <c r="F39" s="53">
+      <c r="F39" s="55">
         <f>IF(AND($B$7="Y",C39&gt;=30,$B$8+(A39-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G39" s="54">
+      <c r="G39" s="56">
         <f>MIN($B$21,D39*C39+0.02*MAX(0,C39-24))</f>
         <v/>
       </c>
-      <c r="H39" s="65">
+      <c r="H39" s="67">
         <f>IF(F39="Y",G39,E39)</f>
         <v/>
       </c>
-      <c r="I39" s="66">
+      <c r="I39" s="68">
         <f>H39*($B$13*((1+$B$14)^(A39-$B$11)+(1+$B$14)^(A39-$B$11-1)+(1+$B$14)^(A39-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J39" s="53">
+      <c r="J39" s="55">
         <f>IF(H39&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="53" t="n">
+      <c r="A40" s="55" t="n">
         <v>57</v>
       </c>
-      <c r="B40" s="53">
+      <c r="B40" s="55">
         <f>$B$12+(A40-$B$11)</f>
         <v/>
       </c>
-      <c r="C40" s="64">
+      <c r="C40" s="66">
         <f>$B$6+(A40-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D40" s="54">
+      <c r="D40" s="56">
         <f>IF(A40&lt;55,0,IF(A40&gt;=65,0.025,0.015+(A40-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E40" s="54">
+      <c r="E40" s="56">
         <f>MIN($B$21,D40*C40)</f>
         <v/>
       </c>
-      <c r="F40" s="53">
+      <c r="F40" s="55">
         <f>IF(AND($B$7="Y",C40&gt;=30,$B$8+(A40-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G40" s="54">
+      <c r="G40" s="56">
         <f>MIN($B$21,D40*C40+0.02*MAX(0,C40-24))</f>
         <v/>
       </c>
-      <c r="H40" s="65">
+      <c r="H40" s="67">
         <f>IF(F40="Y",G40,E40)</f>
         <v/>
       </c>
-      <c r="I40" s="66">
+      <c r="I40" s="68">
         <f>H40*($B$13*((1+$B$14)^(A40-$B$11)+(1+$B$14)^(A40-$B$11-1)+(1+$B$14)^(A40-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J40" s="53">
+      <c r="J40" s="55">
         <f>IF(H40&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="53" t="n">
+      <c r="A41" s="55" t="n">
         <v>58</v>
       </c>
-      <c r="B41" s="53">
+      <c r="B41" s="55">
         <f>$B$12+(A41-$B$11)</f>
         <v/>
       </c>
-      <c r="C41" s="64">
+      <c r="C41" s="66">
         <f>$B$6+(A41-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D41" s="54">
+      <c r="D41" s="56">
         <f>IF(A41&lt;55,0,IF(A41&gt;=65,0.025,0.015+(A41-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E41" s="54">
+      <c r="E41" s="56">
         <f>MIN($B$21,D41*C41)</f>
         <v/>
       </c>
-      <c r="F41" s="53">
+      <c r="F41" s="55">
         <f>IF(AND($B$7="Y",C41&gt;=30,$B$8+(A41-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G41" s="54">
+      <c r="G41" s="56">
         <f>MIN($B$21,D41*C41+0.02*MAX(0,C41-24))</f>
         <v/>
       </c>
-      <c r="H41" s="65">
+      <c r="H41" s="67">
         <f>IF(F41="Y",G41,E41)</f>
         <v/>
       </c>
-      <c r="I41" s="66">
+      <c r="I41" s="68">
         <f>H41*($B$13*((1+$B$14)^(A41-$B$11)+(1+$B$14)^(A41-$B$11-1)+(1+$B$14)^(A41-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J41" s="53">
+      <c r="J41" s="55">
         <f>IF(H41&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="53" t="n">
+      <c r="A42" s="55" t="n">
         <v>59</v>
       </c>
-      <c r="B42" s="53">
+      <c r="B42" s="55">
         <f>$B$12+(A42-$B$11)</f>
         <v/>
       </c>
-      <c r="C42" s="64">
+      <c r="C42" s="66">
         <f>$B$6+(A42-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D42" s="54">
+      <c r="D42" s="56">
         <f>IF(A42&lt;55,0,IF(A42&gt;=65,0.025,0.015+(A42-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E42" s="54">
+      <c r="E42" s="56">
         <f>MIN($B$21,D42*C42)</f>
         <v/>
       </c>
-      <c r="F42" s="53">
+      <c r="F42" s="55">
         <f>IF(AND($B$7="Y",C42&gt;=30,$B$8+(A42-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G42" s="54">
+      <c r="G42" s="56">
         <f>MIN($B$21,D42*C42+0.02*MAX(0,C42-24))</f>
         <v/>
       </c>
-      <c r="H42" s="65">
+      <c r="H42" s="67">
         <f>IF(F42="Y",G42,E42)</f>
         <v/>
       </c>
-      <c r="I42" s="66">
+      <c r="I42" s="68">
         <f>H42*($B$13*((1+$B$14)^(A42-$B$11)+(1+$B$14)^(A42-$B$11-1)+(1+$B$14)^(A42-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J42" s="53">
+      <c r="J42" s="55">
         <f>IF(H42&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="53" t="n">
+      <c r="A43" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="B43" s="53">
+      <c r="B43" s="55">
         <f>$B$12+(A43-$B$11)</f>
         <v/>
       </c>
-      <c r="C43" s="64">
+      <c r="C43" s="66">
         <f>$B$6+(A43-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D43" s="54">
+      <c r="D43" s="56">
         <f>IF(A43&lt;55,0,IF(A43&gt;=65,0.025,0.015+(A43-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E43" s="54">
+      <c r="E43" s="56">
         <f>MIN($B$21,D43*C43)</f>
         <v/>
       </c>
-      <c r="F43" s="53">
+      <c r="F43" s="55">
         <f>IF(AND($B$7="Y",C43&gt;=30,$B$8+(A43-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G43" s="54">
+      <c r="G43" s="56">
         <f>MIN($B$21,D43*C43+0.02*MAX(0,C43-24))</f>
         <v/>
       </c>
-      <c r="H43" s="65">
+      <c r="H43" s="67">
         <f>IF(F43="Y",G43,E43)</f>
         <v/>
       </c>
-      <c r="I43" s="66">
+      <c r="I43" s="68">
         <f>H43*($B$13*((1+$B$14)^(A43-$B$11)+(1+$B$14)^(A43-$B$11-1)+(1+$B$14)^(A43-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J43" s="53">
+      <c r="J43" s="55">
         <f>IF(H43&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="53" t="n">
+      <c r="A44" s="55" t="n">
         <v>61</v>
       </c>
-      <c r="B44" s="53">
+      <c r="B44" s="55">
         <f>$B$12+(A44-$B$11)</f>
         <v/>
       </c>
-      <c r="C44" s="64">
+      <c r="C44" s="66">
         <f>$B$6+(A44-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D44" s="54">
+      <c r="D44" s="56">
         <f>IF(A44&lt;55,0,IF(A44&gt;=65,0.025,0.015+(A44-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E44" s="54">
+      <c r="E44" s="56">
         <f>MIN($B$21,D44*C44)</f>
         <v/>
       </c>
-      <c r="F44" s="53">
+      <c r="F44" s="55">
         <f>IF(AND($B$7="Y",C44&gt;=30,$B$8+(A44-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G44" s="54">
+      <c r="G44" s="56">
         <f>MIN($B$21,D44*C44+0.02*MAX(0,C44-24))</f>
         <v/>
       </c>
-      <c r="H44" s="65">
+      <c r="H44" s="67">
         <f>IF(F44="Y",G44,E44)</f>
         <v/>
       </c>
-      <c r="I44" s="66">
+      <c r="I44" s="68">
         <f>H44*($B$13*((1+$B$14)^(A44-$B$11)+(1+$B$14)^(A44-$B$11-1)+(1+$B$14)^(A44-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J44" s="53">
+      <c r="J44" s="55">
         <f>IF(H44&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="53" t="n">
+      <c r="A45" s="55" t="n">
         <v>62</v>
       </c>
-      <c r="B45" s="53">
+      <c r="B45" s="55">
         <f>$B$12+(A45-$B$11)</f>
         <v/>
       </c>
-      <c r="C45" s="64">
+      <c r="C45" s="66">
         <f>$B$6+(A45-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D45" s="54">
+      <c r="D45" s="56">
         <f>IF(A45&lt;55,0,IF(A45&gt;=65,0.025,0.015+(A45-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E45" s="54">
+      <c r="E45" s="56">
         <f>MIN($B$21,D45*C45)</f>
         <v/>
       </c>
-      <c r="F45" s="53">
+      <c r="F45" s="55">
         <f>IF(AND($B$7="Y",C45&gt;=30,$B$8+(A45-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G45" s="54">
+      <c r="G45" s="56">
         <f>MIN($B$21,D45*C45+0.02*MAX(0,C45-24))</f>
         <v/>
       </c>
-      <c r="H45" s="65">
+      <c r="H45" s="67">
         <f>IF(F45="Y",G45,E45)</f>
         <v/>
       </c>
-      <c r="I45" s="66">
+      <c r="I45" s="68">
         <f>H45*($B$13*((1+$B$14)^(A45-$B$11)+(1+$B$14)^(A45-$B$11-1)+(1+$B$14)^(A45-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J45" s="53">
+      <c r="J45" s="55">
         <f>IF(H45&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="53" t="n">
+      <c r="A46" s="55" t="n">
         <v>63</v>
       </c>
-      <c r="B46" s="53">
+      <c r="B46" s="55">
         <f>$B$12+(A46-$B$11)</f>
         <v/>
       </c>
-      <c r="C46" s="64">
+      <c r="C46" s="66">
         <f>$B$6+(A46-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D46" s="54">
+      <c r="D46" s="56">
         <f>IF(A46&lt;55,0,IF(A46&gt;=65,0.025,0.015+(A46-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E46" s="54">
+      <c r="E46" s="56">
         <f>MIN($B$21,D46*C46)</f>
         <v/>
       </c>
-      <c r="F46" s="53">
+      <c r="F46" s="55">
         <f>IF(AND($B$7="Y",C46&gt;=30,$B$8+(A46-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G46" s="54">
+      <c r="G46" s="56">
         <f>MIN($B$21,D46*C46+0.02*MAX(0,C46-24))</f>
         <v/>
       </c>
-      <c r="H46" s="65">
+      <c r="H46" s="67">
         <f>IF(F46="Y",G46,E46)</f>
         <v/>
       </c>
-      <c r="I46" s="66">
+      <c r="I46" s="68">
         <f>H46*($B$13*((1+$B$14)^(A46-$B$11)+(1+$B$14)^(A46-$B$11-1)+(1+$B$14)^(A46-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J46" s="53">
+      <c r="J46" s="55">
         <f>IF(H46&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="53" t="n">
+      <c r="A47" s="55" t="n">
         <v>64</v>
       </c>
-      <c r="B47" s="53">
+      <c r="B47" s="55">
         <f>$B$12+(A47-$B$11)</f>
         <v/>
       </c>
-      <c r="C47" s="64">
+      <c r="C47" s="66">
         <f>$B$6+(A47-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D47" s="54">
+      <c r="D47" s="56">
         <f>IF(A47&lt;55,0,IF(A47&gt;=65,0.025,0.015+(A47-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E47" s="54">
+      <c r="E47" s="56">
         <f>MIN($B$21,D47*C47)</f>
         <v/>
       </c>
-      <c r="F47" s="53">
+      <c r="F47" s="55">
         <f>IF(AND($B$7="Y",C47&gt;=30,$B$8+(A47-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G47" s="54">
+      <c r="G47" s="56">
         <f>MIN($B$21,D47*C47+0.02*MAX(0,C47-24))</f>
         <v/>
       </c>
-      <c r="H47" s="65">
+      <c r="H47" s="67">
         <f>IF(F47="Y",G47,E47)</f>
         <v/>
       </c>
-      <c r="I47" s="66">
+      <c r="I47" s="68">
         <f>H47*($B$13*((1+$B$14)^(A47-$B$11)+(1+$B$14)^(A47-$B$11-1)+(1+$B$14)^(A47-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J47" s="53">
+      <c r="J47" s="55">
         <f>IF(H47&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="53" t="n">
+      <c r="A48" s="55" t="n">
         <v>65</v>
       </c>
-      <c r="B48" s="53">
+      <c r="B48" s="55">
         <f>$B$12+(A48-$B$11)</f>
         <v/>
       </c>
-      <c r="C48" s="64">
+      <c r="C48" s="66">
         <f>$B$6+(A48-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D48" s="54">
+      <c r="D48" s="56">
         <f>IF(A48&lt;55,0,IF(A48&gt;=65,0.025,0.015+(A48-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E48" s="54">
+      <c r="E48" s="56">
         <f>MIN($B$21,D48*C48)</f>
         <v/>
       </c>
-      <c r="F48" s="53">
+      <c r="F48" s="55">
         <f>IF(AND($B$7="Y",C48&gt;=30,$B$8+(A48-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G48" s="54">
+      <c r="G48" s="56">
         <f>MIN($B$21,D48*C48+0.02*MAX(0,C48-24))</f>
         <v/>
       </c>
-      <c r="H48" s="65">
+      <c r="H48" s="67">
         <f>IF(F48="Y",G48,E48)</f>
         <v/>
       </c>
-      <c r="I48" s="66">
+      <c r="I48" s="68">
         <f>H48*($B$13*((1+$B$14)^(A48-$B$11)+(1+$B$14)^(A48-$B$11-1)+(1+$B$14)^(A48-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J48" s="53">
+      <c r="J48" s="55">
         <f>IF(H48&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="53" t="n">
+      <c r="A49" s="55" t="n">
         <v>66</v>
       </c>
-      <c r="B49" s="53">
+      <c r="B49" s="55">
         <f>$B$12+(A49-$B$11)</f>
         <v/>
       </c>
-      <c r="C49" s="64">
+      <c r="C49" s="66">
         <f>$B$6+(A49-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D49" s="54">
+      <c r="D49" s="56">
         <f>IF(A49&lt;55,0,IF(A49&gt;=65,0.025,0.015+(A49-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E49" s="54">
+      <c r="E49" s="56">
         <f>MIN($B$21,D49*C49)</f>
         <v/>
       </c>
-      <c r="F49" s="53">
+      <c r="F49" s="55">
         <f>IF(AND($B$7="Y",C49&gt;=30,$B$8+(A49-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G49" s="54">
+      <c r="G49" s="56">
         <f>MIN($B$21,D49*C49+0.02*MAX(0,C49-24))</f>
         <v/>
       </c>
-      <c r="H49" s="65">
+      <c r="H49" s="67">
         <f>IF(F49="Y",G49,E49)</f>
         <v/>
       </c>
-      <c r="I49" s="66">
+      <c r="I49" s="68">
         <f>H49*($B$13*((1+$B$14)^(A49-$B$11)+(1+$B$14)^(A49-$B$11-1)+(1+$B$14)^(A49-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J49" s="53">
+      <c r="J49" s="55">
         <f>IF(H49&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="53" t="n">
+      <c r="A50" s="55" t="n">
         <v>67</v>
       </c>
-      <c r="B50" s="53">
+      <c r="B50" s="55">
         <f>$B$12+(A50-$B$11)</f>
         <v/>
       </c>
-      <c r="C50" s="64">
+      <c r="C50" s="66">
         <f>$B$6+(A50-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D50" s="54">
+      <c r="D50" s="56">
         <f>IF(A50&lt;55,0,IF(A50&gt;=65,0.025,0.015+(A50-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E50" s="54">
+      <c r="E50" s="56">
         <f>MIN($B$21,D50*C50)</f>
         <v/>
       </c>
-      <c r="F50" s="53">
+      <c r="F50" s="55">
         <f>IF(AND($B$7="Y",C50&gt;=30,$B$8+(A50-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G50" s="54">
+      <c r="G50" s="56">
         <f>MIN($B$21,D50*C50+0.02*MAX(0,C50-24))</f>
         <v/>
       </c>
-      <c r="H50" s="65">
+      <c r="H50" s="67">
         <f>IF(F50="Y",G50,E50)</f>
         <v/>
       </c>
-      <c r="I50" s="66">
+      <c r="I50" s="68">
         <f>H50*($B$13*((1+$B$14)^(A50-$B$11)+(1+$B$14)^(A50-$B$11-1)+(1+$B$14)^(A50-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J50" s="53">
+      <c r="J50" s="55">
         <f>IF(H50&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="61" t="inlineStr">
+      <c r="A52" s="63" t="inlineStr">
         <is>
           <t>Earliest age at 80% cap:</t>
         </is>
       </c>
-      <c r="C52" s="67">
+      <c r="C52" s="69">
         <f>IFERROR(INDEX(A38:A50,MATCH(TRUE,INDEX(H38:H50&gt;=$B$21,0),0)),"Not by 67")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="61" t="inlineStr">
+      <c r="A53" s="63" t="inlineStr">
         <is>
           <t>…in calendar year:</t>
         </is>
       </c>
-      <c r="C53" s="67">
+      <c r="C53" s="69">
         <f>IFERROR($B$12+(C52-$B$11),"—")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="68" t="inlineStr">
+      <c r="A55" s="41" t="inlineStr">
         <is>
           <t>Note: salary average is a simple projection (current salary grown by the raise rate, averaged over the final 3 years). MTRS uses actual highest-3-consecutive-year earnings. R+ enhanced benefit only applies once she reaches 30 creditable years; otherwise the regular formula applies and R+ contributions are refunded.</t>
         </is>
@@ -14918,27 +14932,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>FIRE Dashboard — Naughton Family</t>
         </is>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1" s="39">
-      <c r="A2" s="41" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Educational planning tool, not investment advice. ORANGE = assumptions you set  •  YELLOW = balances/contributions (snapshot as of now — update over time). FI math uses a REAL (inflation-adjusted) return.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>① HOUSEHOLD ASSUMPTIONS</t>
         </is>
       </c>
-      <c r="B4" s="43" t="n"/>
-      <c r="C4" s="43" t="n"/>
+      <c r="B4" s="45" t="n"/>
+      <c r="C4" s="45" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14946,7 +14960,7 @@
           <t>Matt's current age</t>
         </is>
       </c>
-      <c r="B5" s="47" t="n">
+      <c r="B5" s="49" t="n">
         <v>45</v>
       </c>
     </row>
@@ -14956,7 +14970,7 @@
           <t>Sue's current age</t>
         </is>
       </c>
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="49" t="n">
         <v>45</v>
       </c>
     </row>
@@ -14966,7 +14980,7 @@
           <t>Current calendar year</t>
         </is>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="49" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14976,10 +14990,10 @@
           <t>Target annual retirement spend ($)</t>
         </is>
       </c>
-      <c r="B8" s="48" t="n">
+      <c r="B8" s="50" t="n">
         <v>90000</v>
       </c>
-      <c r="C8" s="45" t="inlineStr">
+      <c r="C8" s="47" t="inlineStr">
         <is>
           <t>Use your Income Statement expenses as a guide.</t>
         </is>
@@ -14991,7 +15005,7 @@
           <t>Safe withdrawal rate (SWR)</t>
         </is>
       </c>
-      <c r="B9" s="69" t="n">
+      <c r="B9" s="70" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -15001,10 +15015,10 @@
           <t>Nominal expected return</t>
         </is>
       </c>
-      <c r="B10" s="69" t="n">
+      <c r="B10" s="70" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C10" s="45" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>Matches the 7% on your Scenarios tab.</t>
         </is>
@@ -15016,7 +15030,7 @@
           <t>Assumed inflation</t>
         </is>
       </c>
-      <c r="B11" s="69" t="n">
+      <c r="B11" s="70" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -15026,19 +15040,19 @@
           <t>Real return (auto)</t>
         </is>
       </c>
-      <c r="B12" s="70">
+      <c r="B12" s="71">
         <f>(1+B10)/(1+B11)-1</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="44" t="inlineStr">
         <is>
           <t>② CURRENT INVESTED ASSETS  (from Balances)</t>
         </is>
       </c>
-      <c r="B14" s="43" t="n"/>
-      <c r="C14" s="43" t="n"/>
+      <c r="B14" s="45" t="n"/>
+      <c r="C14" s="45" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15046,7 +15060,7 @@
           <t>Matt 401k (MathWorks)</t>
         </is>
       </c>
-      <c r="B15" s="71" t="n">
+      <c r="B15" s="72" t="n">
         <v>228000</v>
       </c>
     </row>
@@ -15056,7 +15070,7 @@
           <t>Sue 403b (Equitable)</t>
         </is>
       </c>
-      <c r="B16" s="71" t="n">
+      <c r="B16" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15066,7 +15080,7 @@
           <t>IRAs (Matt + Sue)</t>
         </is>
       </c>
-      <c r="B17" s="71" t="n">
+      <c r="B17" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15076,7 +15090,7 @@
           <t>HSA (invested portion)</t>
         </is>
       </c>
-      <c r="B18" s="71" t="n">
+      <c r="B18" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15086,7 +15100,7 @@
           <t>Taxable brokerage (Schwab)</t>
         </is>
       </c>
-      <c r="B19" s="71" t="n">
+      <c r="B19" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15096,22 +15110,22 @@
           <t>Cash earmarked for FI</t>
         </is>
       </c>
-      <c r="B20" s="71" t="n">
+      <c r="B20" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="45" t="inlineStr">
+      <c r="C20" s="47" t="inlineStr">
         <is>
           <t>Exclude your emergency fund.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="61" t="inlineStr">
+      <c r="A21" s="63" t="inlineStr">
         <is>
           <t>TOTAL INVESTED</t>
         </is>
       </c>
-      <c r="B21" s="62">
+      <c r="B21" s="64">
         <f>SUM(B15:B20)</f>
         <v/>
       </c>
@@ -15122,23 +15136,23 @@
           <t>(memo) 529 — excluded from FI</t>
         </is>
       </c>
-      <c r="B22" s="72" t="n">
+      <c r="B22" s="73" t="n">
         <v>14298</v>
       </c>
-      <c r="C22" s="45" t="inlineStr">
+      <c r="C22" s="47" t="inlineStr">
         <is>
           <t>Kids' college — not part of your FI number.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="A24" s="44" t="inlineStr">
         <is>
           <t>③ ANNUAL CONTRIBUTIONS</t>
         </is>
       </c>
-      <c r="B24" s="43" t="n"/>
-      <c r="C24" s="43" t="n"/>
+      <c r="B24" s="45" t="n"/>
+      <c r="C24" s="45" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15146,7 +15160,7 @@
           <t>Matt 401k (employee)</t>
         </is>
       </c>
-      <c r="B25" s="71" t="n">
+      <c r="B25" s="72" t="n">
         <v>23500</v>
       </c>
     </row>
@@ -15156,7 +15170,7 @@
           <t>Employer 401k match</t>
         </is>
       </c>
-      <c r="B26" s="71" t="n">
+      <c r="B26" s="72" t="n">
         <v>4338</v>
       </c>
     </row>
@@ -15166,7 +15180,7 @@
           <t>Sue 403b</t>
         </is>
       </c>
-      <c r="B27" s="71" t="n">
+      <c r="B27" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15176,10 +15190,10 @@
           <t>HSA</t>
         </is>
       </c>
-      <c r="B28" s="71" t="n">
+      <c r="B28" s="72" t="n">
         <v>9000</v>
       </c>
-      <c r="C28" s="45" t="inlineStr">
+      <c r="C28" s="47" t="inlineStr">
         <is>
           <t>2027 family HSA limit.</t>
         </is>
@@ -15191,7 +15205,7 @@
           <t>IRAs (both)</t>
         </is>
       </c>
-      <c r="B29" s="71" t="n">
+      <c r="B29" s="72" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -15201,7 +15215,7 @@
           <t>Taxable brokerage</t>
         </is>
       </c>
-      <c r="B30" s="71" t="n">
+      <c r="B30" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15211,29 +15225,29 @@
           <t>529</t>
         </is>
       </c>
-      <c r="B31" s="71" t="n">
+      <c r="B31" s="72" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="61" t="inlineStr">
+      <c r="A32" s="63" t="inlineStr">
         <is>
           <t>TOTAL ANNUAL INVESTED</t>
         </is>
       </c>
-      <c r="B32" s="62">
+      <c r="B32" s="64">
         <f>SUM(B25:B31)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="42" t="inlineStr">
+      <c r="A34" s="44" t="inlineStr">
         <is>
           <t>④ SAVINGS RATE</t>
         </is>
       </c>
-      <c r="B34" s="43" t="n"/>
-      <c r="C34" s="43" t="n"/>
+      <c r="B34" s="45" t="n"/>
+      <c r="C34" s="45" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15241,10 +15255,10 @@
           <t>Gross household income ($)</t>
         </is>
       </c>
-      <c r="B35" s="48" t="n">
+      <c r="B35" s="50" t="n">
         <v>229000</v>
       </c>
-      <c r="C35" s="45" t="inlineStr">
+      <c r="C35" s="47" t="inlineStr">
         <is>
           <t>Matt (~$144k) + Sue's salary.</t>
         </is>
@@ -15256,19 +15270,19 @@
           <t>Savings rate</t>
         </is>
       </c>
-      <c r="B36" s="73">
+      <c r="B36" s="74">
         <f>B32/B35</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="42" t="inlineStr">
+      <c r="A38" s="44" t="inlineStr">
         <is>
           <t>⑤ FI NUMBER  (with &amp; without the pension)</t>
         </is>
       </c>
-      <c r="B38" s="43" t="n"/>
-      <c r="C38" s="43" t="n"/>
+      <c r="B38" s="45" t="n"/>
+      <c r="C38" s="45" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -15276,11 +15290,11 @@
           <t>Gross FI number (spend ÷ SWR)</t>
         </is>
       </c>
-      <c r="B39" s="62">
+      <c r="B39" s="64">
         <f>B8/B9</f>
         <v/>
       </c>
-      <c r="C39" s="45" t="inlineStr">
+      <c r="C39" s="47" t="inlineStr">
         <is>
           <t>Portfolio-only target, today's dollars — the conservative number to aim at.</t>
         </is>
@@ -15292,11 +15306,11 @@
           <t>Sue's annual pension (from Pension tab)</t>
         </is>
       </c>
-      <c r="B40" s="72">
+      <c r="B40" s="73">
         <f>'Pension - Sue'!B33</f>
         <v/>
       </c>
-      <c r="C40" s="45" t="inlineStr">
+      <c r="C40" s="47" t="inlineStr">
         <is>
           <t>Future nominal $ (grown to her retirement) — treat the offset below as approximate.</t>
         </is>
@@ -15308,10 +15322,10 @@
           <t>Social Security household (annual, est)</t>
         </is>
       </c>
-      <c r="B41" s="48" t="n">
+      <c r="B41" s="50" t="n">
         <v>40000</v>
       </c>
-      <c r="C41" s="45" t="inlineStr">
+      <c r="C41" s="47" t="inlineStr">
         <is>
           <t>WEP/GPO repealed (2025) — Sue keeps full spousal/survivor SS. Verify her record.</t>
         </is>
@@ -15323,7 +15337,7 @@
           <t>Income floor (pension + SS)</t>
         </is>
       </c>
-      <c r="B42" s="72">
+      <c r="B42" s="73">
         <f>B40+B41</f>
         <v/>
       </c>
@@ -15334,40 +15348,40 @@
           <t>Pension+SS capitalized value</t>
         </is>
       </c>
-      <c r="B43" s="72">
+      <c r="B43" s="73">
         <f>B42/B9</f>
         <v/>
       </c>
-      <c r="C43" s="45" t="inlineStr">
+      <c r="C43" s="47" t="inlineStr">
         <is>
           <t>Roughly what that income floor is 'worth' vs a portfolio — it reduces the target below.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="61" t="inlineStr">
+      <c r="A44" s="63" t="inlineStr">
         <is>
           <t>NET FI number (target once floor starts)</t>
         </is>
       </c>
-      <c r="B44" s="62">
+      <c r="B44" s="64">
         <f>MAX(0,(B8-B42)/B9)</f>
         <v/>
       </c>
-      <c r="C44" s="45" t="inlineStr">
+      <c r="C44" s="47" t="inlineStr">
         <is>
           <t>$0 means pension+SS alone cover target spend in the traditional-retirement phase.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="42" t="inlineStr">
+      <c r="A48" s="44" t="inlineStr">
         <is>
           <t>⑥ YEARS TO FI  (portfolio-only runway)</t>
         </is>
       </c>
-      <c r="B48" s="43" t="n"/>
-      <c r="C48" s="43" t="n"/>
+      <c r="B48" s="45" t="n"/>
+      <c r="C48" s="45" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -15375,11 +15389,11 @@
           <t>Years to reach GROSS FI number</t>
         </is>
       </c>
-      <c r="B49" s="74">
+      <c r="B49" s="75">
         <f>IFERROR(NPER(B12,-B32,-B21,B39),"check inputs")</f>
         <v/>
       </c>
-      <c r="C49" s="68" t="inlineStr">
+      <c r="C49" s="41" t="inlineStr">
         <is>
           <t>Current invested + annual contributions growing at the real return. Pension+SS shorten this once they begin (see ⑤).</t>
         </is>
@@ -15391,7 +15405,7 @@
           <t>Matt's age at FI</t>
         </is>
       </c>
-      <c r="B50" s="75">
+      <c r="B50" s="76">
         <f>IF(ISNUMBER(B49),B5+B49,"—")</f>
         <v/>
       </c>
@@ -15402,19 +15416,19 @@
           <t>FI calendar year</t>
         </is>
       </c>
-      <c r="B51" s="76">
+      <c r="B51" s="77">
         <f>IF(ISNUMBER(B49),B7+B49,"—")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="42" t="inlineStr">
+      <c r="A53" s="44" t="inlineStr">
         <is>
           <t>⑦ PRE-59½ BRIDGE  (early-access runway)</t>
         </is>
       </c>
-      <c r="B53" s="43" t="n"/>
-      <c r="C53" s="43" t="n"/>
+      <c r="B53" s="45" t="n"/>
+      <c r="C53" s="45" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15422,7 +15436,7 @@
           <t>Planned early-retire age (Matt)</t>
         </is>
       </c>
-      <c r="B54" s="47" t="n">
+      <c r="B54" s="49" t="n">
         <v>55</v>
       </c>
     </row>
@@ -15432,7 +15446,7 @@
           <t>Roth IRA contributions (accessible)</t>
         </is>
       </c>
-      <c r="B55" s="71" t="n">
+      <c r="B55" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15442,7 +15456,7 @@
           <t>HSA receipt shoebox (accessible)</t>
         </is>
       </c>
-      <c r="B56" s="71" t="n">
+      <c r="B56" s="72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15452,17 +15466,17 @@
           <t>Taxable brokerage</t>
         </is>
       </c>
-      <c r="B57" s="71" t="n">
+      <c r="B57" s="72" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="61" t="inlineStr">
+      <c r="A58" s="63" t="inlineStr">
         <is>
           <t>Total accessible before 59½</t>
         </is>
       </c>
-      <c r="B58" s="62">
+      <c r="B58" s="64">
         <f>SUM(B55:B57)</f>
         <v/>
       </c>
@@ -15473,7 +15487,7 @@
           <t>Years until 59½</t>
         </is>
       </c>
-      <c r="B59" s="75">
+      <c r="B59" s="76">
         <f>59.5-B54</f>
         <v/>
       </c>
@@ -15484,10 +15498,10 @@
           <t>Annual spend uncovered in bridge ($)</t>
         </is>
       </c>
-      <c r="B60" s="48" t="n">
+      <c r="B60" s="50" t="n">
         <v>90000</v>
       </c>
-      <c r="C60" s="45" t="inlineStr">
+      <c r="C60" s="47" t="inlineStr">
         <is>
           <t>If Sue is still teaching, subtract her take-home — the gap may be small or zero.</t>
         </is>
@@ -15499,40 +15513,40 @@
           <t>Bridge need</t>
         </is>
       </c>
-      <c r="B61" s="72">
+      <c r="B61" s="73">
         <f>B59*B60</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="61" t="inlineStr">
+      <c r="A62" s="63" t="inlineStr">
         <is>
           <t>Bridge surplus / (gap)</t>
         </is>
       </c>
-      <c r="B62" s="62">
+      <c r="B62" s="64">
         <f>B58-B61</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="42" t="inlineStr">
+      <c r="A64" s="44" t="inlineStr">
         <is>
           <t>⑧ TWO-PHASE PLAN</t>
         </is>
       </c>
-      <c r="B64" s="43" t="n"/>
-      <c r="C64" s="43" t="n"/>
+      <c r="B64" s="45" t="n"/>
+      <c r="C64" s="45" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="61" t="inlineStr">
+      <c r="A65" s="63" t="inlineStr">
         <is>
           <t>Phase 1 — Matt steps back first</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="68" t="inlineStr">
+      <c r="A66" s="41" t="inlineStr">
         <is>
           <t>Sue keeps teaching: her salary + retiree-eligible health coverage bridge the household, so the portfolio keeps compounding and the pre-59½ gap above stays small.</t>
         </is>
@@ -15540,14 +15554,14 @@
     </row>
     <row r="67"/>
     <row r="68">
-      <c r="A68" s="61" t="inlineStr">
+      <c r="A68" s="63" t="inlineStr">
         <is>
           <t>Phase 2 — Sue reaches her 80% pension cap</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="77">
+      <c r="A69" s="78">
         <f>CONCATENATE("Sue hits the 80% cap at age ",'Pension - Sue'!C52," (year ",'Pension - Sue'!C53,"); ","both fully retired — the pension+SS floor then covers about ",TEXT(B42/B8,"0%")," of target spend.")</f>
         <v/>
       </c>
@@ -15590,875 +15604,875 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>Amazon — Monthly Reconciliation</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" s="39">
-      <c r="A2" s="41" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>All Amazon spend now lands in ONE bucket — 'Amazon (misc)', CC Detail row 14 — via a single regex rule (AMZN|AMAZON). Each month, split that total into real categories below. ORANGE = you enter $. The reference list at the bottom shows the actual Amazon transactions to guide the split.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>① AMAZON TOTAL TO RECONCILE  (auto — from CC Detail)</t>
         </is>
       </c>
-      <c r="B4" s="43" t="n"/>
-      <c r="C4" s="43" t="n"/>
-      <c r="D4" s="43" t="n"/>
-      <c r="E4" s="43" t="n"/>
-      <c r="F4" s="43" t="n"/>
-      <c r="G4" s="43" t="n"/>
-      <c r="H4" s="43" t="n"/>
-      <c r="I4" s="43" t="n"/>
-      <c r="J4" s="43" t="n"/>
-      <c r="K4" s="43" t="n"/>
-      <c r="L4" s="43" t="n"/>
-      <c r="M4" s="43" t="n"/>
-      <c r="N4" s="43" t="n"/>
+      <c r="B4" s="45" t="n"/>
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+      <c r="F4" s="45" t="n"/>
+      <c r="G4" s="45" t="n"/>
+      <c r="H4" s="45" t="n"/>
+      <c r="I4" s="45" t="n"/>
+      <c r="J4" s="45" t="n"/>
+      <c r="K4" s="45" t="n"/>
+      <c r="L4" s="45" t="n"/>
+      <c r="M4" s="45" t="n"/>
+      <c r="N4" s="45" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="inlineStr">
+      <c r="A5" s="79" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B5" s="51" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C5" s="51" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D5" s="51" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E5" s="51" t="inlineStr">
+      <c r="E5" s="53" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F5" s="51" t="inlineStr">
+      <c r="F5" s="53" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G5" s="51" t="inlineStr">
+      <c r="G5" s="53" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H5" s="51" t="inlineStr">
+      <c r="H5" s="53" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I5" s="51" t="inlineStr">
+      <c r="I5" s="53" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J5" s="51" t="inlineStr">
+      <c r="J5" s="53" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K5" s="51" t="inlineStr">
+      <c r="K5" s="53" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L5" s="51" t="inlineStr">
+      <c r="L5" s="53" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M5" s="51" t="inlineStr">
+      <c r="M5" s="53" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="N5" s="51" t="inlineStr">
+      <c r="N5" s="53" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="79" t="inlineStr">
+      <c r="A6" s="80" t="inlineStr">
         <is>
           <t>Amazon (misc) — to reconcile</t>
         </is>
       </c>
-      <c r="B6" s="80">
+      <c r="B6" s="81">
         <f>'CC Detail'!B14</f>
         <v/>
       </c>
-      <c r="C6" s="80">
+      <c r="C6" s="81">
         <f>'CC Detail'!C14</f>
         <v/>
       </c>
-      <c r="D6" s="80">
+      <c r="D6" s="81">
         <f>'CC Detail'!D14</f>
         <v/>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="81">
         <f>'CC Detail'!E14</f>
         <v/>
       </c>
-      <c r="F6" s="80">
+      <c r="F6" s="81">
         <f>'CC Detail'!F14</f>
         <v/>
       </c>
-      <c r="G6" s="80">
+      <c r="G6" s="81">
         <f>'CC Detail'!G14</f>
         <v/>
       </c>
-      <c r="H6" s="80">
+      <c r="H6" s="81">
         <f>'CC Detail'!H14</f>
         <v/>
       </c>
-      <c r="I6" s="80">
+      <c r="I6" s="81">
         <f>'CC Detail'!I14</f>
         <v/>
       </c>
-      <c r="J6" s="80">
+      <c r="J6" s="81">
         <f>'CC Detail'!J14</f>
         <v/>
       </c>
-      <c r="K6" s="80">
+      <c r="K6" s="81">
         <f>'CC Detail'!K14</f>
         <v/>
       </c>
-      <c r="L6" s="80">
+      <c r="L6" s="81">
         <f>'CC Detail'!L14</f>
         <v/>
       </c>
-      <c r="M6" s="80">
+      <c r="M6" s="81">
         <f>'CC Detail'!M14</f>
         <v/>
       </c>
-      <c r="N6" s="81">
+      <c r="N6" s="82">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="44" t="inlineStr">
         <is>
           <t>② ALLOCATE INTO CATEGORIES  (enter $ per month)</t>
         </is>
       </c>
-      <c r="B8" s="43" t="n"/>
-      <c r="C8" s="43" t="n"/>
-      <c r="D8" s="43" t="n"/>
-      <c r="E8" s="43" t="n"/>
-      <c r="F8" s="43" t="n"/>
-      <c r="G8" s="43" t="n"/>
-      <c r="H8" s="43" t="n"/>
-      <c r="I8" s="43" t="n"/>
-      <c r="J8" s="43" t="n"/>
-      <c r="K8" s="43" t="n"/>
-      <c r="L8" s="43" t="n"/>
-      <c r="M8" s="43" t="n"/>
-      <c r="N8" s="43" t="n"/>
+      <c r="B8" s="45" t="n"/>
+      <c r="C8" s="45" t="n"/>
+      <c r="D8" s="45" t="n"/>
+      <c r="E8" s="45" t="n"/>
+      <c r="F8" s="45" t="n"/>
+      <c r="G8" s="45" t="n"/>
+      <c r="H8" s="45" t="n"/>
+      <c r="I8" s="45" t="n"/>
+      <c r="J8" s="45" t="n"/>
+      <c r="K8" s="45" t="n"/>
+      <c r="L8" s="45" t="n"/>
+      <c r="M8" s="45" t="n"/>
+      <c r="N8" s="45" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="78" t="inlineStr">
+      <c r="A9" s="79" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B9" s="51" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C9" s="51" t="inlineStr">
+      <c r="C9" s="53" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D9" s="51" t="inlineStr">
+      <c r="D9" s="53" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E9" s="51" t="inlineStr">
+      <c r="E9" s="53" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F9" s="51" t="inlineStr">
+      <c r="F9" s="53" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G9" s="51" t="inlineStr">
+      <c r="G9" s="53" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H9" s="51" t="inlineStr">
+      <c r="H9" s="53" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I9" s="51" t="inlineStr">
+      <c r="I9" s="53" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J9" s="51" t="inlineStr">
+      <c r="J9" s="53" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K9" s="51" t="inlineStr">
+      <c r="K9" s="53" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L9" s="51" t="inlineStr">
+      <c r="L9" s="53" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M9" s="51" t="inlineStr">
+      <c r="M9" s="53" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="N9" s="51" t="inlineStr">
+      <c r="N9" s="53" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="82" t="inlineStr">
+      <c r="A10" s="83" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="B10" s="83" t="n">
+      <c r="B10" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="83" t="n">
+      <c r="C10" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="83" t="n">
+      <c r="D10" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="83" t="n">
+      <c r="E10" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="83" t="n">
+      <c r="F10" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="83" t="n">
+      <c r="G10" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="83" t="n">
+      <c r="H10" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="83" t="n">
+      <c r="I10" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="83" t="n">
+      <c r="J10" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="83" t="n">
+      <c r="K10" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="83" t="n">
+      <c r="L10" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="83" t="n">
+      <c r="M10" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="80">
+      <c r="N10" s="81">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="82" t="inlineStr">
+      <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Kids / Activities</t>
         </is>
       </c>
-      <c r="B11" s="83" t="n">
+      <c r="B11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="83" t="n">
+      <c r="C11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="83" t="n">
+      <c r="D11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="83" t="n">
+      <c r="E11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="83" t="n">
+      <c r="F11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="83" t="n">
+      <c r="G11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="83" t="n">
+      <c r="H11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="83" t="n">
+      <c r="I11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="83" t="n">
+      <c r="J11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="83" t="n">
+      <c r="K11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="83" t="n">
+      <c r="L11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="83" t="n">
+      <c r="M11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="80">
+      <c r="N11" s="81">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="82" t="inlineStr">
+      <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Personal Care</t>
         </is>
       </c>
-      <c r="B12" s="83" t="n">
+      <c r="B12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="83" t="n">
+      <c r="C12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="83" t="n">
+      <c r="D12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="83" t="n">
+      <c r="E12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="83" t="n">
+      <c r="F12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="83" t="n">
+      <c r="G12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="83" t="n">
+      <c r="H12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="83" t="n">
+      <c r="I12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="83" t="n">
+      <c r="J12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="83" t="n">
+      <c r="K12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="83" t="n">
+      <c r="L12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="83" t="n">
+      <c r="M12" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="80">
+      <c r="N12" s="81">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="82" t="inlineStr">
+      <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Pharmacy / Health</t>
         </is>
       </c>
-      <c r="B13" s="83" t="n">
+      <c r="B13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="83" t="n">
+      <c r="C13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="83" t="n">
+      <c r="D13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="83" t="n">
+      <c r="E13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="83" t="n">
+      <c r="F13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="83" t="n">
+      <c r="G13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="83" t="n">
+      <c r="H13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="83" t="n">
+      <c r="I13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="83" t="n">
+      <c r="J13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="83" t="n">
+      <c r="K13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="83" t="n">
+      <c r="L13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="83" t="n">
+      <c r="M13" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="80">
+      <c r="N13" s="81">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="82" t="inlineStr">
+      <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Home / Hardware</t>
         </is>
       </c>
-      <c r="B14" s="83" t="n">
+      <c r="B14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="83" t="n">
+      <c r="C14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="83" t="n">
+      <c r="D14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="83" t="n">
+      <c r="E14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="83" t="n">
+      <c r="F14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="83" t="n">
+      <c r="G14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="83" t="n">
+      <c r="H14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="83" t="n">
+      <c r="I14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="83" t="n">
+      <c r="J14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="83" t="n">
+      <c r="K14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="83" t="n">
+      <c r="L14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="83" t="n">
+      <c r="M14" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="80">
+      <c r="N14" s="81">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="82" t="inlineStr">
+      <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Subscriptions (Prime/Kindle/Audible)</t>
         </is>
       </c>
-      <c r="B15" s="83" t="n">
+      <c r="B15" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="83" t="n">
+      <c r="C15" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="83" t="n">
+      <c r="D15" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="83" t="n">
+      <c r="E15" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="83" t="n">
+      <c r="F15" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="83" t="n">
+      <c r="G15" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="83" t="n">
+      <c r="H15" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="83" t="n">
+      <c r="I15" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="83" t="n">
+      <c r="J15" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="83" t="n">
+      <c r="K15" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="83" t="n">
+      <c r="L15" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="83" t="n">
+      <c r="M15" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="80">
+      <c r="N15" s="81">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="82" t="inlineStr">
+      <c r="A16" s="83" t="inlineStr">
         <is>
           <t>Other / gifts</t>
         </is>
       </c>
-      <c r="B16" s="83" t="n">
+      <c r="B16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="83" t="n">
+      <c r="C16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="83" t="n">
+      <c r="D16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="83" t="n">
+      <c r="E16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="83" t="n">
+      <c r="F16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="83" t="n">
+      <c r="G16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="83" t="n">
+      <c r="H16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="83" t="n">
+      <c r="I16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="83" t="n">
+      <c r="J16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="83" t="n">
+      <c r="K16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="83" t="n">
+      <c r="L16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="83" t="n">
+      <c r="M16" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="80">
+      <c r="N16" s="81">
         <f>SUM(B16:M16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="79" t="inlineStr">
+      <c r="A17" s="80" t="inlineStr">
         <is>
           <t>Allocated total</t>
         </is>
       </c>
-      <c r="B17" s="84">
+      <c r="B17" s="85">
         <f>SUM(B10:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="84">
+      <c r="C17" s="85">
         <f>SUM(C10:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="84">
+      <c r="D17" s="85">
         <f>SUM(D10:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="84">
+      <c r="E17" s="85">
         <f>SUM(E10:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="84">
+      <c r="F17" s="85">
         <f>SUM(F10:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="84">
+      <c r="G17" s="85">
         <f>SUM(G10:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="84">
+      <c r="H17" s="85">
         <f>SUM(H10:H16)</f>
         <v/>
       </c>
-      <c r="I17" s="84">
+      <c r="I17" s="85">
         <f>SUM(I10:I16)</f>
         <v/>
       </c>
-      <c r="J17" s="84">
+      <c r="J17" s="85">
         <f>SUM(J10:J16)</f>
         <v/>
       </c>
-      <c r="K17" s="84">
+      <c r="K17" s="85">
         <f>SUM(K10:K16)</f>
         <v/>
       </c>
-      <c r="L17" s="84">
+      <c r="L17" s="85">
         <f>SUM(L10:L16)</f>
         <v/>
       </c>
-      <c r="M17" s="84">
+      <c r="M17" s="85">
         <f>SUM(M10:M16)</f>
         <v/>
       </c>
-      <c r="N17" s="84">
+      <c r="N17" s="85">
         <f>SUM(N10:N16)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="79" t="inlineStr">
+      <c r="A18" s="80" t="inlineStr">
         <is>
           <t>Unallocated remaining</t>
         </is>
       </c>
-      <c r="B18" s="81">
+      <c r="B18" s="82">
         <f>B6-B17</f>
         <v/>
       </c>
-      <c r="C18" s="81">
+      <c r="C18" s="82">
         <f>C6-C17</f>
         <v/>
       </c>
-      <c r="D18" s="81">
+      <c r="D18" s="82">
         <f>D6-D17</f>
         <v/>
       </c>
-      <c r="E18" s="81">
+      <c r="E18" s="82">
         <f>E6-E17</f>
         <v/>
       </c>
-      <c r="F18" s="81">
+      <c r="F18" s="82">
         <f>F6-F17</f>
         <v/>
       </c>
-      <c r="G18" s="81">
+      <c r="G18" s="82">
         <f>G6-G17</f>
         <v/>
       </c>
-      <c r="H18" s="81">
+      <c r="H18" s="82">
         <f>H6-H17</f>
         <v/>
       </c>
-      <c r="I18" s="81">
+      <c r="I18" s="82">
         <f>I6-I17</f>
         <v/>
       </c>
-      <c r="J18" s="81">
+      <c r="J18" s="82">
         <f>J6-J17</f>
         <v/>
       </c>
-      <c r="K18" s="81">
+      <c r="K18" s="82">
         <f>K6-K17</f>
         <v/>
       </c>
-      <c r="L18" s="81">
+      <c r="L18" s="82">
         <f>L6-L17</f>
         <v/>
       </c>
-      <c r="M18" s="81">
+      <c r="M18" s="82">
         <f>M6-M17</f>
         <v/>
       </c>
-      <c r="N18" s="81">
+      <c r="N18" s="82">
         <f>N6-N17</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="42" t="inlineStr">
+      <c r="A20" s="44" t="inlineStr">
         <is>
           <t>③ RECONCILED CATEGORY TOTALS (YTD) — the un-muddied picture</t>
         </is>
       </c>
-      <c r="B20" s="43" t="n"/>
-      <c r="C20" s="43" t="n"/>
-      <c r="D20" s="43" t="n"/>
+      <c r="B20" s="45" t="n"/>
+      <c r="C20" s="45" t="n"/>
+      <c r="D20" s="45" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="78" t="inlineStr">
+      <c r="A21" s="79" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B21" s="51" t="inlineStr">
+      <c r="B21" s="53" t="inlineStr">
         <is>
           <t>Native (CC Detail)</t>
         </is>
       </c>
-      <c r="C21" s="51" t="inlineStr">
+      <c r="C21" s="53" t="inlineStr">
         <is>
           <t>+ Amazon</t>
         </is>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="53">
         <f> True total (YTD)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="82" t="inlineStr">
+      <c r="A22" s="83" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="B22" s="80">
+      <c r="B22" s="81">
         <f>'CC Detail'!N5</f>
         <v/>
       </c>
-      <c r="C22" s="80">
+      <c r="C22" s="81">
         <f>N10</f>
         <v/>
       </c>
-      <c r="D22" s="81">
+      <c r="D22" s="82">
         <f>B22+C22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="82" t="inlineStr">
+      <c r="A23" s="83" t="inlineStr">
         <is>
           <t>Kids / Activities</t>
         </is>
       </c>
-      <c r="B23" s="80">
+      <c r="B23" s="81">
         <f>'CC Detail'!N9</f>
         <v/>
       </c>
-      <c r="C23" s="80">
+      <c r="C23" s="81">
         <f>N11</f>
         <v/>
       </c>
-      <c r="D23" s="81">
+      <c r="D23" s="82">
         <f>B23+C23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="82" t="inlineStr">
+      <c r="A24" s="83" t="inlineStr">
         <is>
           <t>Personal Care</t>
         </is>
       </c>
-      <c r="B24" s="80">
+      <c r="B24" s="81">
         <f>'CC Detail'!N11</f>
         <v/>
       </c>
-      <c r="C24" s="80">
+      <c r="C24" s="81">
         <f>N12</f>
         <v/>
       </c>
-      <c r="D24" s="81">
+      <c r="D24" s="82">
         <f>B24+C24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="82" t="inlineStr">
+      <c r="A25" s="83" t="inlineStr">
         <is>
           <t>Pharmacy / Health</t>
         </is>
       </c>
-      <c r="B25" s="80">
+      <c r="B25" s="81">
         <f>'CC Detail'!N12</f>
         <v/>
       </c>
-      <c r="C25" s="80">
+      <c r="C25" s="81">
         <f>N13</f>
         <v/>
       </c>
-      <c r="D25" s="81">
+      <c r="D25" s="82">
         <f>B25+C25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="82" t="inlineStr">
+      <c r="A26" s="83" t="inlineStr">
         <is>
           <t>Home / Hardware</t>
         </is>
       </c>
-      <c r="B26" s="80">
+      <c r="B26" s="81">
         <f>'CC Detail'!N13</f>
         <v/>
       </c>
-      <c r="C26" s="80">
+      <c r="C26" s="81">
         <f>N14</f>
         <v/>
       </c>
-      <c r="D26" s="81">
+      <c r="D26" s="82">
         <f>B26+C26</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="82" t="inlineStr">
+      <c r="A27" s="83" t="inlineStr">
         <is>
           <t>Subscriptions</t>
         </is>
       </c>
-      <c r="B27" s="80">
+      <c r="B27" s="81">
         <f>'CC Detail'!N8</f>
         <v/>
       </c>
-      <c r="C27" s="80">
+      <c r="C27" s="81">
         <f>N15</f>
         <v/>
       </c>
-      <c r="D27" s="81">
+      <c r="D27" s="82">
         <f>B27+C27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="82" t="inlineStr">
+      <c r="A28" s="83" t="inlineStr">
         <is>
           <t>Other / gifts</t>
         </is>
       </c>
-      <c r="B28" s="80">
+      <c r="B28" s="81">
         <f>'CC Detail'!N17</f>
         <v/>
       </c>
-      <c r="C28" s="80">
+      <c r="C28" s="81">
         <f>N16</f>
         <v/>
       </c>
-      <c r="D28" s="81">
+      <c r="D28" s="82">
         <f>B28+C28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="68" t="inlineStr">
+      <c r="A29" s="41" t="inlineStr">
         <is>
           <t>Note: once split, these 'true totals' show real spend per category — Amazon no longer hides hardware, hygiene, and kids' purchases in one lump. Feed these into the guardrail when it's built.</t>
         </is>
@@ -16466,39 +16480,39 @@
     </row>
     <row r="30"/>
     <row r="32">
-      <c r="A32" s="42" t="inlineStr">
+      <c r="A32" s="44" t="inlineStr">
         <is>
           <t>④ REFERENCE — current Amazon transactions  (auto, read-only)</t>
         </is>
       </c>
-      <c r="B32" s="43" t="n"/>
-      <c r="C32" s="43" t="n"/>
-      <c r="D32" s="43" t="n"/>
+      <c r="B32" s="45" t="n"/>
+      <c r="C32" s="45" t="n"/>
+      <c r="D32" s="45" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="68" t="inlineStr">
+      <c r="A33" s="41" t="inlineStr">
         <is>
           <t>Pulls Amazon rows from your Barclay import so you can see what to split. Refreshes when you paste new data.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="78" t="inlineStr">
+      <c r="A34" s="79" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B34" s="78" t="inlineStr">
+      <c r="B34" s="79" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C34" s="51" t="inlineStr">
+      <c r="C34" s="53" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D34" s="51" t="inlineStr">
+      <c r="D34" s="53" t="inlineStr">
         <is>
           <t>Purchased by</t>
         </is>
@@ -16522,6 +16536,1837 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C55A11"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" style="39" min="1" max="1"/>
+    <col width="13" customWidth="1" style="39" min="2" max="2"/>
+    <col width="13" customWidth="1" style="39" min="3" max="3"/>
+    <col width="13" customWidth="1" style="39" min="4" max="4"/>
+    <col width="13" customWidth="1" style="39" min="5" max="5"/>
+    <col width="13" customWidth="1" style="39" min="6" max="6"/>
+    <col width="13" customWidth="1" style="39" min="7" max="7"/>
+    <col width="13" customWidth="1" style="39" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>Solar — Reinvestment &amp; Effective ROI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1" s="39">
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>Goal: redirect your former electric-bill spend into a growth vehicle so the solar's ROI compounds. ORANGE = inputs. Enphase has no CSV export, so enter the monthly energy log by hand (you can backfill Mar–Sep now, then add one row per month). Educational planning, not investment/tax advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="44" t="inlineStr">
+        <is>
+          <t>① INCENTIVES &amp; NET CAPITAL COST</t>
+        </is>
+      </c>
+      <c r="B4" s="45" t="n"/>
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+      <c r="F4" s="45" t="n"/>
+      <c r="G4" s="45" t="n"/>
+      <c r="H4" s="45" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross capital outlay</t>
+        </is>
+      </c>
+      <c r="B5" s="73">
+        <f>'Solar ROI'!N5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Federal ITC (25D)</t>
+        </is>
+      </c>
+      <c r="B6" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>$0 if placed in service in 2026 (OBBB ended 25D after 12/31/2025). If PTO by 12/31/2025, use ~0.30×gross.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MA state credit (15%, max $1,000)</t>
+        </is>
+      </c>
+      <c r="B7" s="73">
+        <f>MIN(1000,0.15*B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Other rebates / utility</t>
+        </is>
+      </c>
+      <c r="B8" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="63" t="inlineStr">
+        <is>
+          <t>NET CAPITAL COST</t>
+        </is>
+      </c>
+      <c r="B9" s="64">
+        <f>B5-B6-B7-B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>② MONTHLY ENERGY LOG  (Enphase — manual entry, kWh)</t>
+        </is>
+      </c>
+      <c r="B11" s="45" t="n"/>
+      <c r="C11" s="45" t="n"/>
+      <c r="D11" s="45" t="n"/>
+      <c r="E11" s="45" t="n"/>
+      <c r="F11" s="45" t="n"/>
+      <c r="G11" s="45" t="n"/>
+      <c r="H11" s="45" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="47" t="inlineStr">
+        <is>
+          <t>Enter each month from your Enphase report. Net export = Exported − Imported (auto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="79" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="inlineStr">
+        <is>
+          <t>Produced</t>
+        </is>
+      </c>
+      <c r="C13" s="53" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D13" s="53" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="E13" s="53" t="inlineStr">
+        <is>
+          <t>Exported</t>
+        </is>
+      </c>
+      <c r="F13" s="53" t="inlineStr">
+        <is>
+          <t>Net export</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="83" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="B14" s="86" t="n"/>
+      <c r="C14" s="86" t="n"/>
+      <c r="D14" s="86" t="n"/>
+      <c r="E14" s="86" t="n"/>
+      <c r="F14" s="87">
+        <f>E14-D14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="83" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="B15" s="86" t="n"/>
+      <c r="C15" s="86" t="n"/>
+      <c r="D15" s="86" t="n"/>
+      <c r="E15" s="86" t="n"/>
+      <c r="F15" s="87">
+        <f>E15-D15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="83" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="B16" s="86" t="n"/>
+      <c r="C16" s="86" t="n"/>
+      <c r="D16" s="86" t="n"/>
+      <c r="E16" s="86" t="n"/>
+      <c r="F16" s="87">
+        <f>E16-D16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="83" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="B17" s="86" t="n"/>
+      <c r="C17" s="86" t="n"/>
+      <c r="D17" s="86" t="n"/>
+      <c r="E17" s="86" t="n"/>
+      <c r="F17" s="87">
+        <f>E17-D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="83" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B18" s="86" t="n"/>
+      <c r="C18" s="86" t="n"/>
+      <c r="D18" s="86" t="n"/>
+      <c r="E18" s="86" t="n"/>
+      <c r="F18" s="87">
+        <f>E18-D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="83" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B19" s="86" t="n"/>
+      <c r="C19" s="86" t="n"/>
+      <c r="D19" s="86" t="n"/>
+      <c r="E19" s="86" t="n"/>
+      <c r="F19" s="87">
+        <f>E19-D19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="83" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B20" s="86" t="n"/>
+      <c r="C20" s="86" t="n"/>
+      <c r="D20" s="86" t="n"/>
+      <c r="E20" s="86" t="n"/>
+      <c r="F20" s="87">
+        <f>E20-D20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="83" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B21" s="86" t="n"/>
+      <c r="C21" s="86" t="n"/>
+      <c r="D21" s="86" t="n"/>
+      <c r="E21" s="86" t="n"/>
+      <c r="F21" s="87">
+        <f>E21-D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="83" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B22" s="86" t="n"/>
+      <c r="C22" s="86" t="n"/>
+      <c r="D22" s="86" t="n"/>
+      <c r="E22" s="86" t="n"/>
+      <c r="F22" s="87">
+        <f>E22-D22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="83" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B23" s="86" t="n"/>
+      <c r="C23" s="86" t="n"/>
+      <c r="D23" s="86" t="n"/>
+      <c r="E23" s="86" t="n"/>
+      <c r="F23" s="87">
+        <f>E23-D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="83" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B24" s="86" t="n"/>
+      <c r="C24" s="86" t="n"/>
+      <c r="D24" s="86" t="n"/>
+      <c r="E24" s="86" t="n"/>
+      <c r="F24" s="87">
+        <f>E24-D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="83" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="B25" s="86" t="n"/>
+      <c r="C25" s="86" t="n"/>
+      <c r="D25" s="86" t="n"/>
+      <c r="E25" s="86" t="n"/>
+      <c r="F25" s="87">
+        <f>E25-D25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="80" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B26" s="88">
+        <f>SUM(B14:B25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="88">
+        <f>SUM(C14:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="88">
+        <f>SUM(D14:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="88">
+        <f>SUM(E14:E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="88">
+        <f>SUM(F14:F25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>Latest Enphase snapshot (dashboard view): Produced 3.4 MWh · Consumed 2.6 MWh · Imported 1.3 MWh · Exported 2.2 MWh · Net exported ~872 kWh · Solar offset 134%. Replace with monthly report values above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="30">
+      <c r="A30" s="44" t="inlineStr">
+        <is>
+          <t>③ SAVINGS TO REINVEST</t>
+        </is>
+      </c>
+      <c r="B30" s="45" t="n"/>
+      <c r="C30" s="45" t="n"/>
+      <c r="D30" s="45" t="n"/>
+      <c r="E30" s="45" t="n"/>
+      <c r="F30" s="45" t="n"/>
+      <c r="G30" s="45" t="n"/>
+      <c r="H30" s="45" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Pre-solar baseline bill ($/mo)</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n">
+        <v>300</v>
+      </c>
+      <c r="C31" s="47" t="inlineStr">
+        <is>
+          <t>What you used to pay — this is the money you're freeing up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Post-solar actual bill ($/mo)</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" s="47" t="inlineStr">
+        <is>
+          <t>Fixed customer/connection charges that remain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="63" t="inlineStr">
+        <is>
+          <t>Monthly avoided cost (reinvest)</t>
+        </is>
+      </c>
+      <c r="B33" s="89">
+        <f>MAX(0,B31-B32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Annual avoided cost</t>
+        </is>
+      </c>
+      <c r="B34" s="73">
+        <f>B33*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SMART incentive ($/kWh)</t>
+        </is>
+      </c>
+      <c r="B35" s="90" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Est. annual production (kWh)</t>
+        </is>
+      </c>
+      <c r="B36" s="91" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Annual SMART payment (yrs 1–10)</t>
+        </is>
+      </c>
+      <c r="B37" s="73">
+        <f>B35*B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Blended electric rate ($/kWh)</t>
+        </is>
+      </c>
+      <c r="B38" s="90" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C38" s="47" t="inlineStr">
+        <is>
+          <t>Used to value net-metering credits from exports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="44" t="inlineStr">
+        <is>
+          <t>④ REINVESTMENT MODEL — accelerate the ROI</t>
+        </is>
+      </c>
+      <c r="B40" s="45" t="n"/>
+      <c r="C40" s="45" t="n"/>
+      <c r="D40" s="45" t="n"/>
+      <c r="E40" s="45" t="n"/>
+      <c r="F40" s="45" t="n"/>
+      <c r="G40" s="45" t="n"/>
+      <c r="H40" s="45" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Reinvestment return (nominal)</t>
+        </is>
+      </c>
+      <c r="B41" s="51" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C41" s="47" t="inlineStr">
+        <is>
+          <t>Matches the 7% on your Scenarios tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Electric rate escalation (%/yr)</t>
+        </is>
+      </c>
+      <c r="B42" s="51" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Horizon (years)</t>
+        </is>
+      </c>
+      <c r="B43" s="49" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>First full year</t>
+        </is>
+      </c>
+      <c r="B44" s="49" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1" s="39">
+      <c r="A46" s="65" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B46" s="65" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C46" s="65" t="inlineStr">
+        <is>
+          <t>Avoided cost</t>
+        </is>
+      </c>
+      <c r="D46" s="65" t="inlineStr">
+        <is>
+          <t>SMART</t>
+        </is>
+      </c>
+      <c r="E46" s="65" t="inlineStr">
+        <is>
+          <t>Reinvested/yr</t>
+        </is>
+      </c>
+      <c r="F46" s="65" t="inlineStr">
+        <is>
+          <t>Reinvested bal.</t>
+        </is>
+      </c>
+      <c r="G46" s="65" t="inlineStr">
+        <is>
+          <t>Simple cum.</t>
+        </is>
+      </c>
+      <c r="H46" s="65" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" s="92">
+        <f>$B$44+(A47-1)</f>
+        <v/>
+      </c>
+      <c r="C47" s="68">
+        <f>$B$34*(1+$B$42)^(A47-1)</f>
+        <v/>
+      </c>
+      <c r="D47" s="68">
+        <f>IF(A47&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E47" s="68">
+        <f>C47+D47</f>
+        <v/>
+      </c>
+      <c r="F47" s="85">
+        <f>E47</f>
+        <v/>
+      </c>
+      <c r="G47" s="68">
+        <f>E47</f>
+        <v/>
+      </c>
+      <c r="H47" s="83">
+        <f>IF(F47&gt;=$B$9,"◄ accelerated payback",IF(G47&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" s="92">
+        <f>$B$44+(A48-1)</f>
+        <v/>
+      </c>
+      <c r="C48" s="68">
+        <f>$B$34*(1+$B$42)^(A48-1)</f>
+        <v/>
+      </c>
+      <c r="D48" s="68">
+        <f>IF(A48&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E48" s="68">
+        <f>C48+D48</f>
+        <v/>
+      </c>
+      <c r="F48" s="85">
+        <f>F47*(1+$B$41)+E48</f>
+        <v/>
+      </c>
+      <c r="G48" s="68">
+        <f>G47+E48</f>
+        <v/>
+      </c>
+      <c r="H48" s="83">
+        <f>IF(F48&gt;=$B$9,"◄ accelerated payback",IF(G48&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" s="92">
+        <f>$B$44+(A49-1)</f>
+        <v/>
+      </c>
+      <c r="C49" s="68">
+        <f>$B$34*(1+$B$42)^(A49-1)</f>
+        <v/>
+      </c>
+      <c r="D49" s="68">
+        <f>IF(A49&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E49" s="68">
+        <f>C49+D49</f>
+        <v/>
+      </c>
+      <c r="F49" s="85">
+        <f>F48*(1+$B$41)+E49</f>
+        <v/>
+      </c>
+      <c r="G49" s="68">
+        <f>G48+E49</f>
+        <v/>
+      </c>
+      <c r="H49" s="83">
+        <f>IF(F49&gt;=$B$9,"◄ accelerated payback",IF(G49&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="55" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" s="92">
+        <f>$B$44+(A50-1)</f>
+        <v/>
+      </c>
+      <c r="C50" s="68">
+        <f>$B$34*(1+$B$42)^(A50-1)</f>
+        <v/>
+      </c>
+      <c r="D50" s="68">
+        <f>IF(A50&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E50" s="68">
+        <f>C50+D50</f>
+        <v/>
+      </c>
+      <c r="F50" s="85">
+        <f>F49*(1+$B$41)+E50</f>
+        <v/>
+      </c>
+      <c r="G50" s="68">
+        <f>G49+E50</f>
+        <v/>
+      </c>
+      <c r="H50" s="83">
+        <f>IF(F50&gt;=$B$9,"◄ accelerated payback",IF(G50&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="B51" s="92">
+        <f>$B$44+(A51-1)</f>
+        <v/>
+      </c>
+      <c r="C51" s="68">
+        <f>$B$34*(1+$B$42)^(A51-1)</f>
+        <v/>
+      </c>
+      <c r="D51" s="68">
+        <f>IF(A51&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E51" s="68">
+        <f>C51+D51</f>
+        <v/>
+      </c>
+      <c r="F51" s="85">
+        <f>F50*(1+$B$41)+E51</f>
+        <v/>
+      </c>
+      <c r="G51" s="68">
+        <f>G50+E51</f>
+        <v/>
+      </c>
+      <c r="H51" s="83">
+        <f>IF(F51&gt;=$B$9,"◄ accelerated payback",IF(G51&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="55" t="n">
+        <v>6</v>
+      </c>
+      <c r="B52" s="92">
+        <f>$B$44+(A52-1)</f>
+        <v/>
+      </c>
+      <c r="C52" s="68">
+        <f>$B$34*(1+$B$42)^(A52-1)</f>
+        <v/>
+      </c>
+      <c r="D52" s="68">
+        <f>IF(A52&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E52" s="68">
+        <f>C52+D52</f>
+        <v/>
+      </c>
+      <c r="F52" s="85">
+        <f>F51*(1+$B$41)+E52</f>
+        <v/>
+      </c>
+      <c r="G52" s="68">
+        <f>G51+E52</f>
+        <v/>
+      </c>
+      <c r="H52" s="83">
+        <f>IF(F52&gt;=$B$9,"◄ accelerated payback",IF(G52&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="55" t="n">
+        <v>7</v>
+      </c>
+      <c r="B53" s="92">
+        <f>$B$44+(A53-1)</f>
+        <v/>
+      </c>
+      <c r="C53" s="68">
+        <f>$B$34*(1+$B$42)^(A53-1)</f>
+        <v/>
+      </c>
+      <c r="D53" s="68">
+        <f>IF(A53&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E53" s="68">
+        <f>C53+D53</f>
+        <v/>
+      </c>
+      <c r="F53" s="85">
+        <f>F52*(1+$B$41)+E53</f>
+        <v/>
+      </c>
+      <c r="G53" s="68">
+        <f>G52+E53</f>
+        <v/>
+      </c>
+      <c r="H53" s="83">
+        <f>IF(F53&gt;=$B$9,"◄ accelerated payback",IF(G53&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="55" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" s="92">
+        <f>$B$44+(A54-1)</f>
+        <v/>
+      </c>
+      <c r="C54" s="68">
+        <f>$B$34*(1+$B$42)^(A54-1)</f>
+        <v/>
+      </c>
+      <c r="D54" s="68">
+        <f>IF(A54&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E54" s="68">
+        <f>C54+D54</f>
+        <v/>
+      </c>
+      <c r="F54" s="85">
+        <f>F53*(1+$B$41)+E54</f>
+        <v/>
+      </c>
+      <c r="G54" s="68">
+        <f>G53+E54</f>
+        <v/>
+      </c>
+      <c r="H54" s="83">
+        <f>IF(F54&gt;=$B$9,"◄ accelerated payback",IF(G54&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="55" t="n">
+        <v>9</v>
+      </c>
+      <c r="B55" s="92">
+        <f>$B$44+(A55-1)</f>
+        <v/>
+      </c>
+      <c r="C55" s="68">
+        <f>$B$34*(1+$B$42)^(A55-1)</f>
+        <v/>
+      </c>
+      <c r="D55" s="68">
+        <f>IF(A55&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E55" s="68">
+        <f>C55+D55</f>
+        <v/>
+      </c>
+      <c r="F55" s="85">
+        <f>F54*(1+$B$41)+E55</f>
+        <v/>
+      </c>
+      <c r="G55" s="68">
+        <f>G54+E55</f>
+        <v/>
+      </c>
+      <c r="H55" s="83">
+        <f>IF(F55&gt;=$B$9,"◄ accelerated payback",IF(G55&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="B56" s="92">
+        <f>$B$44+(A56-1)</f>
+        <v/>
+      </c>
+      <c r="C56" s="68">
+        <f>$B$34*(1+$B$42)^(A56-1)</f>
+        <v/>
+      </c>
+      <c r="D56" s="68">
+        <f>IF(A56&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E56" s="68">
+        <f>C56+D56</f>
+        <v/>
+      </c>
+      <c r="F56" s="85">
+        <f>F55*(1+$B$41)+E56</f>
+        <v/>
+      </c>
+      <c r="G56" s="68">
+        <f>G55+E56</f>
+        <v/>
+      </c>
+      <c r="H56" s="83">
+        <f>IF(F56&gt;=$B$9,"◄ accelerated payback",IF(G56&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="55" t="n">
+        <v>11</v>
+      </c>
+      <c r="B57" s="92">
+        <f>$B$44+(A57-1)</f>
+        <v/>
+      </c>
+      <c r="C57" s="68">
+        <f>$B$34*(1+$B$42)^(A57-1)</f>
+        <v/>
+      </c>
+      <c r="D57" s="68">
+        <f>IF(A57&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E57" s="68">
+        <f>C57+D57</f>
+        <v/>
+      </c>
+      <c r="F57" s="85">
+        <f>F56*(1+$B$41)+E57</f>
+        <v/>
+      </c>
+      <c r="G57" s="68">
+        <f>G56+E57</f>
+        <v/>
+      </c>
+      <c r="H57" s="83">
+        <f>IF(F57&gt;=$B$9,"◄ accelerated payback",IF(G57&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="55" t="n">
+        <v>12</v>
+      </c>
+      <c r="B58" s="92">
+        <f>$B$44+(A58-1)</f>
+        <v/>
+      </c>
+      <c r="C58" s="68">
+        <f>$B$34*(1+$B$42)^(A58-1)</f>
+        <v/>
+      </c>
+      <c r="D58" s="68">
+        <f>IF(A58&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E58" s="68">
+        <f>C58+D58</f>
+        <v/>
+      </c>
+      <c r="F58" s="85">
+        <f>F57*(1+$B$41)+E58</f>
+        <v/>
+      </c>
+      <c r="G58" s="68">
+        <f>G57+E58</f>
+        <v/>
+      </c>
+      <c r="H58" s="83">
+        <f>IF(F58&gt;=$B$9,"◄ accelerated payback",IF(G58&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="55" t="n">
+        <v>13</v>
+      </c>
+      <c r="B59" s="92">
+        <f>$B$44+(A59-1)</f>
+        <v/>
+      </c>
+      <c r="C59" s="68">
+        <f>$B$34*(1+$B$42)^(A59-1)</f>
+        <v/>
+      </c>
+      <c r="D59" s="68">
+        <f>IF(A59&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E59" s="68">
+        <f>C59+D59</f>
+        <v/>
+      </c>
+      <c r="F59" s="85">
+        <f>F58*(1+$B$41)+E59</f>
+        <v/>
+      </c>
+      <c r="G59" s="68">
+        <f>G58+E59</f>
+        <v/>
+      </c>
+      <c r="H59" s="83">
+        <f>IF(F59&gt;=$B$9,"◄ accelerated payback",IF(G59&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="55" t="n">
+        <v>14</v>
+      </c>
+      <c r="B60" s="92">
+        <f>$B$44+(A60-1)</f>
+        <v/>
+      </c>
+      <c r="C60" s="68">
+        <f>$B$34*(1+$B$42)^(A60-1)</f>
+        <v/>
+      </c>
+      <c r="D60" s="68">
+        <f>IF(A60&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E60" s="68">
+        <f>C60+D60</f>
+        <v/>
+      </c>
+      <c r="F60" s="85">
+        <f>F59*(1+$B$41)+E60</f>
+        <v/>
+      </c>
+      <c r="G60" s="68">
+        <f>G59+E60</f>
+        <v/>
+      </c>
+      <c r="H60" s="83">
+        <f>IF(F60&gt;=$B$9,"◄ accelerated payback",IF(G60&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="55" t="n">
+        <v>15</v>
+      </c>
+      <c r="B61" s="92">
+        <f>$B$44+(A61-1)</f>
+        <v/>
+      </c>
+      <c r="C61" s="68">
+        <f>$B$34*(1+$B$42)^(A61-1)</f>
+        <v/>
+      </c>
+      <c r="D61" s="68">
+        <f>IF(A61&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E61" s="68">
+        <f>C61+D61</f>
+        <v/>
+      </c>
+      <c r="F61" s="85">
+        <f>F60*(1+$B$41)+E61</f>
+        <v/>
+      </c>
+      <c r="G61" s="68">
+        <f>G60+E61</f>
+        <v/>
+      </c>
+      <c r="H61" s="83">
+        <f>IF(F61&gt;=$B$9,"◄ accelerated payback",IF(G61&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="55" t="n">
+        <v>16</v>
+      </c>
+      <c r="B62" s="92">
+        <f>$B$44+(A62-1)</f>
+        <v/>
+      </c>
+      <c r="C62" s="68">
+        <f>$B$34*(1+$B$42)^(A62-1)</f>
+        <v/>
+      </c>
+      <c r="D62" s="68">
+        <f>IF(A62&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E62" s="68">
+        <f>C62+D62</f>
+        <v/>
+      </c>
+      <c r="F62" s="85">
+        <f>F61*(1+$B$41)+E62</f>
+        <v/>
+      </c>
+      <c r="G62" s="68">
+        <f>G61+E62</f>
+        <v/>
+      </c>
+      <c r="H62" s="83">
+        <f>IF(F62&gt;=$B$9,"◄ accelerated payback",IF(G62&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="55" t="n">
+        <v>17</v>
+      </c>
+      <c r="B63" s="92">
+        <f>$B$44+(A63-1)</f>
+        <v/>
+      </c>
+      <c r="C63" s="68">
+        <f>$B$34*(1+$B$42)^(A63-1)</f>
+        <v/>
+      </c>
+      <c r="D63" s="68">
+        <f>IF(A63&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E63" s="68">
+        <f>C63+D63</f>
+        <v/>
+      </c>
+      <c r="F63" s="85">
+        <f>F62*(1+$B$41)+E63</f>
+        <v/>
+      </c>
+      <c r="G63" s="68">
+        <f>G62+E63</f>
+        <v/>
+      </c>
+      <c r="H63" s="83">
+        <f>IF(F63&gt;=$B$9,"◄ accelerated payback",IF(G63&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="55" t="n">
+        <v>18</v>
+      </c>
+      <c r="B64" s="92">
+        <f>$B$44+(A64-1)</f>
+        <v/>
+      </c>
+      <c r="C64" s="68">
+        <f>$B$34*(1+$B$42)^(A64-1)</f>
+        <v/>
+      </c>
+      <c r="D64" s="68">
+        <f>IF(A64&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E64" s="68">
+        <f>C64+D64</f>
+        <v/>
+      </c>
+      <c r="F64" s="85">
+        <f>F63*(1+$B$41)+E64</f>
+        <v/>
+      </c>
+      <c r="G64" s="68">
+        <f>G63+E64</f>
+        <v/>
+      </c>
+      <c r="H64" s="83">
+        <f>IF(F64&gt;=$B$9,"◄ accelerated payback",IF(G64&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="55" t="n">
+        <v>19</v>
+      </c>
+      <c r="B65" s="92">
+        <f>$B$44+(A65-1)</f>
+        <v/>
+      </c>
+      <c r="C65" s="68">
+        <f>$B$34*(1+$B$42)^(A65-1)</f>
+        <v/>
+      </c>
+      <c r="D65" s="68">
+        <f>IF(A65&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E65" s="68">
+        <f>C65+D65</f>
+        <v/>
+      </c>
+      <c r="F65" s="85">
+        <f>F64*(1+$B$41)+E65</f>
+        <v/>
+      </c>
+      <c r="G65" s="68">
+        <f>G64+E65</f>
+        <v/>
+      </c>
+      <c r="H65" s="83">
+        <f>IF(F65&gt;=$B$9,"◄ accelerated payback",IF(G65&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="55" t="n">
+        <v>20</v>
+      </c>
+      <c r="B66" s="92">
+        <f>$B$44+(A66-1)</f>
+        <v/>
+      </c>
+      <c r="C66" s="68">
+        <f>$B$34*(1+$B$42)^(A66-1)</f>
+        <v/>
+      </c>
+      <c r="D66" s="68">
+        <f>IF(A66&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E66" s="68">
+        <f>C66+D66</f>
+        <v/>
+      </c>
+      <c r="F66" s="85">
+        <f>F65*(1+$B$41)+E66</f>
+        <v/>
+      </c>
+      <c r="G66" s="68">
+        <f>G65+E66</f>
+        <v/>
+      </c>
+      <c r="H66" s="83">
+        <f>IF(F66&gt;=$B$9,"◄ accelerated payback",IF(G66&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="55" t="n">
+        <v>21</v>
+      </c>
+      <c r="B67" s="92">
+        <f>$B$44+(A67-1)</f>
+        <v/>
+      </c>
+      <c r="C67" s="68">
+        <f>$B$34*(1+$B$42)^(A67-1)</f>
+        <v/>
+      </c>
+      <c r="D67" s="68">
+        <f>IF(A67&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E67" s="68">
+        <f>C67+D67</f>
+        <v/>
+      </c>
+      <c r="F67" s="85">
+        <f>F66*(1+$B$41)+E67</f>
+        <v/>
+      </c>
+      <c r="G67" s="68">
+        <f>G66+E67</f>
+        <v/>
+      </c>
+      <c r="H67" s="83">
+        <f>IF(F67&gt;=$B$9,"◄ accelerated payback",IF(G67&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="55" t="n">
+        <v>22</v>
+      </c>
+      <c r="B68" s="92">
+        <f>$B$44+(A68-1)</f>
+        <v/>
+      </c>
+      <c r="C68" s="68">
+        <f>$B$34*(1+$B$42)^(A68-1)</f>
+        <v/>
+      </c>
+      <c r="D68" s="68">
+        <f>IF(A68&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E68" s="68">
+        <f>C68+D68</f>
+        <v/>
+      </c>
+      <c r="F68" s="85">
+        <f>F67*(1+$B$41)+E68</f>
+        <v/>
+      </c>
+      <c r="G68" s="68">
+        <f>G67+E68</f>
+        <v/>
+      </c>
+      <c r="H68" s="83">
+        <f>IF(F68&gt;=$B$9,"◄ accelerated payback",IF(G68&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="55" t="n">
+        <v>23</v>
+      </c>
+      <c r="B69" s="92">
+        <f>$B$44+(A69-1)</f>
+        <v/>
+      </c>
+      <c r="C69" s="68">
+        <f>$B$34*(1+$B$42)^(A69-1)</f>
+        <v/>
+      </c>
+      <c r="D69" s="68">
+        <f>IF(A69&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E69" s="68">
+        <f>C69+D69</f>
+        <v/>
+      </c>
+      <c r="F69" s="85">
+        <f>F68*(1+$B$41)+E69</f>
+        <v/>
+      </c>
+      <c r="G69" s="68">
+        <f>G68+E69</f>
+        <v/>
+      </c>
+      <c r="H69" s="83">
+        <f>IF(F69&gt;=$B$9,"◄ accelerated payback",IF(G69&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="55" t="n">
+        <v>24</v>
+      </c>
+      <c r="B70" s="92">
+        <f>$B$44+(A70-1)</f>
+        <v/>
+      </c>
+      <c r="C70" s="68">
+        <f>$B$34*(1+$B$42)^(A70-1)</f>
+        <v/>
+      </c>
+      <c r="D70" s="68">
+        <f>IF(A70&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E70" s="68">
+        <f>C70+D70</f>
+        <v/>
+      </c>
+      <c r="F70" s="85">
+        <f>F69*(1+$B$41)+E70</f>
+        <v/>
+      </c>
+      <c r="G70" s="68">
+        <f>G69+E70</f>
+        <v/>
+      </c>
+      <c r="H70" s="83">
+        <f>IF(F70&gt;=$B$9,"◄ accelerated payback",IF(G70&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="55" t="n">
+        <v>25</v>
+      </c>
+      <c r="B71" s="92">
+        <f>$B$44+(A71-1)</f>
+        <v/>
+      </c>
+      <c r="C71" s="68">
+        <f>$B$34*(1+$B$42)^(A71-1)</f>
+        <v/>
+      </c>
+      <c r="D71" s="68">
+        <f>IF(A71&lt;=10,$B$37,0)</f>
+        <v/>
+      </c>
+      <c r="E71" s="68">
+        <f>C71+D71</f>
+        <v/>
+      </c>
+      <c r="F71" s="85">
+        <f>F70*(1+$B$41)+E71</f>
+        <v/>
+      </c>
+      <c r="G71" s="68">
+        <f>G70+E71</f>
+        <v/>
+      </c>
+      <c r="H71" s="83">
+        <f>IF(F71&gt;=$B$9,"◄ accelerated payback",IF(G71&gt;=$B$9,"simple payback",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="63" t="inlineStr">
+        <is>
+          <t>Simple payback (year #):</t>
+        </is>
+      </c>
+      <c r="C73" s="69">
+        <f>IFERROR(INDEX(A47:A71,MATCH(TRUE,INDEX(G47:G71&gt;=$B$9,0),0)),"&gt;25")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="63" t="inlineStr">
+        <is>
+          <t>Accelerated payback (year #):</t>
+        </is>
+      </c>
+      <c r="C74" s="69">
+        <f>IFERROR(INDEX(A47:A71,MATCH(TRUE,INDEX(F47:F71&gt;=$B$9,0),0)),"&gt;25")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="63" t="inlineStr">
+        <is>
+          <t>Reinvested value at horizon:</t>
+        </is>
+      </c>
+      <c r="C75" s="64">
+        <f>INDEX(F47:F71,MATCH($B$43,A47:A71,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="63" t="inlineStr">
+        <is>
+          <t>Net gain (value − net capital):</t>
+        </is>
+      </c>
+      <c r="C76" s="64">
+        <f>C75-B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="41" t="inlineStr">
+        <is>
+          <t>Takeaway: 'Simple payback' is when avoided bills alone repay the system. 'Accelerated payback' is when those same dollars — invested at your return — repay it. The gap between them, and the horizon value above, is the compounding you unlock by reinvesting instead of just banking lower bills. Add the monthly avoided cost (B33) to the FIRE Dashboard contributions to fold it into your savings rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79"/>
+    <row r="80"/>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="A78:H80"/>
+    <mergeCell ref="A27:H28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00548235"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" style="39" min="1" max="1"/>
+    <col width="14" customWidth="1" style="39" min="2" max="2"/>
+    <col width="50" customWidth="1" style="39" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>HSA Election Planner — November open enrollment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1" s="39">
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>Turns your freed-up cash (solar + mobile + old FSA) into a concrete HSA election for the 2027 plan year. ORANGE = inputs. Educational planning, not tax advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="44" t="inlineStr">
+        <is>
+          <t>① 2027 HSA LIMIT</t>
+        </is>
+      </c>
+      <c r="B4" s="45" t="n"/>
+      <c r="C4" s="45" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Coverage type</t>
+        </is>
+      </c>
+      <c r="B5" s="54" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2027 HSA limit (family)</t>
+        </is>
+      </c>
+      <c r="B6" s="73" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>Self-only 2027 = $4,500. Family = $9,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Catch-up (age 55+, each)</t>
+        </is>
+      </c>
+      <c r="B7" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>You're 45 — the +$1,000 each starts in 2036.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Employer HSA seed/contribution</t>
+        </is>
+      </c>
+      <c r="B8" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>If MathWorks seeds the HSA, it counts against the limit — enter it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="63" t="inlineStr">
+        <is>
+          <t>Your max employee election</t>
+        </is>
+      </c>
+      <c r="B9" s="64">
+        <f>B6+B7-B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pay periods / year</t>
+        </is>
+      </c>
+      <c r="B10" s="49" t="n">
+        <v>26</v>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>MathWorks is biweekly = 26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Max per paycheck</t>
+        </is>
+      </c>
+      <c r="B11" s="73">
+        <f>B9/B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>② FREED-UP CASH TO REDIRECT  (annual)</t>
+        </is>
+      </c>
+      <c r="B13" s="45" t="n"/>
+      <c r="C13" s="45" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Solar avoided cost (from Solar tab)</t>
+        </is>
+      </c>
+      <c r="B14" s="73">
+        <f>'Solar Reinvestment'!B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mobile / phone savings</t>
+        </is>
+      </c>
+      <c r="B15" s="50" t="n">
+        <v>600</v>
+      </c>
+      <c r="C15" s="47" t="inlineStr">
+        <is>
+          <t>From switching to the cheaper carrier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Former FSA Health Care contribution</t>
+        </is>
+      </c>
+      <c r="B16" s="50" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C16" s="47" t="inlineStr">
+        <is>
+          <t>What you were putting in the FSA (~$96/pay × 26). This moves to the HSA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other freed cash</t>
+        </is>
+      </c>
+      <c r="B17" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="63" t="inlineStr">
+        <is>
+          <t>TOTAL new annual money</t>
+        </is>
+      </c>
+      <c r="B18" s="64">
+        <f>SUM(B14:B17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>③ ELECTION PLAN</t>
+        </is>
+      </c>
+      <c r="B20" s="45" t="n"/>
+      <c r="C20" s="45" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Suggested election (fund HSA from freed cash)</t>
+        </is>
+      </c>
+      <c r="B21" s="73">
+        <f>MIN(B9,B18)</f>
+        <v/>
+      </c>
+      <c r="C21" s="47" t="inlineStr">
+        <is>
+          <t>Fund the more tax-efficient HSA first, up to the limit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Your chosen HSA election</t>
+        </is>
+      </c>
+      <c r="B22" s="50">
+        <f>B21</f>
+        <v/>
+      </c>
+      <c r="C22" s="47" t="inlineStr">
+        <is>
+          <t>Override with the number you actually elect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="63" t="inlineStr">
+        <is>
+          <t>→ Per paycheck</t>
+        </is>
+      </c>
+      <c r="B23" s="64">
+        <f>B22/B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>→ % of family limit used</t>
+        </is>
+      </c>
+      <c r="B24" s="93">
+        <f>B22/B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Remaining freed cash → IRAs</t>
+        </is>
+      </c>
+      <c r="B25" s="73">
+        <f>MAX(0,B18-B22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Extra needed to hit $9,000 max</t>
+        </is>
+      </c>
+      <c r="B26" s="73">
+        <f>MAX(0,B9-B18)</f>
+        <v/>
+      </c>
+      <c r="C26" s="47" t="inlineStr">
+        <is>
+          <t>Shortfall between freed cash and a full max — pull from elsewhere if you want to top out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>④ DECISION NOTES  (from our planning)</t>
+        </is>
+      </c>
+      <c r="B28" s="45" t="n"/>
+      <c r="C28" s="45" t="n"/>
+    </row>
+    <row r="29" ht="28" customHeight="1" s="39">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>• HSA is the most tax-efficient bucket (triple advantage + the payroll-tax break) — fund it first from freed cash, then overflow to IRAs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" s="39">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>• Orthodontia: pay out of pocket, save every receipt, let the HSA stay invested and reimburse yourself later (the 'shoebox' growth play).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" s="39">
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>• Open + fund the HSA (even $1) BEFORE the first ortho expense — expenses incurred before the account exists can never be reimbursed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" s="39">
+      <c r="A32" s="41" t="inlineStr">
+        <is>
+          <t>• Confirm your 2026 FSA has no carryover/grace period bleeding into 2027 — it can block HSA eligibility early in the year. Consider a limited-purpose (dental/vision) FSA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" s="39">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t>• 2027 IRA limit isn't official yet (~$7,500 each expected); confirm in November before finalizing the IRA split.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21350,7 +23195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="40" customWidth="1" style="39" min="1" max="1"/>
@@ -21479,18 +23324,18 @@
           <t>Tax credits / incentives</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="8" t="n"/>
+      <c r="B6" s="40" t="n"/>
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="40" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="40" t="n"/>
+      <c r="G6" s="40" t="n"/>
+      <c r="H6" s="40" t="n"/>
+      <c r="I6" s="40" t="n"/>
+      <c r="J6" s="40" t="n"/>
+      <c r="K6" s="40" t="n"/>
+      <c r="L6" s="40" t="n"/>
+      <c r="M6" s="40" t="n"/>
       <c r="N6" s="15">
         <f>SUM(B6:M6)</f>
         <v/>
@@ -21525,18 +23370,18 @@
           <t>Baseline electric (estimate)</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="8" t="n"/>
-      <c r="M9" s="8" t="n"/>
+      <c r="B9" s="40" t="n"/>
+      <c r="C9" s="40" t="n"/>
+      <c r="D9" s="40" t="n"/>
+      <c r="E9" s="40" t="n"/>
+      <c r="F9" s="40" t="n"/>
+      <c r="G9" s="40" t="n"/>
+      <c r="H9" s="40" t="n"/>
+      <c r="I9" s="40" t="n"/>
+      <c r="J9" s="40" t="n"/>
+      <c r="K9" s="40" t="n"/>
+      <c r="L9" s="40" t="n"/>
+      <c r="M9" s="40" t="n"/>
       <c r="N9" s="15">
         <f>SUM(B9:M9)</f>
         <v/>
@@ -21744,7 +23589,13 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="39"/>
+    <row r="21" ht="15.75" customHeight="1" s="39">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>⚠ To make payback compute: (1) enter pre-solar baseline monthly bills in row 9 (orange). (2) Enter incentives in row 6 — NOTE: the 30% federal solar credit (25D) ended for systems placed in service after 12/31/2025 (OBBB, 7/4/2025); if yours went live in 2026 the federal credit is $0. MA still gives a 15% state credit up to $1,000. Full reinvestment model on the 'Solar Reinvestment' tab →</t>
+        </is>
+      </c>
+    </row>
     <row r="22" ht="15.75" customHeight="1" s="39"/>
     <row r="23" ht="15.75" customHeight="1" s="39"/>
     <row r="24" ht="15.75" customHeight="1" s="39"/>
@@ -22725,7 +24576,8 @@
     <row r="999" ht="15.75" customHeight="1" s="39"/>
     <row r="1000" ht="15.75" customHeight="1" s="39"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A21:N23"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>

--- a/Family_Income_Statement_2026_v5_FIRE.xlsx
+++ b/Family_Income_Statement_2026_v5_FIRE.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Amazon Reconciliation" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Solar Reinvestment" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="HSA Election Planner" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Monthly Entry" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -248,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -417,6 +418,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18371,6 +18373,494 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" style="39" min="1" max="1"/>
+    <col width="14" customWidth="1" style="39" min="2" max="2"/>
+    <col width="46" customWidth="1" style="39" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>Monthly Entry — one place to update everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1" s="39">
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>Pick the month, fill in what you have (blanks are skipped), then run 📊 Family Finances → Post Monthly Entry. Values fan out to Balances, Solar, Amazon Reconciliation and Comp &amp; Benefits. You can also fill this from your phone via the linked Google Form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>Month to post</t>
+        </is>
+      </c>
+      <c r="B4" s="49" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="C4" s="47" t="inlineStr">
+        <is>
+          <t>Choose the month these figures belong to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Data as of (date)</t>
+        </is>
+      </c>
+      <c r="B5" s="94" t="n"/>
+      <c r="C5" s="47" t="inlineStr">
+        <is>
+          <t>Optional — for your records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>① ACCOUNT BALANCES  (month-end)</t>
+        </is>
+      </c>
+      <c r="B6" s="45" t="n"/>
+      <c r="C6" s="45" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Capital One Checking</t>
+        </is>
+      </c>
+      <c r="B7" s="50" t="n"/>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>→ Balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Capital One Savings</t>
+        </is>
+      </c>
+      <c r="B8" s="50" t="n"/>
+      <c r="C8" s="47" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Venmo float</t>
+        </is>
+      </c>
+      <c r="B9" s="50" t="n"/>
+      <c r="C9" s="47" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fidelity Money Market</t>
+        </is>
+      </c>
+      <c r="B10" s="50" t="n"/>
+      <c r="C10" s="47" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Schwab investment</t>
+        </is>
+      </c>
+      <c r="B11" s="50" t="n"/>
+      <c r="C11" s="47" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="B12" s="50" t="n"/>
+      <c r="C12" s="47" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FSA Dep Care balance</t>
+        </is>
+      </c>
+      <c r="B13" s="50" t="n"/>
+      <c r="C13" s="47" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FSA Health Care balance</t>
+        </is>
+      </c>
+      <c r="B14" s="50" t="n"/>
+      <c r="C14" s="47" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Matt 401k</t>
+        </is>
+      </c>
+      <c r="B15" s="50" t="n"/>
+      <c r="C15" s="47" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sue 403b</t>
+        </is>
+      </c>
+      <c r="B16" s="50" t="n"/>
+      <c r="C16" s="47" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sue pension (est.)</t>
+        </is>
+      </c>
+      <c r="B17" s="50" t="n"/>
+      <c r="C17" s="47" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B18" s="50" t="n"/>
+      <c r="C18" s="47" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>② SOLAR — ENERGY  (Enphase, kWh)</t>
+        </is>
+      </c>
+      <c r="B20" s="45" t="n"/>
+      <c r="C20" s="45" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Produced (kWh)</t>
+        </is>
+      </c>
+      <c r="B21" s="91" t="n"/>
+      <c r="C21" s="47" t="inlineStr">
+        <is>
+          <t>→ Solar Reinvestment log</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Consumed (kWh)</t>
+        </is>
+      </c>
+      <c r="B22" s="91" t="n"/>
+      <c r="C22" s="47" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Imported (kWh)</t>
+        </is>
+      </c>
+      <c r="B23" s="91" t="n"/>
+      <c r="C23" s="47" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Exported (kWh)</t>
+        </is>
+      </c>
+      <c r="B24" s="91" t="n"/>
+      <c r="C24" s="47" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>③ SOLAR — ELECTRIC BILL</t>
+        </is>
+      </c>
+      <c r="B25" s="45" t="n"/>
+      <c r="C25" s="45" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Baseline electric (would-have-paid)</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="47" t="inlineStr">
+        <is>
+          <t>→ Solar ROI row 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Actual electric bill</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="47" t="inlineStr">
+        <is>
+          <t>→ Solar ROI row 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>④ AMAZON — split this month's total into buckets</t>
+        </is>
+      </c>
+      <c r="B29" s="45" t="n"/>
+      <c r="C29" s="45" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Amazon total to split (auto)</t>
+        </is>
+      </c>
+      <c r="B30" s="73">
+        <f>IFERROR(INDEX('CC Detail'!B14:M14,MATCH($B$4,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="47" t="inlineStr">
+        <is>
+          <t>Pulled from CC Detail for the chosen month — split it below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="47" t="inlineStr">
+        <is>
+          <t>→ Amazon Reconciliation</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Kids / Activities</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="47" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="47" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Pharmacy / Health</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="47" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Home / Hardware</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="47" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="47" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Other / gifts</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="47" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Split check (should match total)</t>
+        </is>
+      </c>
+      <c r="B38" s="73">
+        <f>SUM(B31:B37)</f>
+        <v/>
+      </c>
+      <c r="C38" s="47" t="inlineStr">
+        <is>
+          <t>Compare to Amazon total above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="44" t="inlineStr">
+        <is>
+          <t>⑤ COMP &amp; BENEFITS  (YTD, from paystub)</t>
+        </is>
+      </c>
+      <c r="B40" s="45" t="n"/>
+      <c r="C40" s="45" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Matt gross earnings YTD</t>
+        </is>
+      </c>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="47" t="inlineStr">
+        <is>
+          <t>→ Comp &amp; Benefits</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Matt 401k contribution YTD</t>
+        </is>
+      </c>
+      <c r="B42" s="50" t="n"/>
+      <c r="C42" s="47" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Matt 401k match YTD</t>
+        </is>
+      </c>
+      <c r="B43" s="50" t="n"/>
+      <c r="C43" s="47" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FSA Dep Care YTD</t>
+        </is>
+      </c>
+      <c r="B44" s="50" t="n"/>
+      <c r="C44" s="47" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FSA Health Care YTD</t>
+        </is>
+      </c>
+      <c r="B45" s="50" t="n"/>
+      <c r="C45" s="47" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Tuition reimbursement YTD</t>
+        </is>
+      </c>
+      <c r="B46" s="50" t="n"/>
+      <c r="C46" s="47" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Stakeholder earnings YTD</t>
+        </is>
+      </c>
+      <c r="B47" s="50" t="n"/>
+      <c r="C47" s="47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Sue 403b YTD</t>
+        </is>
+      </c>
+      <c r="B48" s="50" t="n"/>
+      <c r="C48" s="47" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>529 contributions YTD</t>
+        </is>
+      </c>
+      <c r="B49" s="50" t="n"/>
+      <c r="C49" s="47" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>After posting, blank the input cells for next month (or use the Form). The script only writes fields you filled, into the month you chose above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Jan,Feb,Mar,Apr,May,Jun,Jul,Aug,Sep,Oct,Nov,Dec"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Family_Income_Statement_2026_v5_FIRE.xlsx
+++ b/Family_Income_Statement_2026_v5_FIRE.xlsx
@@ -21,6 +21,7 @@
     <sheet name="Solar Reinvestment" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="HSA Election Planner" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Monthly Entry" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Spending Guardrail" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -249,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -419,11 +420,14 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="16" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <font>
         <b val="1"/>
@@ -451,6 +455,16 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -18380,7 +18394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="39" min="1" max="1"/>
@@ -18840,20 +18854,1170 @@
       <c r="C49" s="47" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="41" t="inlineStr">
+      <c r="A51" s="44" t="inlineStr">
+        <is>
+          <t>⑥ DISCRETIONARY SPENT  (this month)</t>
+        </is>
+      </c>
+      <c r="B51" s="45" t="n"/>
+      <c r="C51" s="45" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Matt discretionary spent</t>
+        </is>
+      </c>
+      <c r="B52" s="50" t="n"/>
+      <c r="C52" s="47" t="inlineStr">
+        <is>
+          <t>→ Spending Guardrail</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sue discretionary spent</t>
+        </is>
+      </c>
+      <c r="B53" s="50" t="n"/>
+      <c r="C53" s="47" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Household discretionary spent</t>
+        </is>
+      </c>
+      <c r="B54" s="50" t="n"/>
+      <c r="C54" s="47" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="41" t="inlineStr">
         <is>
           <t>After posting, blank the input cells for next month (or use the Form). The script only writes fields you filled, into the month you chose above.</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
+    <row r="57"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="A56:C57"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Jan,Feb,Mar,Apr,May,Jun,Jul,Aug,Sep,Oct,Nov,Dec"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="39" min="1" max="1"/>
+    <col width="8" customWidth="1" style="39" min="2" max="2"/>
+    <col width="8" customWidth="1" style="39" min="3" max="3"/>
+    <col width="8" customWidth="1" style="39" min="4" max="4"/>
+    <col width="8" customWidth="1" style="39" min="5" max="5"/>
+    <col width="8" customWidth="1" style="39" min="6" max="6"/>
+    <col width="8" customWidth="1" style="39" min="7" max="7"/>
+    <col width="8" customWidth="1" style="39" min="8" max="8"/>
+    <col width="8" customWidth="1" style="39" min="9" max="9"/>
+    <col width="8" customWidth="1" style="39" min="10" max="10"/>
+    <col width="8" customWidth="1" style="39" min="11" max="11"/>
+    <col width="8" customWidth="1" style="39" min="12" max="12"/>
+    <col width="8" customWidth="1" style="39" min="13" max="13"/>
+    <col width="10" customWidth="1" style="39" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>Discretionary Spending Guardrail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1" s="39">
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>Three lanes — Matt, Sue, Household — for dinners, drinks, coffee, entertainment, convenience &amp; vices. Unused budget ROLLS OVER, so a high 'available' balance = green light to splurge; a negative one = pause. ORANGE = inputs (actuals arrive via Monthly Entry). Educational tool, not advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="44" t="inlineStr">
+        <is>
+          <t>① BUDGET CONFIG  (per month)</t>
+        </is>
+      </c>
+      <c r="B4" s="45" t="n"/>
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+      <c r="F4" s="45" t="n"/>
+      <c r="G4" s="45" t="n"/>
+      <c r="H4" s="45" t="n"/>
+      <c r="I4" s="45" t="n"/>
+      <c r="J4" s="45" t="n"/>
+      <c r="K4" s="45" t="n"/>
+      <c r="L4" s="45" t="n"/>
+      <c r="M4" s="45" t="n"/>
+      <c r="N4" s="45" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Matt monthly budget</t>
+        </is>
+      </c>
+      <c r="B5" s="50" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sue monthly budget</t>
+        </is>
+      </c>
+      <c r="B6" s="50" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Household monthly budget</t>
+        </is>
+      </c>
+      <c r="B7" s="50" t="n">
+        <v>300</v>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>Shared dinners/entertainment together — set to taste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="63" t="inlineStr">
+        <is>
+          <t>Combined monthly budget</t>
+        </is>
+      </c>
+      <c r="B8" s="95">
+        <f>B5+B6+B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Splurge-room threshold ($)</t>
+        </is>
+      </c>
+      <c r="B9" s="50" t="n">
+        <v>150</v>
+      </c>
+      <c r="C9" s="47" t="inlineStr">
+        <is>
+          <t>When a lane's rollover balance clears this, it's green to splurge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Reporting month</t>
+        </is>
+      </c>
+      <c r="B10" s="49" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>Drives the standings panel below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>② WHERE YOU STAND  (reporting month)</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="n"/>
+      <c r="C12" s="45" t="n"/>
+      <c r="D12" s="45" t="n"/>
+      <c r="E12" s="45" t="n"/>
+      <c r="F12" s="45" t="n"/>
+      <c r="G12" s="45" t="n"/>
+      <c r="H12" s="45" t="n"/>
+      <c r="I12" s="45" t="n"/>
+      <c r="J12" s="45" t="n"/>
+      <c r="K12" s="45" t="n"/>
+      <c r="L12" s="45" t="n"/>
+      <c r="M12" s="45" t="n"/>
+      <c r="N12" s="45" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="53" t="inlineStr">
+        <is>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="C13" s="53" t="inlineStr">
+        <is>
+          <t>Spent (mo)</t>
+        </is>
+      </c>
+      <c r="D13" s="53" t="inlineStr">
+        <is>
+          <t>Rollover avail.</t>
+        </is>
+      </c>
+      <c r="E13" s="53" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="83" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="B14" s="68">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C14" s="68">
+        <f>INDEX(B22:M22,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
+        <v/>
+      </c>
+      <c r="D14" s="82">
+        <f>INDEX(B23:M23,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
+        <v/>
+      </c>
+      <c r="E14" s="83">
+        <f>IF(D14="","",IF(D14&lt;0,"🔴 over — pause",IF(D14&gt;=$B$9,"🟢 splurge OK","🟡 on track")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="83" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="B15" s="68">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C15" s="68">
+        <f>INDEX(B25:M25,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
+        <v/>
+      </c>
+      <c r="D15" s="82">
+        <f>INDEX(B26:M26,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
+        <v/>
+      </c>
+      <c r="E15" s="83">
+        <f>IF(D15="","",IF(D15&lt;0,"🔴 over — pause",IF(D15&gt;=$B$9,"🟢 splurge OK","🟡 on track")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="83" t="inlineStr">
+        <is>
+          <t>Household</t>
+        </is>
+      </c>
+      <c r="B16" s="68">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="C16" s="68">
+        <f>INDEX(B28:M28,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
+        <v/>
+      </c>
+      <c r="D16" s="82">
+        <f>INDEX(B29:M29,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
+        <v/>
+      </c>
+      <c r="E16" s="83">
+        <f>IF(D16="","",IF(D16&lt;0,"🔴 over — pause",IF(D16&gt;=$B$9,"🟢 splurge OK","🟡 on track")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="80" t="inlineStr">
+        <is>
+          <t>Combined</t>
+        </is>
+      </c>
+      <c r="B17" s="68">
+        <f>B8</f>
+        <v/>
+      </c>
+      <c r="C17" s="68">
+        <f>INDEX(B30:M30,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
+        <v/>
+      </c>
+      <c r="D17" s="82">
+        <f>INDEX(B32:M32,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
+        <v/>
+      </c>
+      <c r="E17" s="83">
+        <f>IF(D17="","",IF(D17&lt;0,"🔴 over — pause",IF(D17&gt;=$B$9,"🟢 splurge OK","🟡 on track")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>③ MONTHLY TRACKER  (rollover carries forward)</t>
+        </is>
+      </c>
+      <c r="B19" s="45" t="n"/>
+      <c r="C19" s="45" t="n"/>
+      <c r="D19" s="45" t="n"/>
+      <c r="E19" s="45" t="n"/>
+      <c r="F19" s="45" t="n"/>
+      <c r="G19" s="45" t="n"/>
+      <c r="H19" s="45" t="n"/>
+      <c r="I19" s="45" t="n"/>
+      <c r="J19" s="45" t="n"/>
+      <c r="K19" s="45" t="n"/>
+      <c r="L19" s="45" t="n"/>
+      <c r="M19" s="45" t="n"/>
+      <c r="N19" s="45" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="96" t="inlineStr"/>
+      <c r="B20" s="53" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C20" s="53" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D20" s="53" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E20" s="53" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F20" s="53" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G20" s="53" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H20" s="53" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I20" s="53" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J20" s="53" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K20" s="53" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L20" s="53" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M20" s="53" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N20" s="53" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="83" t="inlineStr">
+        <is>
+          <t>Matt — Budget</t>
+        </is>
+      </c>
+      <c r="B21" s="68">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="C21" s="68">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D21" s="68">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E21" s="68">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="F21" s="68">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="G21" s="68">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="H21" s="68">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="I21" s="68">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="J21" s="68">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="K21" s="68">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="L21" s="68">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="M21" s="68">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="N21" s="68">
+        <f>SUM(B21:M21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="83" t="inlineStr">
+        <is>
+          <t>Matt — Actual (spent)</t>
+        </is>
+      </c>
+      <c r="B22" s="84" t="n"/>
+      <c r="C22" s="84" t="n"/>
+      <c r="D22" s="84" t="n"/>
+      <c r="E22" s="84" t="n"/>
+      <c r="F22" s="84" t="n"/>
+      <c r="G22" s="84" t="n"/>
+      <c r="H22" s="84" t="n"/>
+      <c r="I22" s="84" t="n"/>
+      <c r="J22" s="84" t="n"/>
+      <c r="K22" s="84" t="n"/>
+      <c r="L22" s="84" t="n"/>
+      <c r="M22" s="84" t="n"/>
+      <c r="N22" s="68">
+        <f>SUM(B22:M22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="80" t="inlineStr">
+        <is>
+          <t>Matt — Rollover available</t>
+        </is>
+      </c>
+      <c r="B23" s="85">
+        <f>B21-B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="85">
+        <f>B23+C21-C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="85">
+        <f>C23+D21-D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="85">
+        <f>D23+E21-E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="85">
+        <f>E23+F21-F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="85">
+        <f>F23+G21-G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="85">
+        <f>G23+H21-H22</f>
+        <v/>
+      </c>
+      <c r="I23" s="85">
+        <f>H23+I21-I22</f>
+        <v/>
+      </c>
+      <c r="J23" s="85">
+        <f>I23+J21-J22</f>
+        <v/>
+      </c>
+      <c r="K23" s="85">
+        <f>J23+K21-K22</f>
+        <v/>
+      </c>
+      <c r="L23" s="85">
+        <f>K23+L21-L22</f>
+        <v/>
+      </c>
+      <c r="M23" s="85">
+        <f>L23+M21-M22</f>
+        <v/>
+      </c>
+      <c r="N23" s="85">
+        <f>M23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="83" t="inlineStr">
+        <is>
+          <t>Sue — Budget</t>
+        </is>
+      </c>
+      <c r="B24" s="68">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="C24" s="68">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="D24" s="68">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="E24" s="68">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F24" s="68">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="G24" s="68">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H24" s="68">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I24" s="68">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="J24" s="68">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="K24" s="68">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="L24" s="68">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="M24" s="68">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="N24" s="68">
+        <f>SUM(B24:M24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="83" t="inlineStr">
+        <is>
+          <t>Sue — Actual (spent)</t>
+        </is>
+      </c>
+      <c r="B25" s="84" t="n"/>
+      <c r="C25" s="84" t="n"/>
+      <c r="D25" s="84" t="n"/>
+      <c r="E25" s="84" t="n"/>
+      <c r="F25" s="84" t="n"/>
+      <c r="G25" s="84" t="n"/>
+      <c r="H25" s="84" t="n"/>
+      <c r="I25" s="84" t="n"/>
+      <c r="J25" s="84" t="n"/>
+      <c r="K25" s="84" t="n"/>
+      <c r="L25" s="84" t="n"/>
+      <c r="M25" s="84" t="n"/>
+      <c r="N25" s="68">
+        <f>SUM(B25:M25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="80" t="inlineStr">
+        <is>
+          <t>Sue — Rollover available</t>
+        </is>
+      </c>
+      <c r="B26" s="85">
+        <f>B24-B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="85">
+        <f>B26+C24-C25</f>
+        <v/>
+      </c>
+      <c r="D26" s="85">
+        <f>C26+D24-D25</f>
+        <v/>
+      </c>
+      <c r="E26" s="85">
+        <f>D26+E24-E25</f>
+        <v/>
+      </c>
+      <c r="F26" s="85">
+        <f>E26+F24-F25</f>
+        <v/>
+      </c>
+      <c r="G26" s="85">
+        <f>F26+G24-G25</f>
+        <v/>
+      </c>
+      <c r="H26" s="85">
+        <f>G26+H24-H25</f>
+        <v/>
+      </c>
+      <c r="I26" s="85">
+        <f>H26+I24-I25</f>
+        <v/>
+      </c>
+      <c r="J26" s="85">
+        <f>I26+J24-J25</f>
+        <v/>
+      </c>
+      <c r="K26" s="85">
+        <f>J26+K24-K25</f>
+        <v/>
+      </c>
+      <c r="L26" s="85">
+        <f>K26+L24-L25</f>
+        <v/>
+      </c>
+      <c r="M26" s="85">
+        <f>L26+M24-M25</f>
+        <v/>
+      </c>
+      <c r="N26" s="85">
+        <f>M26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="83" t="inlineStr">
+        <is>
+          <t>Household — Budget</t>
+        </is>
+      </c>
+      <c r="B27" s="68">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="C27" s="68">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="D27" s="68">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="E27" s="68">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="F27" s="68">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="G27" s="68">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="H27" s="68">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="I27" s="68">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="J27" s="68">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="K27" s="68">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="L27" s="68">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="M27" s="68">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="N27" s="68">
+        <f>SUM(B27:M27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="83" t="inlineStr">
+        <is>
+          <t>Household — Actual (spent)</t>
+        </is>
+      </c>
+      <c r="B28" s="84" t="n"/>
+      <c r="C28" s="84" t="n"/>
+      <c r="D28" s="84" t="n"/>
+      <c r="E28" s="84" t="n"/>
+      <c r="F28" s="84" t="n"/>
+      <c r="G28" s="84" t="n"/>
+      <c r="H28" s="84" t="n"/>
+      <c r="I28" s="84" t="n"/>
+      <c r="J28" s="84" t="n"/>
+      <c r="K28" s="84" t="n"/>
+      <c r="L28" s="84" t="n"/>
+      <c r="M28" s="84" t="n"/>
+      <c r="N28" s="68">
+        <f>SUM(B28:M28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="80" t="inlineStr">
+        <is>
+          <t>Household — Rollover available</t>
+        </is>
+      </c>
+      <c r="B29" s="85">
+        <f>B27-B28</f>
+        <v/>
+      </c>
+      <c r="C29" s="85">
+        <f>B29+C27-C28</f>
+        <v/>
+      </c>
+      <c r="D29" s="85">
+        <f>C29+D27-D28</f>
+        <v/>
+      </c>
+      <c r="E29" s="85">
+        <f>D29+E27-E28</f>
+        <v/>
+      </c>
+      <c r="F29" s="85">
+        <f>E29+F27-F28</f>
+        <v/>
+      </c>
+      <c r="G29" s="85">
+        <f>F29+G27-G28</f>
+        <v/>
+      </c>
+      <c r="H29" s="85">
+        <f>G29+H27-H28</f>
+        <v/>
+      </c>
+      <c r="I29" s="85">
+        <f>H29+I27-I28</f>
+        <v/>
+      </c>
+      <c r="J29" s="85">
+        <f>I29+J27-J28</f>
+        <v/>
+      </c>
+      <c r="K29" s="85">
+        <f>J29+K27-K28</f>
+        <v/>
+      </c>
+      <c r="L29" s="85">
+        <f>K29+L27-L28</f>
+        <v/>
+      </c>
+      <c r="M29" s="85">
+        <f>L29+M27-M28</f>
+        <v/>
+      </c>
+      <c r="N29" s="85">
+        <f>M29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="83" t="inlineStr">
+        <is>
+          <t>Combined — Actual</t>
+        </is>
+      </c>
+      <c r="B30" s="68">
+        <f>B22+B25+B28</f>
+        <v/>
+      </c>
+      <c r="C30" s="68">
+        <f>C22+C25+C28</f>
+        <v/>
+      </c>
+      <c r="D30" s="68">
+        <f>D22+D25+D28</f>
+        <v/>
+      </c>
+      <c r="E30" s="68">
+        <f>E22+E25+E28</f>
+        <v/>
+      </c>
+      <c r="F30" s="68">
+        <f>F22+F25+F28</f>
+        <v/>
+      </c>
+      <c r="G30" s="68">
+        <f>G22+G25+G28</f>
+        <v/>
+      </c>
+      <c r="H30" s="68">
+        <f>H22+H25+H28</f>
+        <v/>
+      </c>
+      <c r="I30" s="68">
+        <f>I22+I25+I28</f>
+        <v/>
+      </c>
+      <c r="J30" s="68">
+        <f>J22+J25+J28</f>
+        <v/>
+      </c>
+      <c r="K30" s="68">
+        <f>K22+K25+K28</f>
+        <v/>
+      </c>
+      <c r="L30" s="68">
+        <f>L22+L25+L28</f>
+        <v/>
+      </c>
+      <c r="M30" s="68">
+        <f>M22+M25+M28</f>
+        <v/>
+      </c>
+      <c r="N30" s="68">
+        <f>SUM(B30:M30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="83" t="inlineStr">
+        <is>
+          <t>Combined — Budget</t>
+        </is>
+      </c>
+      <c r="B31" s="68">
+        <f>B21+B24+B27</f>
+        <v/>
+      </c>
+      <c r="C31" s="68">
+        <f>C21+C24+C27</f>
+        <v/>
+      </c>
+      <c r="D31" s="68">
+        <f>D21+D24+D27</f>
+        <v/>
+      </c>
+      <c r="E31" s="68">
+        <f>E21+E24+E27</f>
+        <v/>
+      </c>
+      <c r="F31" s="68">
+        <f>F21+F24+F27</f>
+        <v/>
+      </c>
+      <c r="G31" s="68">
+        <f>G21+G24+G27</f>
+        <v/>
+      </c>
+      <c r="H31" s="68">
+        <f>H21+H24+H27</f>
+        <v/>
+      </c>
+      <c r="I31" s="68">
+        <f>I21+I24+I27</f>
+        <v/>
+      </c>
+      <c r="J31" s="68">
+        <f>J21+J24+J27</f>
+        <v/>
+      </c>
+      <c r="K31" s="68">
+        <f>K21+K24+K27</f>
+        <v/>
+      </c>
+      <c r="L31" s="68">
+        <f>L21+L24+L27</f>
+        <v/>
+      </c>
+      <c r="M31" s="68">
+        <f>M21+M24+M27</f>
+        <v/>
+      </c>
+      <c r="N31" s="68">
+        <f>SUM(B31:M31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="80" t="inlineStr">
+        <is>
+          <t>Combined — Rollover available</t>
+        </is>
+      </c>
+      <c r="B32" s="85">
+        <f>B23+B26+B29</f>
+        <v/>
+      </c>
+      <c r="C32" s="85">
+        <f>C23+C26+C29</f>
+        <v/>
+      </c>
+      <c r="D32" s="85">
+        <f>D23+D26+D29</f>
+        <v/>
+      </c>
+      <c r="E32" s="85">
+        <f>E23+E26+E29</f>
+        <v/>
+      </c>
+      <c r="F32" s="85">
+        <f>F23+F26+F29</f>
+        <v/>
+      </c>
+      <c r="G32" s="85">
+        <f>G23+G26+G29</f>
+        <v/>
+      </c>
+      <c r="H32" s="85">
+        <f>H23+H26+H29</f>
+        <v/>
+      </c>
+      <c r="I32" s="85">
+        <f>I23+I26+I29</f>
+        <v/>
+      </c>
+      <c r="J32" s="85">
+        <f>J23+J26+J29</f>
+        <v/>
+      </c>
+      <c r="K32" s="85">
+        <f>K23+K26+K29</f>
+        <v/>
+      </c>
+      <c r="L32" s="85">
+        <f>L23+L26+L29</f>
+        <v/>
+      </c>
+      <c r="M32" s="85">
+        <f>M23+M26+M29</f>
+        <v/>
+      </c>
+      <c r="N32" s="85">
+        <f>M32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="inlineStr">
+        <is>
+          <t>④ IMPACT ON YOUR SAVINGS / FIRE</t>
+        </is>
+      </c>
+      <c r="B34" s="45" t="n"/>
+      <c r="C34" s="45" t="n"/>
+      <c r="D34" s="45" t="n"/>
+      <c r="E34" s="45" t="n"/>
+      <c r="F34" s="45" t="n"/>
+      <c r="G34" s="45" t="n"/>
+      <c r="H34" s="45" t="n"/>
+      <c r="I34" s="45" t="n"/>
+      <c r="J34" s="45" t="n"/>
+      <c r="K34" s="45" t="n"/>
+      <c r="L34" s="45" t="n"/>
+      <c r="M34" s="45" t="n"/>
+      <c r="N34" s="45" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>YTD combined budget</t>
+        </is>
+      </c>
+      <c r="B35" s="73">
+        <f>N31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>YTD combined actual</t>
+        </is>
+      </c>
+      <c r="B36" s="73">
+        <f>N30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="63" t="inlineStr">
+        <is>
+          <t>YTD over / (under)</t>
+        </is>
+      </c>
+      <c r="B37" s="64">
+        <f>N30-N31</f>
+        <v/>
+      </c>
+      <c r="C37" s="47" t="inlineStr">
+        <is>
+          <t>Positive = overspent (money that didn't get invested).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Growth factor (real, 20 yrs)</t>
+        </is>
+      </c>
+      <c r="B38" s="97">
+        <f>(1+'FIRE Dashboard'!B12)^20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="63" t="inlineStr">
+        <is>
+          <t>Compounded cost of overspend</t>
+        </is>
+      </c>
+      <c r="B39" s="64">
+        <f>MAX(0,B37)*B38</f>
+        <v/>
+      </c>
+      <c r="C39" s="47" t="inlineStr">
+        <is>
+          <t>What this year's overspend would be worth in 20 yrs if invested instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="41" t="inlineStr">
+        <is>
+          <t>How rollover works: each month adds the lane's budget and subtracts what you spent. Underspend and the balance grows (bank it for a guilt-free splurge later); overspend and it goes negative until you claw it back. Actuals post automatically from the Monthly Entry tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43"/>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="A41:N43"/>
+    <mergeCell ref="C7:H7"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B23:M23">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="3">
+      <formula>$B$9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:M26">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="3">
+      <formula>$B$9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29:M29">
+    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="3">
+      <formula>$B$9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32:M32">
+    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="3">
+      <formula>$B$9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Jan,Feb,Mar,Apr,May,Jun,Jul,Aug,Sep,Oct,Nov,Dec"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Family_Income_Statement_2026_v5_FIRE.xlsx
+++ b/Family_Income_Statement_2026_v5_FIRE.xlsx
@@ -13901,11 +13901,11 @@
         </is>
       </c>
       <c r="B5" s="46" t="n">
-        <v>2003</v>
+        <v>2010</v>
       </c>
       <c r="C5" s="47" t="inlineStr">
         <is>
-          <t>2003 if funds left on account; 2010 if she took a refund &amp; rejoined. Either way = Tier 1.</t>
+          <t>Confirmed 2010 (refund taken on 2003–07 service, rejoined 2010). Post-2001 join → Tier 1, mandatory R+.</t>
         </is>
       </c>
     </row>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C6" s="47" t="inlineStr">
         <is>
-          <t>~16 if she refunded the 2003–07 years; ~20 if that service is still on account. MyTRS shows the exact figure.</t>
+          <t>~16 years (2010 → 2026, continuous). Confirm the exact figure in MyTRS.</t>
         </is>
       </c>
     </row>
@@ -16751,10 +16751,18 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="B16" s="86" t="n"/>
-      <c r="C16" s="86" t="n"/>
-      <c r="D16" s="86" t="n"/>
-      <c r="E16" s="86" t="n"/>
+      <c r="B16" s="86" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="C16" s="86" t="n">
+        <v>661.4</v>
+      </c>
+      <c r="D16" s="86" t="n">
+        <v>528.3</v>
+      </c>
+      <c r="E16" s="86" t="n">
+        <v>0</v>
+      </c>
       <c r="F16" s="87">
         <f>E16-D16</f>
         <v/>
@@ -16925,7 +16933,7 @@
     <row r="27">
       <c r="A27" s="41" t="inlineStr">
         <is>
-          <t>Latest Enphase snapshot (dashboard view): Produced 3.4 MWh · Consumed 2.6 MWh · Imported 1.3 MWh · Exported 2.2 MWh · Net exported ~872 kWh · Solar offset 134%. Replace with monthly report values above.</t>
+          <t>Enter each month from your Enphase monthly report (no CSV export — read the tile values). Production swings seasonally: March is pre-filled from your report (133 kWh produced vs 661 consumed → net import), while summer months over-produce and export. Net export = Exported − Imported (negative = net import).</t>
         </is>
       </c>
     </row>

--- a/Family_Income_Statement_2026_v5_FIRE.xlsx
+++ b/Family_Income_Statement_2026_v5_FIRE.xlsx
@@ -16789,10 +16789,18 @@
           <t>May</t>
         </is>
       </c>
-      <c r="B18" s="86" t="n"/>
-      <c r="C18" s="86" t="n"/>
-      <c r="D18" s="86" t="n"/>
-      <c r="E18" s="86" t="n"/>
+      <c r="B18" s="86" t="n">
+        <v>997.1</v>
+      </c>
+      <c r="C18" s="86" t="n">
+        <v>475.1</v>
+      </c>
+      <c r="D18" s="86" t="n">
+        <v>246.7</v>
+      </c>
+      <c r="E18" s="86" t="n">
+        <v>768.7</v>
+      </c>
       <c r="F18" s="87">
         <f>E18-D18</f>
         <v/>
@@ -16804,10 +16812,18 @@
           <t>Jun</t>
         </is>
       </c>
-      <c r="B19" s="86" t="n"/>
-      <c r="C19" s="86" t="n"/>
-      <c r="D19" s="86" t="n"/>
-      <c r="E19" s="86" t="n"/>
+      <c r="B19" s="86" t="n">
+        <v>1128.1</v>
+      </c>
+      <c r="C19" s="86" t="n">
+        <v>784.5</v>
+      </c>
+      <c r="D19" s="86" t="n">
+        <v>383</v>
+      </c>
+      <c r="E19" s="86" t="n">
+        <v>726.6</v>
+      </c>
       <c r="F19" s="87">
         <f>E19-D19</f>
         <v/>
@@ -16819,10 +16835,18 @@
           <t>Jul</t>
         </is>
       </c>
-      <c r="B20" s="86" t="n"/>
-      <c r="C20" s="86" t="n"/>
-      <c r="D20" s="86" t="n"/>
-      <c r="E20" s="86" t="n"/>
+      <c r="B20" s="86" t="n">
+        <v>1058.5</v>
+      </c>
+      <c r="C20" s="86" t="n">
+        <v>964.6</v>
+      </c>
+      <c r="D20" s="86" t="n">
+        <v>507.4</v>
+      </c>
+      <c r="E20" s="86" t="n">
+        <v>601.3</v>
+      </c>
       <c r="F20" s="87">
         <f>E20-D20</f>
         <v/>
@@ -16834,10 +16858,18 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="B21" s="86" t="n"/>
-      <c r="C21" s="86" t="n"/>
-      <c r="D21" s="86" t="n"/>
-      <c r="E21" s="86" t="n"/>
+      <c r="B21" s="86" t="n">
+        <v>919.3</v>
+      </c>
+      <c r="C21" s="86" t="n">
+        <v>938.4</v>
+      </c>
+      <c r="D21" s="86" t="n">
+        <v>531.1</v>
+      </c>
+      <c r="E21" s="86" t="n">
+        <v>512</v>
+      </c>
       <c r="F21" s="87">
         <f>E21-D21</f>
         <v/>
@@ -17021,7 +17053,12 @@
         </is>
       </c>
       <c r="B36" s="91" t="n">
-        <v>11000</v>
+        <v>7000</v>
+      </c>
+      <c r="C36" s="47" t="inlineStr">
+        <is>
+          <t>Rough full-year estimate from your 2026 trajectory (YTD ~5 MWh by Aug). Refine after a full year.</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -18030,12 +18067,13 @@
     <row r="79"/>
     <row r="80"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C38:H38"/>
     <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C36:H36"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C31:H31"/>
     <mergeCell ref="A78:H80"/>

--- a/Family_Income_Statement_2026_v5_FIRE.xlsx
+++ b/Family_Income_Statement_2026_v5_FIRE.xlsx
@@ -16774,10 +16774,18 @@
           <t>Apr</t>
         </is>
       </c>
-      <c r="B17" s="86" t="n"/>
-      <c r="C17" s="86" t="n"/>
-      <c r="D17" s="86" t="n"/>
-      <c r="E17" s="86" t="n"/>
+      <c r="B17" s="86" t="n">
+        <v>314.2</v>
+      </c>
+      <c r="C17" s="86" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="D17" s="86" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E17" s="86" t="n">
+        <v>261.7</v>
+      </c>
       <c r="F17" s="87">
         <f>E17-D17</f>
         <v/>

--- a/Family_Income_Statement_2026_v5_FIRE.xlsx
+++ b/Family_Income_Statement_2026_v5_FIRE.xlsx
@@ -250,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -312,6 +312,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -13872,27 +13873,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>Sue — MTRS Pension Calculator (Massachusetts Teachers' Retirement System)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" s="39">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>Membership Tier 1 confirmed — both 2003 and 2010 predate the 4/2/2012 Tier 2 cutoff. YELLOW = confirm in MyTRS  •  ORANGE = scenario inputs  •  Not affiliated with MTRS; verify against the official MTRS estimator before relying on any figure.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>① CONFIRM IN MyTRS  (mtrs.state.ma.us)</t>
         </is>
       </c>
-      <c r="B4" s="45" t="n"/>
-      <c r="C4" s="45" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13900,10 +13901,10 @@
           <t>Effective membership date (year)</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n">
+      <c r="B5" s="47" t="n">
         <v>2010</v>
       </c>
-      <c r="C5" s="47" t="inlineStr">
+      <c r="C5" s="48" t="inlineStr">
         <is>
           <t>Confirmed 2010 (refund taken on 2003–07 service, rejoined 2010). Post-2001 join → Tier 1, mandatory R+.</t>
         </is>
@@ -13915,10 +13916,10 @@
           <t>Current creditable service (yrs, today)</t>
         </is>
       </c>
-      <c r="B6" s="48" t="n">
+      <c r="B6" s="49" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="47" t="inlineStr">
+      <c r="C6" s="48" t="inlineStr">
         <is>
           <t>~16 years (2010 → 2026, continuous). Confirm the exact figure in MyTRS.</t>
         </is>
@@ -13930,12 +13931,12 @@
           <t>RetirementPlus participant? (Y/N)</t>
         </is>
       </c>
-      <c r="B7" s="46" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C7" s="47" t="inlineStr">
+      <c r="C7" s="48" t="inlineStr">
         <is>
           <t>Auto-YES: joined post-7/1/2001 → mandatory R+ at 11%. A flat 11% on her paystub confirms it.</t>
         </is>
@@ -13947,23 +13948,23 @@
           <t>Years as MTRS teacher (R+ 20-yr test)</t>
         </is>
       </c>
-      <c r="B8" s="48" t="n">
+      <c r="B8" s="49" t="n">
         <v>16</v>
       </c>
-      <c r="C8" s="47" t="inlineStr">
+      <c r="C8" s="48" t="inlineStr">
         <is>
           <t>Almost all her creditable service is teacher service; used only for the R+ 20-year test.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="44" t="inlineStr">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t>② SCENARIO INPUTS</t>
         </is>
       </c>
-      <c r="B10" s="45" t="n"/>
-      <c r="C10" s="45" t="n"/>
+      <c r="B10" s="46" t="n"/>
+      <c r="C10" s="46" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13971,7 +13972,7 @@
           <t>Sue's current age</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="50" t="n">
         <v>45</v>
       </c>
     </row>
@@ -13981,7 +13982,7 @@
           <t>Current calendar year</t>
         </is>
       </c>
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="50" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13991,10 +13992,10 @@
           <t>Current annual salary ($)</t>
         </is>
       </c>
-      <c r="B13" s="50" t="n">
+      <c r="B13" s="51" t="n">
         <v>85000</v>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="48" t="inlineStr">
         <is>
           <t>Enter Sue's actual salary.</t>
         </is>
@@ -14006,7 +14007,7 @@
           <t>Expected annual raise (%)</t>
         </is>
       </c>
-      <c r="B14" s="51" t="n">
+      <c r="B14" s="52" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -14016,7 +14017,7 @@
           <t>Planned retirement age (scenario)</t>
         </is>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="50" t="n">
         <v>60</v>
       </c>
     </row>
@@ -14026,29 +14027,29 @@
           <t>Buy-back: early years to restore</t>
         </is>
       </c>
-      <c r="B16" s="52" t="n">
+      <c r="B16" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="48" t="inlineStr">
         <is>
           <t>If she refunded 2003–07, she can repay to restore ~4–5 yrs. Try 4 to see the effect.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="44" t="inlineStr">
+      <c r="A18" s="45" t="inlineStr">
         <is>
           <t>③ TIER 1 RULES  (reference — do not edit)</t>
         </is>
       </c>
-      <c r="B18" s="45" t="n"/>
-      <c r="C18" s="45" t="n"/>
-      <c r="E18" s="53" t="inlineStr">
+      <c r="B18" s="46" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="E18" s="54" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="F18" s="53" t="inlineStr">
+      <c r="F18" s="54" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
@@ -14060,15 +14061,15 @@
           <t>Membership tier</t>
         </is>
       </c>
-      <c r="B19" s="54" t="inlineStr">
+      <c r="B19" s="55" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="E19" s="55" t="n">
+      <c r="E19" s="56" t="n">
         <v>55</v>
       </c>
-      <c r="F19" s="56" t="n">
+      <c r="F19" s="57" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -14078,15 +14079,15 @@
           <t>Salary average period</t>
         </is>
       </c>
-      <c r="B20" s="54" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t>Highest 3 yrs</t>
         </is>
       </c>
-      <c r="E20" s="55" t="n">
+      <c r="E20" s="56" t="n">
         <v>56</v>
       </c>
-      <c r="F20" s="56" t="n">
+      <c r="F20" s="57" t="n">
         <v>0.016</v>
       </c>
     </row>
@@ -14096,13 +14097,13 @@
           <t>Maximum benefit cap</t>
         </is>
       </c>
-      <c r="B21" s="57" t="n">
+      <c r="B21" s="58" t="n">
         <v>0.8</v>
       </c>
-      <c r="E21" s="55" t="n">
+      <c r="E21" s="56" t="n">
         <v>57</v>
       </c>
-      <c r="F21" s="56" t="n">
+      <c r="F21" s="57" t="n">
         <v>0.017</v>
       </c>
     </row>
@@ -14112,20 +14113,20 @@
           <t>R+ enhancement</t>
         </is>
       </c>
-      <c r="B22" s="54" t="inlineStr">
+      <c r="B22" s="55" t="inlineStr">
         <is>
           <t>+2%/yr over 24 yrs</t>
         </is>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C22" s="48" t="inlineStr">
         <is>
           <t>Requires ≥30 yrs creditable, ≥20 as teacher, 11% for 5+ yrs.</t>
         </is>
       </c>
-      <c r="E22" s="55" t="n">
+      <c r="E22" s="56" t="n">
         <v>58</v>
       </c>
-      <c r="F22" s="56" t="n">
+      <c r="F22" s="57" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -14135,36 +14136,36 @@
           <t>Min retirement age (Tier 1)</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n">
+      <c r="B23" s="55" t="n">
         <v>55</v>
       </c>
-      <c r="E23" s="55" t="n">
+      <c r="E23" s="56" t="n">
         <v>59</v>
       </c>
-      <c r="F23" s="56" t="n">
+      <c r="F23" s="57" t="n">
         <v>0.019</v>
       </c>
     </row>
     <row r="24">
-      <c r="E24" s="55" t="n">
+      <c r="E24" s="56" t="n">
         <v>60</v>
       </c>
-      <c r="F24" s="56" t="n">
+      <c r="F24" s="57" t="n">
         <v>0.02</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="44" t="inlineStr">
+      <c r="A25" s="45" t="inlineStr">
         <is>
           <t>④ RESULT AT PLANNED RETIREMENT AGE</t>
         </is>
       </c>
-      <c r="B25" s="45" t="n"/>
-      <c r="C25" s="45" t="n"/>
-      <c r="E25" s="55" t="n">
+      <c r="B25" s="46" t="n"/>
+      <c r="C25" s="46" t="n"/>
+      <c r="E25" s="56" t="n">
         <v>61</v>
       </c>
-      <c r="F25" s="56" t="n">
+      <c r="F25" s="57" t="n">
         <v>0.021</v>
       </c>
     </row>
@@ -14174,14 +14175,14 @@
           <t>Creditable service at retirement</t>
         </is>
       </c>
-      <c r="B26" s="58">
+      <c r="B26" s="59">
         <f>B6+(B15-B11)+B16</f>
         <v/>
       </c>
-      <c r="E26" s="55" t="n">
+      <c r="E26" s="56" t="n">
         <v>62</v>
       </c>
-      <c r="F26" s="56" t="n">
+      <c r="F26" s="57" t="n">
         <v>0.022</v>
       </c>
     </row>
@@ -14191,14 +14192,14 @@
           <t>Age factor at retirement</t>
         </is>
       </c>
-      <c r="B27" s="59">
+      <c r="B27" s="60">
         <f>IF(B15&lt;55,0,IF(B15&gt;=65,0.025,0.015+(B15-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E27" s="55" t="n">
+      <c r="E27" s="56" t="n">
         <v>63</v>
       </c>
-      <c r="F27" s="56" t="n">
+      <c r="F27" s="57" t="n">
         <v>0.023</v>
       </c>
     </row>
@@ -14208,14 +14209,14 @@
           <t>Salary average (3-yr, est.) $</t>
         </is>
       </c>
-      <c r="B28" s="60">
+      <c r="B28" s="61">
         <f>B13*((1+B14)^(B15-B11)+(1+B14)^(B15-B11-1)+(1+B14)^(B15-B11-2))/3</f>
         <v/>
       </c>
-      <c r="E28" s="55" t="n">
+      <c r="E28" s="56" t="n">
         <v>64</v>
       </c>
-      <c r="F28" s="56" t="n">
+      <c r="F28" s="57" t="n">
         <v>0.024</v>
       </c>
     </row>
@@ -14225,14 +14226,14 @@
           <t>Regular formula benefit %</t>
         </is>
       </c>
-      <c r="B29" s="59">
+      <c r="B29" s="60">
         <f>MIN($B$21,B27*B26)</f>
         <v/>
       </c>
-      <c r="E29" s="55" t="n">
+      <c r="E29" s="56" t="n">
         <v>65</v>
       </c>
-      <c r="F29" s="56" t="n">
+      <c r="F29" s="57" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -14242,7 +14243,7 @@
           <t>R+ eligible?</t>
         </is>
       </c>
-      <c r="B30" s="61">
+      <c r="B30" s="62">
         <f>IF(AND($B$7="Y",B26&gt;=30,B8+(B15-B11)&gt;=20),"Yes","No")</f>
         <v/>
       </c>
@@ -14253,7 +14254,7 @@
           <t>R+ formula benefit %</t>
         </is>
       </c>
-      <c r="B31" s="59">
+      <c r="B31" s="60">
         <f>MIN($B$21,B27*B26+0.02*MAX(0,B26-24))</f>
         <v/>
       </c>
@@ -14264,18 +14265,18 @@
           <t>Applied benefit %</t>
         </is>
       </c>
-      <c r="B32" s="62">
+      <c r="B32" s="63">
         <f>IF(B30="Yes",B31,B29)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="63" t="inlineStr">
+      <c r="A33" s="64" t="inlineStr">
         <is>
           <t>ANNUAL PENSION ($)</t>
         </is>
       </c>
-      <c r="B33" s="64">
+      <c r="B33" s="65">
         <f>B32*B28</f>
         <v/>
       </c>
@@ -14286,636 +14287,636 @@
           <t>Monthly pension ($)</t>
         </is>
       </c>
-      <c r="B34" s="60">
+      <c r="B34" s="61">
         <f>B33/12</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="44" t="inlineStr">
+      <c r="A36" s="45" t="inlineStr">
         <is>
           <t>⑤ PROJECTION BY RETIREMENT AGE  (finds the earliest 80% cap)</t>
         </is>
       </c>
-      <c r="B36" s="45" t="n"/>
-      <c r="C36" s="45" t="n"/>
-      <c r="D36" s="45" t="n"/>
-      <c r="E36" s="45" t="n"/>
-      <c r="F36" s="45" t="n"/>
-      <c r="G36" s="45" t="n"/>
-      <c r="H36" s="45" t="n"/>
-      <c r="I36" s="45" t="n"/>
-      <c r="J36" s="45" t="n"/>
+      <c r="B36" s="46" t="n"/>
+      <c r="C36" s="46" t="n"/>
+      <c r="D36" s="46" t="n"/>
+      <c r="E36" s="46" t="n"/>
+      <c r="F36" s="46" t="n"/>
+      <c r="G36" s="46" t="n"/>
+      <c r="H36" s="46" t="n"/>
+      <c r="I36" s="46" t="n"/>
+      <c r="J36" s="46" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1" s="39">
-      <c r="A37" s="65" t="inlineStr">
+      <c r="A37" s="66" t="inlineStr">
         <is>
           <t>Retire age</t>
         </is>
       </c>
-      <c r="B37" s="65" t="inlineStr">
+      <c r="B37" s="66" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C37" s="65" t="inlineStr">
+      <c r="C37" s="66" t="inlineStr">
         <is>
           <t>Cred. svc</t>
         </is>
       </c>
-      <c r="D37" s="65" t="inlineStr">
+      <c r="D37" s="66" t="inlineStr">
         <is>
           <t>Age factor</t>
         </is>
       </c>
-      <c r="E37" s="65" t="inlineStr">
+      <c r="E37" s="66" t="inlineStr">
         <is>
           <t>Regular %</t>
         </is>
       </c>
-      <c r="F37" s="65" t="inlineStr">
+      <c r="F37" s="66" t="inlineStr">
         <is>
           <t>R+ elig?</t>
         </is>
       </c>
-      <c r="G37" s="65" t="inlineStr">
+      <c r="G37" s="66" t="inlineStr">
         <is>
           <t>R+ %</t>
         </is>
       </c>
-      <c r="H37" s="65" t="inlineStr">
+      <c r="H37" s="66" t="inlineStr">
         <is>
           <t>Applied %</t>
         </is>
       </c>
-      <c r="I37" s="65" t="inlineStr">
+      <c r="I37" s="66" t="inlineStr">
         <is>
           <t>Annual pension $</t>
         </is>
       </c>
-      <c r="J37" s="65" t="inlineStr">
+      <c r="J37" s="66" t="inlineStr">
         <is>
           <t>80% cap?</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="55" t="n">
+      <c r="A38" s="56" t="n">
         <v>55</v>
       </c>
-      <c r="B38" s="55">
+      <c r="B38" s="56">
         <f>$B$12+(A38-$B$11)</f>
         <v/>
       </c>
-      <c r="C38" s="66">
+      <c r="C38" s="67">
         <f>$B$6+(A38-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D38" s="56">
+      <c r="D38" s="57">
         <f>IF(A38&lt;55,0,IF(A38&gt;=65,0.025,0.015+(A38-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E38" s="56">
+      <c r="E38" s="57">
         <f>MIN($B$21,D38*C38)</f>
         <v/>
       </c>
-      <c r="F38" s="55">
+      <c r="F38" s="56">
         <f>IF(AND($B$7="Y",C38&gt;=30,$B$8+(A38-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G38" s="56">
+      <c r="G38" s="57">
         <f>MIN($B$21,D38*C38+0.02*MAX(0,C38-24))</f>
         <v/>
       </c>
-      <c r="H38" s="67">
+      <c r="H38" s="68">
         <f>IF(F38="Y",G38,E38)</f>
         <v/>
       </c>
-      <c r="I38" s="68">
+      <c r="I38" s="69">
         <f>H38*($B$13*((1+$B$14)^(A38-$B$11)+(1+$B$14)^(A38-$B$11-1)+(1+$B$14)^(A38-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J38" s="55">
+      <c r="J38" s="56">
         <f>IF(H38&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="55" t="n">
+      <c r="A39" s="56" t="n">
         <v>56</v>
       </c>
-      <c r="B39" s="55">
+      <c r="B39" s="56">
         <f>$B$12+(A39-$B$11)</f>
         <v/>
       </c>
-      <c r="C39" s="66">
+      <c r="C39" s="67">
         <f>$B$6+(A39-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D39" s="56">
+      <c r="D39" s="57">
         <f>IF(A39&lt;55,0,IF(A39&gt;=65,0.025,0.015+(A39-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E39" s="56">
+      <c r="E39" s="57">
         <f>MIN($B$21,D39*C39)</f>
         <v/>
       </c>
-      <c r="F39" s="55">
+      <c r="F39" s="56">
         <f>IF(AND($B$7="Y",C39&gt;=30,$B$8+(A39-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G39" s="56">
+      <c r="G39" s="57">
         <f>MIN($B$21,D39*C39+0.02*MAX(0,C39-24))</f>
         <v/>
       </c>
-      <c r="H39" s="67">
+      <c r="H39" s="68">
         <f>IF(F39="Y",G39,E39)</f>
         <v/>
       </c>
-      <c r="I39" s="68">
+      <c r="I39" s="69">
         <f>H39*($B$13*((1+$B$14)^(A39-$B$11)+(1+$B$14)^(A39-$B$11-1)+(1+$B$14)^(A39-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J39" s="55">
+      <c r="J39" s="56">
         <f>IF(H39&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="55" t="n">
+      <c r="A40" s="56" t="n">
         <v>57</v>
       </c>
-      <c r="B40" s="55">
+      <c r="B40" s="56">
         <f>$B$12+(A40-$B$11)</f>
         <v/>
       </c>
-      <c r="C40" s="66">
+      <c r="C40" s="67">
         <f>$B$6+(A40-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D40" s="56">
+      <c r="D40" s="57">
         <f>IF(A40&lt;55,0,IF(A40&gt;=65,0.025,0.015+(A40-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E40" s="56">
+      <c r="E40" s="57">
         <f>MIN($B$21,D40*C40)</f>
         <v/>
       </c>
-      <c r="F40" s="55">
+      <c r="F40" s="56">
         <f>IF(AND($B$7="Y",C40&gt;=30,$B$8+(A40-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G40" s="56">
+      <c r="G40" s="57">
         <f>MIN($B$21,D40*C40+0.02*MAX(0,C40-24))</f>
         <v/>
       </c>
-      <c r="H40" s="67">
+      <c r="H40" s="68">
         <f>IF(F40="Y",G40,E40)</f>
         <v/>
       </c>
-      <c r="I40" s="68">
+      <c r="I40" s="69">
         <f>H40*($B$13*((1+$B$14)^(A40-$B$11)+(1+$B$14)^(A40-$B$11-1)+(1+$B$14)^(A40-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J40" s="55">
+      <c r="J40" s="56">
         <f>IF(H40&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="55" t="n">
+      <c r="A41" s="56" t="n">
         <v>58</v>
       </c>
-      <c r="B41" s="55">
+      <c r="B41" s="56">
         <f>$B$12+(A41-$B$11)</f>
         <v/>
       </c>
-      <c r="C41" s="66">
+      <c r="C41" s="67">
         <f>$B$6+(A41-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D41" s="56">
+      <c r="D41" s="57">
         <f>IF(A41&lt;55,0,IF(A41&gt;=65,0.025,0.015+(A41-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E41" s="56">
+      <c r="E41" s="57">
         <f>MIN($B$21,D41*C41)</f>
         <v/>
       </c>
-      <c r="F41" s="55">
+      <c r="F41" s="56">
         <f>IF(AND($B$7="Y",C41&gt;=30,$B$8+(A41-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G41" s="56">
+      <c r="G41" s="57">
         <f>MIN($B$21,D41*C41+0.02*MAX(0,C41-24))</f>
         <v/>
       </c>
-      <c r="H41" s="67">
+      <c r="H41" s="68">
         <f>IF(F41="Y",G41,E41)</f>
         <v/>
       </c>
-      <c r="I41" s="68">
+      <c r="I41" s="69">
         <f>H41*($B$13*((1+$B$14)^(A41-$B$11)+(1+$B$14)^(A41-$B$11-1)+(1+$B$14)^(A41-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J41" s="55">
+      <c r="J41" s="56">
         <f>IF(H41&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="55" t="n">
+      <c r="A42" s="56" t="n">
         <v>59</v>
       </c>
-      <c r="B42" s="55">
+      <c r="B42" s="56">
         <f>$B$12+(A42-$B$11)</f>
         <v/>
       </c>
-      <c r="C42" s="66">
+      <c r="C42" s="67">
         <f>$B$6+(A42-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D42" s="56">
+      <c r="D42" s="57">
         <f>IF(A42&lt;55,0,IF(A42&gt;=65,0.025,0.015+(A42-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E42" s="56">
+      <c r="E42" s="57">
         <f>MIN($B$21,D42*C42)</f>
         <v/>
       </c>
-      <c r="F42" s="55">
+      <c r="F42" s="56">
         <f>IF(AND($B$7="Y",C42&gt;=30,$B$8+(A42-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G42" s="56">
+      <c r="G42" s="57">
         <f>MIN($B$21,D42*C42+0.02*MAX(0,C42-24))</f>
         <v/>
       </c>
-      <c r="H42" s="67">
+      <c r="H42" s="68">
         <f>IF(F42="Y",G42,E42)</f>
         <v/>
       </c>
-      <c r="I42" s="68">
+      <c r="I42" s="69">
         <f>H42*($B$13*((1+$B$14)^(A42-$B$11)+(1+$B$14)^(A42-$B$11-1)+(1+$B$14)^(A42-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J42" s="55">
+      <c r="J42" s="56">
         <f>IF(H42&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="55" t="n">
+      <c r="A43" s="56" t="n">
         <v>60</v>
       </c>
-      <c r="B43" s="55">
+      <c r="B43" s="56">
         <f>$B$12+(A43-$B$11)</f>
         <v/>
       </c>
-      <c r="C43" s="66">
+      <c r="C43" s="67">
         <f>$B$6+(A43-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D43" s="56">
+      <c r="D43" s="57">
         <f>IF(A43&lt;55,0,IF(A43&gt;=65,0.025,0.015+(A43-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E43" s="56">
+      <c r="E43" s="57">
         <f>MIN($B$21,D43*C43)</f>
         <v/>
       </c>
-      <c r="F43" s="55">
+      <c r="F43" s="56">
         <f>IF(AND($B$7="Y",C43&gt;=30,$B$8+(A43-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G43" s="56">
+      <c r="G43" s="57">
         <f>MIN($B$21,D43*C43+0.02*MAX(0,C43-24))</f>
         <v/>
       </c>
-      <c r="H43" s="67">
+      <c r="H43" s="68">
         <f>IF(F43="Y",G43,E43)</f>
         <v/>
       </c>
-      <c r="I43" s="68">
+      <c r="I43" s="69">
         <f>H43*($B$13*((1+$B$14)^(A43-$B$11)+(1+$B$14)^(A43-$B$11-1)+(1+$B$14)^(A43-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J43" s="55">
+      <c r="J43" s="56">
         <f>IF(H43&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="55" t="n">
+      <c r="A44" s="56" t="n">
         <v>61</v>
       </c>
-      <c r="B44" s="55">
+      <c r="B44" s="56">
         <f>$B$12+(A44-$B$11)</f>
         <v/>
       </c>
-      <c r="C44" s="66">
+      <c r="C44" s="67">
         <f>$B$6+(A44-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D44" s="56">
+      <c r="D44" s="57">
         <f>IF(A44&lt;55,0,IF(A44&gt;=65,0.025,0.015+(A44-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E44" s="56">
+      <c r="E44" s="57">
         <f>MIN($B$21,D44*C44)</f>
         <v/>
       </c>
-      <c r="F44" s="55">
+      <c r="F44" s="56">
         <f>IF(AND($B$7="Y",C44&gt;=30,$B$8+(A44-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G44" s="56">
+      <c r="G44" s="57">
         <f>MIN($B$21,D44*C44+0.02*MAX(0,C44-24))</f>
         <v/>
       </c>
-      <c r="H44" s="67">
+      <c r="H44" s="68">
         <f>IF(F44="Y",G44,E44)</f>
         <v/>
       </c>
-      <c r="I44" s="68">
+      <c r="I44" s="69">
         <f>H44*($B$13*((1+$B$14)^(A44-$B$11)+(1+$B$14)^(A44-$B$11-1)+(1+$B$14)^(A44-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J44" s="55">
+      <c r="J44" s="56">
         <f>IF(H44&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="55" t="n">
+      <c r="A45" s="56" t="n">
         <v>62</v>
       </c>
-      <c r="B45" s="55">
+      <c r="B45" s="56">
         <f>$B$12+(A45-$B$11)</f>
         <v/>
       </c>
-      <c r="C45" s="66">
+      <c r="C45" s="67">
         <f>$B$6+(A45-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D45" s="56">
+      <c r="D45" s="57">
         <f>IF(A45&lt;55,0,IF(A45&gt;=65,0.025,0.015+(A45-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E45" s="56">
+      <c r="E45" s="57">
         <f>MIN($B$21,D45*C45)</f>
         <v/>
       </c>
-      <c r="F45" s="55">
+      <c r="F45" s="56">
         <f>IF(AND($B$7="Y",C45&gt;=30,$B$8+(A45-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G45" s="56">
+      <c r="G45" s="57">
         <f>MIN($B$21,D45*C45+0.02*MAX(0,C45-24))</f>
         <v/>
       </c>
-      <c r="H45" s="67">
+      <c r="H45" s="68">
         <f>IF(F45="Y",G45,E45)</f>
         <v/>
       </c>
-      <c r="I45" s="68">
+      <c r="I45" s="69">
         <f>H45*($B$13*((1+$B$14)^(A45-$B$11)+(1+$B$14)^(A45-$B$11-1)+(1+$B$14)^(A45-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J45" s="55">
+      <c r="J45" s="56">
         <f>IF(H45&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="55" t="n">
+      <c r="A46" s="56" t="n">
         <v>63</v>
       </c>
-      <c r="B46" s="55">
+      <c r="B46" s="56">
         <f>$B$12+(A46-$B$11)</f>
         <v/>
       </c>
-      <c r="C46" s="66">
+      <c r="C46" s="67">
         <f>$B$6+(A46-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D46" s="56">
+      <c r="D46" s="57">
         <f>IF(A46&lt;55,0,IF(A46&gt;=65,0.025,0.015+(A46-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E46" s="56">
+      <c r="E46" s="57">
         <f>MIN($B$21,D46*C46)</f>
         <v/>
       </c>
-      <c r="F46" s="55">
+      <c r="F46" s="56">
         <f>IF(AND($B$7="Y",C46&gt;=30,$B$8+(A46-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G46" s="56">
+      <c r="G46" s="57">
         <f>MIN($B$21,D46*C46+0.02*MAX(0,C46-24))</f>
         <v/>
       </c>
-      <c r="H46" s="67">
+      <c r="H46" s="68">
         <f>IF(F46="Y",G46,E46)</f>
         <v/>
       </c>
-      <c r="I46" s="68">
+      <c r="I46" s="69">
         <f>H46*($B$13*((1+$B$14)^(A46-$B$11)+(1+$B$14)^(A46-$B$11-1)+(1+$B$14)^(A46-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J46" s="55">
+      <c r="J46" s="56">
         <f>IF(H46&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="55" t="n">
+      <c r="A47" s="56" t="n">
         <v>64</v>
       </c>
-      <c r="B47" s="55">
+      <c r="B47" s="56">
         <f>$B$12+(A47-$B$11)</f>
         <v/>
       </c>
-      <c r="C47" s="66">
+      <c r="C47" s="67">
         <f>$B$6+(A47-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D47" s="56">
+      <c r="D47" s="57">
         <f>IF(A47&lt;55,0,IF(A47&gt;=65,0.025,0.015+(A47-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E47" s="56">
+      <c r="E47" s="57">
         <f>MIN($B$21,D47*C47)</f>
         <v/>
       </c>
-      <c r="F47" s="55">
+      <c r="F47" s="56">
         <f>IF(AND($B$7="Y",C47&gt;=30,$B$8+(A47-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G47" s="56">
+      <c r="G47" s="57">
         <f>MIN($B$21,D47*C47+0.02*MAX(0,C47-24))</f>
         <v/>
       </c>
-      <c r="H47" s="67">
+      <c r="H47" s="68">
         <f>IF(F47="Y",G47,E47)</f>
         <v/>
       </c>
-      <c r="I47" s="68">
+      <c r="I47" s="69">
         <f>H47*($B$13*((1+$B$14)^(A47-$B$11)+(1+$B$14)^(A47-$B$11-1)+(1+$B$14)^(A47-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J47" s="55">
+      <c r="J47" s="56">
         <f>IF(H47&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="55" t="n">
+      <c r="A48" s="56" t="n">
         <v>65</v>
       </c>
-      <c r="B48" s="55">
+      <c r="B48" s="56">
         <f>$B$12+(A48-$B$11)</f>
         <v/>
       </c>
-      <c r="C48" s="66">
+      <c r="C48" s="67">
         <f>$B$6+(A48-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D48" s="56">
+      <c r="D48" s="57">
         <f>IF(A48&lt;55,0,IF(A48&gt;=65,0.025,0.015+(A48-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E48" s="56">
+      <c r="E48" s="57">
         <f>MIN($B$21,D48*C48)</f>
         <v/>
       </c>
-      <c r="F48" s="55">
+      <c r="F48" s="56">
         <f>IF(AND($B$7="Y",C48&gt;=30,$B$8+(A48-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G48" s="56">
+      <c r="G48" s="57">
         <f>MIN($B$21,D48*C48+0.02*MAX(0,C48-24))</f>
         <v/>
       </c>
-      <c r="H48" s="67">
+      <c r="H48" s="68">
         <f>IF(F48="Y",G48,E48)</f>
         <v/>
       </c>
-      <c r="I48" s="68">
+      <c r="I48" s="69">
         <f>H48*($B$13*((1+$B$14)^(A48-$B$11)+(1+$B$14)^(A48-$B$11-1)+(1+$B$14)^(A48-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J48" s="55">
+      <c r="J48" s="56">
         <f>IF(H48&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="55" t="n">
+      <c r="A49" s="56" t="n">
         <v>66</v>
       </c>
-      <c r="B49" s="55">
+      <c r="B49" s="56">
         <f>$B$12+(A49-$B$11)</f>
         <v/>
       </c>
-      <c r="C49" s="66">
+      <c r="C49" s="67">
         <f>$B$6+(A49-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D49" s="56">
+      <c r="D49" s="57">
         <f>IF(A49&lt;55,0,IF(A49&gt;=65,0.025,0.015+(A49-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E49" s="56">
+      <c r="E49" s="57">
         <f>MIN($B$21,D49*C49)</f>
         <v/>
       </c>
-      <c r="F49" s="55">
+      <c r="F49" s="56">
         <f>IF(AND($B$7="Y",C49&gt;=30,$B$8+(A49-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G49" s="56">
+      <c r="G49" s="57">
         <f>MIN($B$21,D49*C49+0.02*MAX(0,C49-24))</f>
         <v/>
       </c>
-      <c r="H49" s="67">
+      <c r="H49" s="68">
         <f>IF(F49="Y",G49,E49)</f>
         <v/>
       </c>
-      <c r="I49" s="68">
+      <c r="I49" s="69">
         <f>H49*($B$13*((1+$B$14)^(A49-$B$11)+(1+$B$14)^(A49-$B$11-1)+(1+$B$14)^(A49-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J49" s="55">
+      <c r="J49" s="56">
         <f>IF(H49&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="55" t="n">
+      <c r="A50" s="56" t="n">
         <v>67</v>
       </c>
-      <c r="B50" s="55">
+      <c r="B50" s="56">
         <f>$B$12+(A50-$B$11)</f>
         <v/>
       </c>
-      <c r="C50" s="66">
+      <c r="C50" s="67">
         <f>$B$6+(A50-$B$11)+$B$16</f>
         <v/>
       </c>
-      <c r="D50" s="56">
+      <c r="D50" s="57">
         <f>IF(A50&lt;55,0,IF(A50&gt;=65,0.025,0.015+(A50-55)*0.001))</f>
         <v/>
       </c>
-      <c r="E50" s="56">
+      <c r="E50" s="57">
         <f>MIN($B$21,D50*C50)</f>
         <v/>
       </c>
-      <c r="F50" s="55">
+      <c r="F50" s="56">
         <f>IF(AND($B$7="Y",C50&gt;=30,$B$8+(A50-$B$11)&gt;=20),"Y","N")</f>
         <v/>
       </c>
-      <c r="G50" s="56">
+      <c r="G50" s="57">
         <f>MIN($B$21,D50*C50+0.02*MAX(0,C50-24))</f>
         <v/>
       </c>
-      <c r="H50" s="67">
+      <c r="H50" s="68">
         <f>IF(F50="Y",G50,E50)</f>
         <v/>
       </c>
-      <c r="I50" s="68">
+      <c r="I50" s="69">
         <f>H50*($B$13*((1+$B$14)^(A50-$B$11)+(1+$B$14)^(A50-$B$11-1)+(1+$B$14)^(A50-$B$11-2))/3)</f>
         <v/>
       </c>
-      <c r="J50" s="55">
+      <c r="J50" s="56">
         <f>IF(H50&gt;=$B$21,"◄ 80% CAP","")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="63" t="inlineStr">
+      <c r="A52" s="64" t="inlineStr">
         <is>
           <t>Earliest age at 80% cap:</t>
         </is>
       </c>
-      <c r="C52" s="69">
+      <c r="C52" s="70">
         <f>IFERROR(INDEX(A38:A50,MATCH(TRUE,INDEX(H38:H50&gt;=$B$21,0),0)),"Not by 67")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="63" t="inlineStr">
+      <c r="A53" s="64" t="inlineStr">
         <is>
           <t>…in calendar year:</t>
         </is>
       </c>
-      <c r="C53" s="69">
+      <c r="C53" s="70">
         <f>IFERROR($B$12+(C52-$B$11),"—")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="41" t="inlineStr">
+      <c r="A55" s="42" t="inlineStr">
         <is>
           <t>Note: salary average is a simple projection (current salary grown by the raise rate, averaged over the final 3 years). MTRS uses actual highest-3-consecutive-year earnings. R+ enhanced benefit only applies once she reaches 30 creditable years; otherwise the regular formula applies and R+ contributions are refunded.</t>
         </is>
@@ -14948,27 +14949,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>FIRE Dashboard — Naughton Family</t>
         </is>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1" s="39">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>Educational planning tool, not investment advice. ORANGE = assumptions you set  •  YELLOW = balances/contributions (snapshot as of now — update over time). FI math uses a REAL (inflation-adjusted) return.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>① HOUSEHOLD ASSUMPTIONS</t>
         </is>
       </c>
-      <c r="B4" s="45" t="n"/>
-      <c r="C4" s="45" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14976,7 +14977,7 @@
           <t>Matt's current age</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="50" t="n">
         <v>45</v>
       </c>
     </row>
@@ -14986,7 +14987,7 @@
           <t>Sue's current age</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="50" t="n">
         <v>45</v>
       </c>
     </row>
@@ -14996,7 +14997,7 @@
           <t>Current calendar year</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="50" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15006,10 +15007,10 @@
           <t>Target annual retirement spend ($)</t>
         </is>
       </c>
-      <c r="B8" s="50" t="n">
+      <c r="B8" s="51" t="n">
         <v>90000</v>
       </c>
-      <c r="C8" s="47" t="inlineStr">
+      <c r="C8" s="48" t="inlineStr">
         <is>
           <t>Use your Income Statement expenses as a guide.</t>
         </is>
@@ -15021,7 +15022,7 @@
           <t>Safe withdrawal rate (SWR)</t>
         </is>
       </c>
-      <c r="B9" s="70" t="n">
+      <c r="B9" s="71" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -15031,10 +15032,10 @@
           <t>Nominal expected return</t>
         </is>
       </c>
-      <c r="B10" s="70" t="n">
+      <c r="B10" s="71" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C10" s="47" t="inlineStr">
+      <c r="C10" s="48" t="inlineStr">
         <is>
           <t>Matches the 7% on your Scenarios tab.</t>
         </is>
@@ -15046,7 +15047,7 @@
           <t>Assumed inflation</t>
         </is>
       </c>
-      <c r="B11" s="70" t="n">
+      <c r="B11" s="71" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -15056,19 +15057,19 @@
           <t>Real return (auto)</t>
         </is>
       </c>
-      <c r="B12" s="71">
+      <c r="B12" s="72">
         <f>(1+B10)/(1+B11)-1</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="44" t="inlineStr">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>② CURRENT INVESTED ASSETS  (from Balances)</t>
         </is>
       </c>
-      <c r="B14" s="45" t="n"/>
-      <c r="C14" s="45" t="n"/>
+      <c r="B14" s="46" t="n"/>
+      <c r="C14" s="46" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15076,7 +15077,7 @@
           <t>Matt 401k (MathWorks)</t>
         </is>
       </c>
-      <c r="B15" s="72" t="n">
+      <c r="B15" s="73" t="n">
         <v>228000</v>
       </c>
     </row>
@@ -15086,7 +15087,7 @@
           <t>Sue 403b (Equitable)</t>
         </is>
       </c>
-      <c r="B16" s="72" t="n">
+      <c r="B16" s="73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15096,7 +15097,7 @@
           <t>IRAs (Matt + Sue)</t>
         </is>
       </c>
-      <c r="B17" s="72" t="n">
+      <c r="B17" s="73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15106,7 +15107,7 @@
           <t>HSA (invested portion)</t>
         </is>
       </c>
-      <c r="B18" s="72" t="n">
+      <c r="B18" s="73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15116,7 +15117,7 @@
           <t>Taxable brokerage (Schwab)</t>
         </is>
       </c>
-      <c r="B19" s="72" t="n">
+      <c r="B19" s="73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15126,22 +15127,22 @@
           <t>Cash earmarked for FI</t>
         </is>
       </c>
-      <c r="B20" s="72" t="n">
+      <c r="B20" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C20" s="48" t="inlineStr">
         <is>
           <t>Exclude your emergency fund.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="63" t="inlineStr">
+      <c r="A21" s="64" t="inlineStr">
         <is>
           <t>TOTAL INVESTED</t>
         </is>
       </c>
-      <c r="B21" s="64">
+      <c r="B21" s="65">
         <f>SUM(B15:B20)</f>
         <v/>
       </c>
@@ -15152,23 +15153,23 @@
           <t>(memo) 529 — excluded from FI</t>
         </is>
       </c>
-      <c r="B22" s="73" t="n">
+      <c r="B22" s="74" t="n">
         <v>14298</v>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C22" s="48" t="inlineStr">
         <is>
           <t>Kids' college — not part of your FI number.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="44" t="inlineStr">
+      <c r="A24" s="45" t="inlineStr">
         <is>
           <t>③ ANNUAL CONTRIBUTIONS</t>
         </is>
       </c>
-      <c r="B24" s="45" t="n"/>
-      <c r="C24" s="45" t="n"/>
+      <c r="B24" s="46" t="n"/>
+      <c r="C24" s="46" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15176,7 +15177,7 @@
           <t>Matt 401k (employee)</t>
         </is>
       </c>
-      <c r="B25" s="72" t="n">
+      <c r="B25" s="73" t="n">
         <v>23500</v>
       </c>
     </row>
@@ -15186,7 +15187,7 @@
           <t>Employer 401k match</t>
         </is>
       </c>
-      <c r="B26" s="72" t="n">
+      <c r="B26" s="73" t="n">
         <v>4338</v>
       </c>
     </row>
@@ -15196,7 +15197,7 @@
           <t>Sue 403b</t>
         </is>
       </c>
-      <c r="B27" s="72" t="n">
+      <c r="B27" s="73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15206,10 +15207,10 @@
           <t>HSA</t>
         </is>
       </c>
-      <c r="B28" s="72" t="n">
+      <c r="B28" s="73" t="n">
         <v>9000</v>
       </c>
-      <c r="C28" s="47" t="inlineStr">
+      <c r="C28" s="48" t="inlineStr">
         <is>
           <t>2027 family HSA limit.</t>
         </is>
@@ -15221,7 +15222,7 @@
           <t>IRAs (both)</t>
         </is>
       </c>
-      <c r="B29" s="72" t="n">
+      <c r="B29" s="73" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -15231,7 +15232,7 @@
           <t>Taxable brokerage</t>
         </is>
       </c>
-      <c r="B30" s="72" t="n">
+      <c r="B30" s="73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15241,29 +15242,29 @@
           <t>529</t>
         </is>
       </c>
-      <c r="B31" s="72" t="n">
+      <c r="B31" s="73" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="63" t="inlineStr">
+      <c r="A32" s="64" t="inlineStr">
         <is>
           <t>TOTAL ANNUAL INVESTED</t>
         </is>
       </c>
-      <c r="B32" s="64">
+      <c r="B32" s="65">
         <f>SUM(B25:B31)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="44" t="inlineStr">
+      <c r="A34" s="45" t="inlineStr">
         <is>
           <t>④ SAVINGS RATE</t>
         </is>
       </c>
-      <c r="B34" s="45" t="n"/>
-      <c r="C34" s="45" t="n"/>
+      <c r="B34" s="46" t="n"/>
+      <c r="C34" s="46" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15271,10 +15272,10 @@
           <t>Gross household income ($)</t>
         </is>
       </c>
-      <c r="B35" s="50" t="n">
+      <c r="B35" s="51" t="n">
         <v>229000</v>
       </c>
-      <c r="C35" s="47" t="inlineStr">
+      <c r="C35" s="48" t="inlineStr">
         <is>
           <t>Matt (~$144k) + Sue's salary.</t>
         </is>
@@ -15286,19 +15287,19 @@
           <t>Savings rate</t>
         </is>
       </c>
-      <c r="B36" s="74">
+      <c r="B36" s="75">
         <f>B32/B35</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="44" t="inlineStr">
+      <c r="A38" s="45" t="inlineStr">
         <is>
           <t>⑤ FI NUMBER  (with &amp; without the pension)</t>
         </is>
       </c>
-      <c r="B38" s="45" t="n"/>
-      <c r="C38" s="45" t="n"/>
+      <c r="B38" s="46" t="n"/>
+      <c r="C38" s="46" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -15306,11 +15307,11 @@
           <t>Gross FI number (spend ÷ SWR)</t>
         </is>
       </c>
-      <c r="B39" s="64">
+      <c r="B39" s="65">
         <f>B8/B9</f>
         <v/>
       </c>
-      <c r="C39" s="47" t="inlineStr">
+      <c r="C39" s="48" t="inlineStr">
         <is>
           <t>Portfolio-only target, today's dollars — the conservative number to aim at.</t>
         </is>
@@ -15322,11 +15323,11 @@
           <t>Sue's annual pension (from Pension tab)</t>
         </is>
       </c>
-      <c r="B40" s="73">
+      <c r="B40" s="74">
         <f>'Pension - Sue'!B33</f>
         <v/>
       </c>
-      <c r="C40" s="47" t="inlineStr">
+      <c r="C40" s="48" t="inlineStr">
         <is>
           <t>Future nominal $ (grown to her retirement) — treat the offset below as approximate.</t>
         </is>
@@ -15338,10 +15339,10 @@
           <t>Social Security household (annual, est)</t>
         </is>
       </c>
-      <c r="B41" s="50" t="n">
+      <c r="B41" s="51" t="n">
         <v>40000</v>
       </c>
-      <c r="C41" s="47" t="inlineStr">
+      <c r="C41" s="48" t="inlineStr">
         <is>
           <t>WEP/GPO repealed (2025) — Sue keeps full spousal/survivor SS. Verify her record.</t>
         </is>
@@ -15353,7 +15354,7 @@
           <t>Income floor (pension + SS)</t>
         </is>
       </c>
-      <c r="B42" s="73">
+      <c r="B42" s="74">
         <f>B40+B41</f>
         <v/>
       </c>
@@ -15364,40 +15365,40 @@
           <t>Pension+SS capitalized value</t>
         </is>
       </c>
-      <c r="B43" s="73">
+      <c r="B43" s="74">
         <f>B42/B9</f>
         <v/>
       </c>
-      <c r="C43" s="47" t="inlineStr">
+      <c r="C43" s="48" t="inlineStr">
         <is>
           <t>Roughly what that income floor is 'worth' vs a portfolio — it reduces the target below.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="63" t="inlineStr">
+      <c r="A44" s="64" t="inlineStr">
         <is>
           <t>NET FI number (target once floor starts)</t>
         </is>
       </c>
-      <c r="B44" s="64">
+      <c r="B44" s="65">
         <f>MAX(0,(B8-B42)/B9)</f>
         <v/>
       </c>
-      <c r="C44" s="47" t="inlineStr">
+      <c r="C44" s="48" t="inlineStr">
         <is>
           <t>$0 means pension+SS alone cover target spend in the traditional-retirement phase.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="44" t="inlineStr">
+      <c r="A48" s="45" t="inlineStr">
         <is>
           <t>⑥ YEARS TO FI  (portfolio-only runway)</t>
         </is>
       </c>
-      <c r="B48" s="45" t="n"/>
-      <c r="C48" s="45" t="n"/>
+      <c r="B48" s="46" t="n"/>
+      <c r="C48" s="46" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -15405,11 +15406,11 @@
           <t>Years to reach GROSS FI number</t>
         </is>
       </c>
-      <c r="B49" s="75">
+      <c r="B49" s="76">
         <f>IFERROR(NPER(B12,-B32,-B21,B39),"check inputs")</f>
         <v/>
       </c>
-      <c r="C49" s="41" t="inlineStr">
+      <c r="C49" s="42" t="inlineStr">
         <is>
           <t>Current invested + annual contributions growing at the real return. Pension+SS shorten this once they begin (see ⑤).</t>
         </is>
@@ -15421,7 +15422,7 @@
           <t>Matt's age at FI</t>
         </is>
       </c>
-      <c r="B50" s="76">
+      <c r="B50" s="77">
         <f>IF(ISNUMBER(B49),B5+B49,"—")</f>
         <v/>
       </c>
@@ -15432,19 +15433,19 @@
           <t>FI calendar year</t>
         </is>
       </c>
-      <c r="B51" s="77">
+      <c r="B51" s="78">
         <f>IF(ISNUMBER(B49),B7+B49,"—")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="44" t="inlineStr">
+      <c r="A53" s="45" t="inlineStr">
         <is>
           <t>⑦ PRE-59½ BRIDGE  (early-access runway)</t>
         </is>
       </c>
-      <c r="B53" s="45" t="n"/>
-      <c r="C53" s="45" t="n"/>
+      <c r="B53" s="46" t="n"/>
+      <c r="C53" s="46" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15452,7 +15453,7 @@
           <t>Planned early-retire age (Matt)</t>
         </is>
       </c>
-      <c r="B54" s="49" t="n">
+      <c r="B54" s="50" t="n">
         <v>55</v>
       </c>
     </row>
@@ -15462,7 +15463,7 @@
           <t>Roth IRA contributions (accessible)</t>
         </is>
       </c>
-      <c r="B55" s="72" t="n">
+      <c r="B55" s="73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15472,7 +15473,7 @@
           <t>HSA receipt shoebox (accessible)</t>
         </is>
       </c>
-      <c r="B56" s="72" t="n">
+      <c r="B56" s="73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15482,17 +15483,17 @@
           <t>Taxable brokerage</t>
         </is>
       </c>
-      <c r="B57" s="72" t="n">
+      <c r="B57" s="73" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="63" t="inlineStr">
+      <c r="A58" s="64" t="inlineStr">
         <is>
           <t>Total accessible before 59½</t>
         </is>
       </c>
-      <c r="B58" s="64">
+      <c r="B58" s="65">
         <f>SUM(B55:B57)</f>
         <v/>
       </c>
@@ -15503,7 +15504,7 @@
           <t>Years until 59½</t>
         </is>
       </c>
-      <c r="B59" s="76">
+      <c r="B59" s="77">
         <f>59.5-B54</f>
         <v/>
       </c>
@@ -15514,10 +15515,10 @@
           <t>Annual spend uncovered in bridge ($)</t>
         </is>
       </c>
-      <c r="B60" s="50" t="n">
+      <c r="B60" s="51" t="n">
         <v>90000</v>
       </c>
-      <c r="C60" s="47" t="inlineStr">
+      <c r="C60" s="48" t="inlineStr">
         <is>
           <t>If Sue is still teaching, subtract her take-home — the gap may be small or zero.</t>
         </is>
@@ -15529,40 +15530,40 @@
           <t>Bridge need</t>
         </is>
       </c>
-      <c r="B61" s="73">
+      <c r="B61" s="74">
         <f>B59*B60</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="63" t="inlineStr">
+      <c r="A62" s="64" t="inlineStr">
         <is>
           <t>Bridge surplus / (gap)</t>
         </is>
       </c>
-      <c r="B62" s="64">
+      <c r="B62" s="65">
         <f>B58-B61</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="44" t="inlineStr">
+      <c r="A64" s="45" t="inlineStr">
         <is>
           <t>⑧ TWO-PHASE PLAN</t>
         </is>
       </c>
-      <c r="B64" s="45" t="n"/>
-      <c r="C64" s="45" t="n"/>
+      <c r="B64" s="46" t="n"/>
+      <c r="C64" s="46" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="63" t="inlineStr">
+      <c r="A65" s="64" t="inlineStr">
         <is>
           <t>Phase 1 — Matt steps back first</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="41" t="inlineStr">
+      <c r="A66" s="42" t="inlineStr">
         <is>
           <t>Sue keeps teaching: her salary + retiree-eligible health coverage bridge the household, so the portfolio keeps compounding and the pre-59½ gap above stays small.</t>
         </is>
@@ -15570,14 +15571,14 @@
     </row>
     <row r="67"/>
     <row r="68">
-      <c r="A68" s="63" t="inlineStr">
+      <c r="A68" s="64" t="inlineStr">
         <is>
           <t>Phase 2 — Sue reaches her 80% pension cap</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="78">
+      <c r="A69" s="79">
         <f>CONCATENATE("Sue hits the 80% cap at age ",'Pension - Sue'!C52," (year ",'Pension - Sue'!C53,"); ","both fully retired — the pension+SS floor then covers about ",TEXT(B42/B8,"0%")," of target spend.")</f>
         <v/>
       </c>
@@ -15620,875 +15621,875 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>Amazon — Monthly Reconciliation</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" s="39">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>All Amazon spend now lands in ONE bucket — 'Amazon (misc)', CC Detail row 14 — via a single regex rule (AMZN|AMAZON). Each month, split that total into real categories below. ORANGE = you enter $. The reference list at the bottom shows the actual Amazon transactions to guide the split.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>① AMAZON TOTAL TO RECONCILE  (auto — from CC Detail)</t>
         </is>
       </c>
-      <c r="B4" s="45" t="n"/>
-      <c r="C4" s="45" t="n"/>
-      <c r="D4" s="45" t="n"/>
-      <c r="E4" s="45" t="n"/>
-      <c r="F4" s="45" t="n"/>
-      <c r="G4" s="45" t="n"/>
-      <c r="H4" s="45" t="n"/>
-      <c r="I4" s="45" t="n"/>
-      <c r="J4" s="45" t="n"/>
-      <c r="K4" s="45" t="n"/>
-      <c r="L4" s="45" t="n"/>
-      <c r="M4" s="45" t="n"/>
-      <c r="N4" s="45" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="46" t="n"/>
+      <c r="L4" s="46" t="n"/>
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="79" t="inlineStr">
+      <c r="A5" s="80" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B5" s="53" t="inlineStr">
+      <c r="B5" s="54" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C5" s="53" t="inlineStr">
+      <c r="C5" s="54" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D5" s="53" t="inlineStr">
+      <c r="D5" s="54" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E5" s="53" t="inlineStr">
+      <c r="E5" s="54" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F5" s="53" t="inlineStr">
+      <c r="F5" s="54" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G5" s="53" t="inlineStr">
+      <c r="G5" s="54" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H5" s="53" t="inlineStr">
+      <c r="H5" s="54" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I5" s="53" t="inlineStr">
+      <c r="I5" s="54" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J5" s="53" t="inlineStr">
+      <c r="J5" s="54" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K5" s="53" t="inlineStr">
+      <c r="K5" s="54" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L5" s="53" t="inlineStr">
+      <c r="L5" s="54" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M5" s="53" t="inlineStr">
+      <c r="M5" s="54" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="N5" s="53" t="inlineStr">
+      <c r="N5" s="54" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="80" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>Amazon (misc) — to reconcile</t>
         </is>
       </c>
-      <c r="B6" s="81">
+      <c r="B6" s="82">
         <f>'CC Detail'!B14</f>
         <v/>
       </c>
-      <c r="C6" s="81">
+      <c r="C6" s="82">
         <f>'CC Detail'!C14</f>
         <v/>
       </c>
-      <c r="D6" s="81">
+      <c r="D6" s="82">
         <f>'CC Detail'!D14</f>
         <v/>
       </c>
-      <c r="E6" s="81">
+      <c r="E6" s="82">
         <f>'CC Detail'!E14</f>
         <v/>
       </c>
-      <c r="F6" s="81">
+      <c r="F6" s="82">
         <f>'CC Detail'!F14</f>
         <v/>
       </c>
-      <c r="G6" s="81">
+      <c r="G6" s="82">
         <f>'CC Detail'!G14</f>
         <v/>
       </c>
-      <c r="H6" s="81">
+      <c r="H6" s="82">
         <f>'CC Detail'!H14</f>
         <v/>
       </c>
-      <c r="I6" s="81">
+      <c r="I6" s="82">
         <f>'CC Detail'!I14</f>
         <v/>
       </c>
-      <c r="J6" s="81">
+      <c r="J6" s="82">
         <f>'CC Detail'!J14</f>
         <v/>
       </c>
-      <c r="K6" s="81">
+      <c r="K6" s="82">
         <f>'CC Detail'!K14</f>
         <v/>
       </c>
-      <c r="L6" s="81">
+      <c r="L6" s="82">
         <f>'CC Detail'!L14</f>
         <v/>
       </c>
-      <c r="M6" s="81">
+      <c r="M6" s="82">
         <f>'CC Detail'!M14</f>
         <v/>
       </c>
-      <c r="N6" s="82">
+      <c r="N6" s="83">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="44" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>② ALLOCATE INTO CATEGORIES  (enter $ per month)</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n"/>
-      <c r="C8" s="45" t="n"/>
-      <c r="D8" s="45" t="n"/>
-      <c r="E8" s="45" t="n"/>
-      <c r="F8" s="45" t="n"/>
-      <c r="G8" s="45" t="n"/>
-      <c r="H8" s="45" t="n"/>
-      <c r="I8" s="45" t="n"/>
-      <c r="J8" s="45" t="n"/>
-      <c r="K8" s="45" t="n"/>
-      <c r="L8" s="45" t="n"/>
-      <c r="M8" s="45" t="n"/>
-      <c r="N8" s="45" t="n"/>
+      <c r="B8" s="46" t="n"/>
+      <c r="C8" s="46" t="n"/>
+      <c r="D8" s="46" t="n"/>
+      <c r="E8" s="46" t="n"/>
+      <c r="F8" s="46" t="n"/>
+      <c r="G8" s="46" t="n"/>
+      <c r="H8" s="46" t="n"/>
+      <c r="I8" s="46" t="n"/>
+      <c r="J8" s="46" t="n"/>
+      <c r="K8" s="46" t="n"/>
+      <c r="L8" s="46" t="n"/>
+      <c r="M8" s="46" t="n"/>
+      <c r="N8" s="46" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="79" t="inlineStr">
+      <c r="A9" s="80" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B9" s="53" t="inlineStr">
+      <c r="B9" s="54" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C9" s="53" t="inlineStr">
+      <c r="C9" s="54" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D9" s="53" t="inlineStr">
+      <c r="D9" s="54" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E9" s="53" t="inlineStr">
+      <c r="E9" s="54" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F9" s="53" t="inlineStr">
+      <c r="F9" s="54" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G9" s="53" t="inlineStr">
+      <c r="G9" s="54" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H9" s="53" t="inlineStr">
+      <c r="H9" s="54" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I9" s="53" t="inlineStr">
+      <c r="I9" s="54" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J9" s="53" t="inlineStr">
+      <c r="J9" s="54" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K9" s="53" t="inlineStr">
+      <c r="K9" s="54" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L9" s="53" t="inlineStr">
+      <c r="L9" s="54" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M9" s="53" t="inlineStr">
+      <c r="M9" s="54" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="N9" s="53" t="inlineStr">
+      <c r="N9" s="54" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="83" t="inlineStr">
+      <c r="A10" s="84" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="B10" s="84" t="n">
+      <c r="B10" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="84" t="n">
+      <c r="C10" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="84" t="n">
+      <c r="D10" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="84" t="n">
+      <c r="E10" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="84" t="n">
+      <c r="F10" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="84" t="n">
+      <c r="G10" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="84" t="n">
+      <c r="H10" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="84" t="n">
+      <c r="I10" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="84" t="n">
+      <c r="J10" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="84" t="n">
+      <c r="K10" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="84" t="n">
+      <c r="L10" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="84" t="n">
+      <c r="M10" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="81">
+      <c r="N10" s="82">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="83" t="inlineStr">
+      <c r="A11" s="84" t="inlineStr">
         <is>
           <t>Kids / Activities</t>
         </is>
       </c>
-      <c r="B11" s="84" t="n">
+      <c r="B11" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="84" t="n">
+      <c r="C11" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="84" t="n">
+      <c r="D11" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="84" t="n">
+      <c r="E11" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="84" t="n">
+      <c r="F11" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="84" t="n">
+      <c r="G11" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="84" t="n">
+      <c r="H11" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="84" t="n">
+      <c r="I11" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="84" t="n">
+      <c r="J11" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="84" t="n">
+      <c r="K11" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="84" t="n">
+      <c r="L11" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="84" t="n">
+      <c r="M11" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="81">
+      <c r="N11" s="82">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="83" t="inlineStr">
+      <c r="A12" s="84" t="inlineStr">
         <is>
           <t>Personal Care</t>
         </is>
       </c>
-      <c r="B12" s="84" t="n">
+      <c r="B12" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="84" t="n">
+      <c r="C12" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="84" t="n">
+      <c r="D12" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="84" t="n">
+      <c r="E12" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="84" t="n">
+      <c r="F12" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="84" t="n">
+      <c r="G12" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="84" t="n">
+      <c r="H12" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="84" t="n">
+      <c r="I12" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="84" t="n">
+      <c r="J12" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="84" t="n">
+      <c r="K12" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="84" t="n">
+      <c r="L12" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="84" t="n">
+      <c r="M12" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="81">
+      <c r="N12" s="82">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="83" t="inlineStr">
+      <c r="A13" s="84" t="inlineStr">
         <is>
           <t>Pharmacy / Health</t>
         </is>
       </c>
-      <c r="B13" s="84" t="n">
+      <c r="B13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="84" t="n">
+      <c r="C13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="84" t="n">
+      <c r="D13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="84" t="n">
+      <c r="E13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="84" t="n">
+      <c r="F13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="84" t="n">
+      <c r="G13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="84" t="n">
+      <c r="H13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="84" t="n">
+      <c r="I13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="84" t="n">
+      <c r="J13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="84" t="n">
+      <c r="K13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="84" t="n">
+      <c r="L13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="84" t="n">
+      <c r="M13" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="81">
+      <c r="N13" s="82">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="83" t="inlineStr">
+      <c r="A14" s="84" t="inlineStr">
         <is>
           <t>Home / Hardware</t>
         </is>
       </c>
-      <c r="B14" s="84" t="n">
+      <c r="B14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="84" t="n">
+      <c r="C14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="84" t="n">
+      <c r="D14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="84" t="n">
+      <c r="E14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="84" t="n">
+      <c r="F14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="84" t="n">
+      <c r="G14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="84" t="n">
+      <c r="H14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="84" t="n">
+      <c r="I14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="84" t="n">
+      <c r="J14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="84" t="n">
+      <c r="K14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="84" t="n">
+      <c r="L14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="84" t="n">
+      <c r="M14" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="81">
+      <c r="N14" s="82">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="83" t="inlineStr">
+      <c r="A15" s="84" t="inlineStr">
         <is>
           <t>Subscriptions (Prime/Kindle/Audible)</t>
         </is>
       </c>
-      <c r="B15" s="84" t="n">
+      <c r="B15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="84" t="n">
+      <c r="C15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="84" t="n">
+      <c r="D15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="84" t="n">
+      <c r="E15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="84" t="n">
+      <c r="F15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="84" t="n">
+      <c r="G15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="84" t="n">
+      <c r="H15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="84" t="n">
+      <c r="I15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="84" t="n">
+      <c r="J15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="84" t="n">
+      <c r="K15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="84" t="n">
+      <c r="L15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="84" t="n">
+      <c r="M15" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="81">
+      <c r="N15" s="82">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="83" t="inlineStr">
+      <c r="A16" s="84" t="inlineStr">
         <is>
           <t>Other / gifts</t>
         </is>
       </c>
-      <c r="B16" s="84" t="n">
+      <c r="B16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="84" t="n">
+      <c r="C16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="84" t="n">
+      <c r="D16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="84" t="n">
+      <c r="E16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="84" t="n">
+      <c r="F16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="84" t="n">
+      <c r="G16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="84" t="n">
+      <c r="H16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="84" t="n">
+      <c r="I16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="84" t="n">
+      <c r="J16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="84" t="n">
+      <c r="K16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="84" t="n">
+      <c r="L16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="84" t="n">
+      <c r="M16" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="81">
+      <c r="N16" s="82">
         <f>SUM(B16:M16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="80" t="inlineStr">
+      <c r="A17" s="81" t="inlineStr">
         <is>
           <t>Allocated total</t>
         </is>
       </c>
-      <c r="B17" s="85">
+      <c r="B17" s="86">
         <f>SUM(B10:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="85">
+      <c r="C17" s="86">
         <f>SUM(C10:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="85">
+      <c r="D17" s="86">
         <f>SUM(D10:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="85">
+      <c r="E17" s="86">
         <f>SUM(E10:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="85">
+      <c r="F17" s="86">
         <f>SUM(F10:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="85">
+      <c r="G17" s="86">
         <f>SUM(G10:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="85">
+      <c r="H17" s="86">
         <f>SUM(H10:H16)</f>
         <v/>
       </c>
-      <c r="I17" s="85">
+      <c r="I17" s="86">
         <f>SUM(I10:I16)</f>
         <v/>
       </c>
-      <c r="J17" s="85">
+      <c r="J17" s="86">
         <f>SUM(J10:J16)</f>
         <v/>
       </c>
-      <c r="K17" s="85">
+      <c r="K17" s="86">
         <f>SUM(K10:K16)</f>
         <v/>
       </c>
-      <c r="L17" s="85">
+      <c r="L17" s="86">
         <f>SUM(L10:L16)</f>
         <v/>
       </c>
-      <c r="M17" s="85">
+      <c r="M17" s="86">
         <f>SUM(M10:M16)</f>
         <v/>
       </c>
-      <c r="N17" s="85">
+      <c r="N17" s="86">
         <f>SUM(N10:N16)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="80" t="inlineStr">
+      <c r="A18" s="81" t="inlineStr">
         <is>
           <t>Unallocated remaining</t>
         </is>
       </c>
-      <c r="B18" s="82">
+      <c r="B18" s="83">
         <f>B6-B17</f>
         <v/>
       </c>
-      <c r="C18" s="82">
+      <c r="C18" s="83">
         <f>C6-C17</f>
         <v/>
       </c>
-      <c r="D18" s="82">
+      <c r="D18" s="83">
         <f>D6-D17</f>
         <v/>
       </c>
-      <c r="E18" s="82">
+      <c r="E18" s="83">
         <f>E6-E17</f>
         <v/>
       </c>
-      <c r="F18" s="82">
+      <c r="F18" s="83">
         <f>F6-F17</f>
         <v/>
       </c>
-      <c r="G18" s="82">
+      <c r="G18" s="83">
         <f>G6-G17</f>
         <v/>
       </c>
-      <c r="H18" s="82">
+      <c r="H18" s="83">
         <f>H6-H17</f>
         <v/>
       </c>
-      <c r="I18" s="82">
+      <c r="I18" s="83">
         <f>I6-I17</f>
         <v/>
       </c>
-      <c r="J18" s="82">
+      <c r="J18" s="83">
         <f>J6-J17</f>
         <v/>
       </c>
-      <c r="K18" s="82">
+      <c r="K18" s="83">
         <f>K6-K17</f>
         <v/>
       </c>
-      <c r="L18" s="82">
+      <c r="L18" s="83">
         <f>L6-L17</f>
         <v/>
       </c>
-      <c r="M18" s="82">
+      <c r="M18" s="83">
         <f>M6-M17</f>
         <v/>
       </c>
-      <c r="N18" s="82">
+      <c r="N18" s="83">
         <f>N6-N17</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="44" t="inlineStr">
+      <c r="A20" s="45" t="inlineStr">
         <is>
           <t>③ RECONCILED CATEGORY TOTALS (YTD) — the un-muddied picture</t>
         </is>
       </c>
-      <c r="B20" s="45" t="n"/>
-      <c r="C20" s="45" t="n"/>
-      <c r="D20" s="45" t="n"/>
+      <c r="B20" s="46" t="n"/>
+      <c r="C20" s="46" t="n"/>
+      <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="79" t="inlineStr">
+      <c r="A21" s="80" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B21" s="53" t="inlineStr">
+      <c r="B21" s="54" t="inlineStr">
         <is>
           <t>Native (CC Detail)</t>
         </is>
       </c>
-      <c r="C21" s="53" t="inlineStr">
+      <c r="C21" s="54" t="inlineStr">
         <is>
           <t>+ Amazon</t>
         </is>
       </c>
-      <c r="D21" s="53">
+      <c r="D21" s="54">
         <f> True total (YTD)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="83" t="inlineStr">
+      <c r="A22" s="84" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="B22" s="81">
+      <c r="B22" s="82">
         <f>'CC Detail'!N5</f>
         <v/>
       </c>
-      <c r="C22" s="81">
+      <c r="C22" s="82">
         <f>N10</f>
         <v/>
       </c>
-      <c r="D22" s="82">
+      <c r="D22" s="83">
         <f>B22+C22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="83" t="inlineStr">
+      <c r="A23" s="84" t="inlineStr">
         <is>
           <t>Kids / Activities</t>
         </is>
       </c>
-      <c r="B23" s="81">
+      <c r="B23" s="82">
         <f>'CC Detail'!N9</f>
         <v/>
       </c>
-      <c r="C23" s="81">
+      <c r="C23" s="82">
         <f>N11</f>
         <v/>
       </c>
-      <c r="D23" s="82">
+      <c r="D23" s="83">
         <f>B23+C23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="83" t="inlineStr">
+      <c r="A24" s="84" t="inlineStr">
         <is>
           <t>Personal Care</t>
         </is>
       </c>
-      <c r="B24" s="81">
+      <c r="B24" s="82">
         <f>'CC Detail'!N11</f>
         <v/>
       </c>
-      <c r="C24" s="81">
+      <c r="C24" s="82">
         <f>N12</f>
         <v/>
       </c>
-      <c r="D24" s="82">
+      <c r="D24" s="83">
         <f>B24+C24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="83" t="inlineStr">
+      <c r="A25" s="84" t="inlineStr">
         <is>
           <t>Pharmacy / Health</t>
         </is>
       </c>
-      <c r="B25" s="81">
+      <c r="B25" s="82">
         <f>'CC Detail'!N12</f>
         <v/>
       </c>
-      <c r="C25" s="81">
+      <c r="C25" s="82">
         <f>N13</f>
         <v/>
       </c>
-      <c r="D25" s="82">
+      <c r="D25" s="83">
         <f>B25+C25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="83" t="inlineStr">
+      <c r="A26" s="84" t="inlineStr">
         <is>
           <t>Home / Hardware</t>
         </is>
       </c>
-      <c r="B26" s="81">
+      <c r="B26" s="82">
         <f>'CC Detail'!N13</f>
         <v/>
       </c>
-      <c r="C26" s="81">
+      <c r="C26" s="82">
         <f>N14</f>
         <v/>
       </c>
-      <c r="D26" s="82">
+      <c r="D26" s="83">
         <f>B26+C26</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="83" t="inlineStr">
+      <c r="A27" s="84" t="inlineStr">
         <is>
           <t>Subscriptions</t>
         </is>
       </c>
-      <c r="B27" s="81">
+      <c r="B27" s="82">
         <f>'CC Detail'!N8</f>
         <v/>
       </c>
-      <c r="C27" s="81">
+      <c r="C27" s="82">
         <f>N15</f>
         <v/>
       </c>
-      <c r="D27" s="82">
+      <c r="D27" s="83">
         <f>B27+C27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="83" t="inlineStr">
+      <c r="A28" s="84" t="inlineStr">
         <is>
           <t>Other / gifts</t>
         </is>
       </c>
-      <c r="B28" s="81">
+      <c r="B28" s="82">
         <f>'CC Detail'!N17</f>
         <v/>
       </c>
-      <c r="C28" s="81">
+      <c r="C28" s="82">
         <f>N16</f>
         <v/>
       </c>
-      <c r="D28" s="82">
+      <c r="D28" s="83">
         <f>B28+C28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="41" t="inlineStr">
+      <c r="A29" s="42" t="inlineStr">
         <is>
           <t>Note: once split, these 'true totals' show real spend per category — Amazon no longer hides hardware, hygiene, and kids' purchases in one lump. Feed these into the guardrail when it's built.</t>
         </is>
@@ -16496,39 +16497,39 @@
     </row>
     <row r="30"/>
     <row r="32">
-      <c r="A32" s="44" t="inlineStr">
+      <c r="A32" s="45" t="inlineStr">
         <is>
           <t>④ REFERENCE — current Amazon transactions  (auto, read-only)</t>
         </is>
       </c>
-      <c r="B32" s="45" t="n"/>
-      <c r="C32" s="45" t="n"/>
-      <c r="D32" s="45" t="n"/>
+      <c r="B32" s="46" t="n"/>
+      <c r="C32" s="46" t="n"/>
+      <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="41" t="inlineStr">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>Pulls Amazon rows from your Barclay import so you can see what to split. Refreshes when you paste new data.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="79" t="inlineStr">
+      <c r="A34" s="80" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B34" s="79" t="inlineStr">
+      <c r="B34" s="80" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C34" s="53" t="inlineStr">
+      <c r="C34" s="54" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D34" s="53" t="inlineStr">
+      <c r="D34" s="54" t="inlineStr">
         <is>
           <t>Purchased by</t>
         </is>
@@ -16577,32 +16578,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>Solar — Reinvestment &amp; Effective ROI</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1" s="39">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>Goal: redirect your former electric-bill spend into a growth vehicle so the solar's ROI compounds. ORANGE = inputs. Enphase has no CSV export, so enter the monthly energy log by hand (you can backfill Mar–Sep now, then add one row per month). Educational planning, not investment/tax advice.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>① INCENTIVES &amp; NET CAPITAL COST</t>
         </is>
       </c>
-      <c r="B4" s="45" t="n"/>
-      <c r="C4" s="45" t="n"/>
-      <c r="D4" s="45" t="n"/>
-      <c r="E4" s="45" t="n"/>
-      <c r="F4" s="45" t="n"/>
-      <c r="G4" s="45" t="n"/>
-      <c r="H4" s="45" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16610,7 +16611,7 @@
           <t>Gross capital outlay</t>
         </is>
       </c>
-      <c r="B5" s="73">
+      <c r="B5" s="74">
         <f>'Solar ROI'!N5</f>
         <v/>
       </c>
@@ -16621,10 +16622,10 @@
           <t>Federal ITC (25D)</t>
         </is>
       </c>
-      <c r="B6" s="50" t="n">
+      <c r="B6" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="41" t="inlineStr">
+      <c r="C6" s="42" t="inlineStr">
         <is>
           <t>$0 if placed in service in 2026 (OBBB ended 25D after 12/31/2025). If PTO by 12/31/2025, use ~0.30×gross.</t>
         </is>
@@ -16636,7 +16637,7 @@
           <t>MA state credit (15%, max $1,000)</t>
         </is>
       </c>
-      <c r="B7" s="73">
+      <c r="B7" s="74">
         <f>MIN(1000,0.15*B5)</f>
         <v/>
       </c>
@@ -16647,331 +16648,331 @@
           <t>Other rebates / utility</t>
         </is>
       </c>
-      <c r="B8" s="50" t="n">
+      <c r="B8" s="51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>NET CAPITAL COST</t>
         </is>
       </c>
-      <c r="B9" s="64">
+      <c r="B9" s="65">
         <f>B5-B6-B7-B8</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="44" t="inlineStr">
+      <c r="A11" s="45" t="inlineStr">
         <is>
           <t>② MONTHLY ENERGY LOG  (Enphase — manual entry, kWh)</t>
         </is>
       </c>
-      <c r="B11" s="45" t="n"/>
-      <c r="C11" s="45" t="n"/>
-      <c r="D11" s="45" t="n"/>
-      <c r="E11" s="45" t="n"/>
-      <c r="F11" s="45" t="n"/>
-      <c r="G11" s="45" t="n"/>
-      <c r="H11" s="45" t="n"/>
+      <c r="B11" s="46" t="n"/>
+      <c r="C11" s="46" t="n"/>
+      <c r="D11" s="46" t="n"/>
+      <c r="E11" s="46" t="n"/>
+      <c r="F11" s="46" t="n"/>
+      <c r="G11" s="46" t="n"/>
+      <c r="H11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="47" t="inlineStr">
+      <c r="A12" s="48" t="inlineStr">
         <is>
           <t>Enter each month from your Enphase report. Net export = Exported − Imported (auto).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="79" t="inlineStr">
+      <c r="A13" s="80" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B13" s="53" t="inlineStr">
+      <c r="B13" s="54" t="inlineStr">
         <is>
           <t>Produced</t>
         </is>
       </c>
-      <c r="C13" s="53" t="inlineStr">
+      <c r="C13" s="54" t="inlineStr">
         <is>
           <t>Consumed</t>
         </is>
       </c>
-      <c r="D13" s="53" t="inlineStr">
+      <c r="D13" s="54" t="inlineStr">
         <is>
           <t>Imported</t>
         </is>
       </c>
-      <c r="E13" s="53" t="inlineStr">
+      <c r="E13" s="54" t="inlineStr">
         <is>
           <t>Exported</t>
         </is>
       </c>
-      <c r="F13" s="53" t="inlineStr">
+      <c r="F13" s="54" t="inlineStr">
         <is>
           <t>Net export</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="83" t="inlineStr">
+      <c r="A14" s="84" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="B14" s="86" t="n"/>
-      <c r="C14" s="86" t="n"/>
-      <c r="D14" s="86" t="n"/>
-      <c r="E14" s="86" t="n"/>
-      <c r="F14" s="87">
+      <c r="B14" s="87" t="n"/>
+      <c r="C14" s="87" t="n"/>
+      <c r="D14" s="87" t="n"/>
+      <c r="E14" s="87" t="n"/>
+      <c r="F14" s="88">
         <f>E14-D14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="83" t="inlineStr">
+      <c r="A15" s="84" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="B15" s="86" t="n"/>
-      <c r="C15" s="86" t="n"/>
-      <c r="D15" s="86" t="n"/>
-      <c r="E15" s="86" t="n"/>
-      <c r="F15" s="87">
+      <c r="B15" s="87" t="n"/>
+      <c r="C15" s="87" t="n"/>
+      <c r="D15" s="87" t="n"/>
+      <c r="E15" s="87" t="n"/>
+      <c r="F15" s="88">
         <f>E15-D15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="83" t="inlineStr">
+      <c r="A16" s="84" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="B16" s="86" t="n">
+      <c r="B16" s="87" t="n">
         <v>133.1</v>
       </c>
-      <c r="C16" s="86" t="n">
+      <c r="C16" s="87" t="n">
         <v>661.4</v>
       </c>
-      <c r="D16" s="86" t="n">
+      <c r="D16" s="87" t="n">
         <v>528.3</v>
       </c>
-      <c r="E16" s="86" t="n">
+      <c r="E16" s="87" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="87">
+      <c r="F16" s="88">
         <f>E16-D16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="83" t="inlineStr">
+      <c r="A17" s="84" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="B17" s="86" t="n">
+      <c r="B17" s="87" t="n">
         <v>314.2</v>
       </c>
-      <c r="C17" s="86" t="n">
+      <c r="C17" s="87" t="n">
         <v>102.6</v>
       </c>
-      <c r="D17" s="86" t="n">
+      <c r="D17" s="87" t="n">
         <v>50.1</v>
       </c>
-      <c r="E17" s="86" t="n">
+      <c r="E17" s="87" t="n">
         <v>261.7</v>
       </c>
-      <c r="F17" s="87">
+      <c r="F17" s="88">
         <f>E17-D17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="83" t="inlineStr">
+      <c r="A18" s="84" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B18" s="86" t="n">
+      <c r="B18" s="87" t="n">
         <v>997.1</v>
       </c>
-      <c r="C18" s="86" t="n">
+      <c r="C18" s="87" t="n">
         <v>475.1</v>
       </c>
-      <c r="D18" s="86" t="n">
+      <c r="D18" s="87" t="n">
         <v>246.7</v>
       </c>
-      <c r="E18" s="86" t="n">
+      <c r="E18" s="87" t="n">
         <v>768.7</v>
       </c>
-      <c r="F18" s="87">
+      <c r="F18" s="88">
         <f>E18-D18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="83" t="inlineStr">
+      <c r="A19" s="84" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="B19" s="86" t="n">
+      <c r="B19" s="87" t="n">
         <v>1128.1</v>
       </c>
-      <c r="C19" s="86" t="n">
+      <c r="C19" s="87" t="n">
         <v>784.5</v>
       </c>
-      <c r="D19" s="86" t="n">
+      <c r="D19" s="87" t="n">
         <v>383</v>
       </c>
-      <c r="E19" s="86" t="n">
+      <c r="E19" s="87" t="n">
         <v>726.6</v>
       </c>
-      <c r="F19" s="87">
+      <c r="F19" s="88">
         <f>E19-D19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="83" t="inlineStr">
+      <c r="A20" s="84" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="B20" s="86" t="n">
+      <c r="B20" s="87" t="n">
         <v>1058.5</v>
       </c>
-      <c r="C20" s="86" t="n">
+      <c r="C20" s="87" t="n">
         <v>964.6</v>
       </c>
-      <c r="D20" s="86" t="n">
+      <c r="D20" s="87" t="n">
         <v>507.4</v>
       </c>
-      <c r="E20" s="86" t="n">
+      <c r="E20" s="87" t="n">
         <v>601.3</v>
       </c>
-      <c r="F20" s="87">
+      <c r="F20" s="88">
         <f>E20-D20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="83" t="inlineStr">
+      <c r="A21" s="84" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="B21" s="86" t="n">
+      <c r="B21" s="87" t="n">
         <v>919.3</v>
       </c>
-      <c r="C21" s="86" t="n">
+      <c r="C21" s="87" t="n">
         <v>938.4</v>
       </c>
-      <c r="D21" s="86" t="n">
+      <c r="D21" s="87" t="n">
         <v>531.1</v>
       </c>
-      <c r="E21" s="86" t="n">
+      <c r="E21" s="87" t="n">
         <v>512</v>
       </c>
-      <c r="F21" s="87">
+      <c r="F21" s="88">
         <f>E21-D21</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="83" t="inlineStr">
+      <c r="A22" s="84" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="B22" s="86" t="n"/>
-      <c r="C22" s="86" t="n"/>
-      <c r="D22" s="86" t="n"/>
-      <c r="E22" s="86" t="n"/>
-      <c r="F22" s="87">
+      <c r="B22" s="87" t="n"/>
+      <c r="C22" s="87" t="n"/>
+      <c r="D22" s="87" t="n"/>
+      <c r="E22" s="87" t="n"/>
+      <c r="F22" s="88">
         <f>E22-D22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="83" t="inlineStr">
+      <c r="A23" s="84" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="B23" s="86" t="n"/>
-      <c r="C23" s="86" t="n"/>
-      <c r="D23" s="86" t="n"/>
-      <c r="E23" s="86" t="n"/>
-      <c r="F23" s="87">
+      <c r="B23" s="87" t="n"/>
+      <c r="C23" s="87" t="n"/>
+      <c r="D23" s="87" t="n"/>
+      <c r="E23" s="87" t="n"/>
+      <c r="F23" s="88">
         <f>E23-D23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="83" t="inlineStr">
+      <c r="A24" s="84" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="B24" s="86" t="n"/>
-      <c r="C24" s="86" t="n"/>
-      <c r="D24" s="86" t="n"/>
-      <c r="E24" s="86" t="n"/>
-      <c r="F24" s="87">
+      <c r="B24" s="87" t="n"/>
+      <c r="C24" s="87" t="n"/>
+      <c r="D24" s="87" t="n"/>
+      <c r="E24" s="87" t="n"/>
+      <c r="F24" s="88">
         <f>E24-D24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="83" t="inlineStr">
+      <c r="A25" s="84" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="B25" s="86" t="n"/>
-      <c r="C25" s="86" t="n"/>
-      <c r="D25" s="86" t="n"/>
-      <c r="E25" s="86" t="n"/>
-      <c r="F25" s="87">
+      <c r="B25" s="87" t="n"/>
+      <c r="C25" s="87" t="n"/>
+      <c r="D25" s="87" t="n"/>
+      <c r="E25" s="87" t="n"/>
+      <c r="F25" s="88">
         <f>E25-D25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="80" t="inlineStr">
+      <c r="A26" s="81" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B26" s="88">
+      <c r="B26" s="89">
         <f>SUM(B14:B25)</f>
         <v/>
       </c>
-      <c r="C26" s="88">
+      <c r="C26" s="89">
         <f>SUM(C14:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="88">
+      <c r="D26" s="89">
         <f>SUM(D14:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="88">
+      <c r="E26" s="89">
         <f>SUM(E14:E25)</f>
         <v/>
       </c>
-      <c r="F26" s="88">
+      <c r="F26" s="89">
         <f>SUM(F14:F25)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="41" t="inlineStr">
+      <c r="A27" s="42" t="inlineStr">
         <is>
           <t>Enter each month from your Enphase monthly report (no CSV export — read the tile values). Production swings seasonally: March is pre-filled from your report (133 kWh produced vs 661 consumed → net import), while summer months over-produce and export. Net export = Exported − Imported (negative = net import).</t>
         </is>
@@ -16979,18 +16980,18 @@
     </row>
     <row r="28"/>
     <row r="30">
-      <c r="A30" s="44" t="inlineStr">
+      <c r="A30" s="45" t="inlineStr">
         <is>
           <t>③ SAVINGS TO REINVEST</t>
         </is>
       </c>
-      <c r="B30" s="45" t="n"/>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
-      <c r="G30" s="45" t="n"/>
-      <c r="H30" s="45" t="n"/>
+      <c r="B30" s="46" t="n"/>
+      <c r="C30" s="46" t="n"/>
+      <c r="D30" s="46" t="n"/>
+      <c r="E30" s="46" t="n"/>
+      <c r="F30" s="46" t="n"/>
+      <c r="G30" s="46" t="n"/>
+      <c r="H30" s="46" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16998,12 +16999,12 @@
           <t>Pre-solar baseline bill ($/mo)</t>
         </is>
       </c>
-      <c r="B31" s="50" t="n">
-        <v>300</v>
-      </c>
-      <c r="C31" s="47" t="inlineStr">
-        <is>
-          <t>What you used to pay — this is the money you're freeing up.</t>
+      <c r="B31" s="51" t="n">
+        <v>166</v>
+      </c>
+      <c r="C31" s="48" t="inlineStr">
+        <is>
+          <t>2025 average actual electric bill (real data: $1,988/yr ÷ 12).</t>
         </is>
       </c>
     </row>
@@ -17013,22 +17014,22 @@
           <t>Post-solar actual bill ($/mo)</t>
         </is>
       </c>
-      <c r="B32" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="C32" s="47" t="inlineStr">
-        <is>
-          <t>Fixed customer/connection charges that remain.</t>
+      <c r="B32" s="51" t="n">
+        <v>95</v>
+      </c>
+      <c r="C32" s="48" t="inlineStr">
+        <is>
+          <t>Est. full-year post-solar avg (summer bills $87–122; winter eased by banked net-metering credits). Preliminary — refine after a full post-solar year.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="63" t="inlineStr">
+      <c r="A33" s="64" t="inlineStr">
         <is>
           <t>Monthly avoided cost (reinvest)</t>
         </is>
       </c>
-      <c r="B33" s="89">
+      <c r="B33" s="90">
         <f>MAX(0,B31-B32)</f>
         <v/>
       </c>
@@ -17039,7 +17040,7 @@
           <t>Annual avoided cost</t>
         </is>
       </c>
-      <c r="B34" s="73">
+      <c r="B34" s="74">
         <f>B33*12</f>
         <v/>
       </c>
@@ -17050,7 +17051,7 @@
           <t>SMART incentive ($/kWh)</t>
         </is>
       </c>
-      <c r="B35" s="90" t="n">
+      <c r="B35" s="91" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -17060,10 +17061,10 @@
           <t>Est. annual production (kWh)</t>
         </is>
       </c>
-      <c r="B36" s="91" t="n">
+      <c r="B36" s="92" t="n">
         <v>7000</v>
       </c>
-      <c r="C36" s="47" t="inlineStr">
+      <c r="C36" s="48" t="inlineStr">
         <is>
           <t>Rough full-year estimate from your 2026 trajectory (YTD ~5 MWh by Aug). Refine after a full year.</t>
         </is>
@@ -17075,7 +17076,7 @@
           <t>Annual SMART payment (yrs 1–10)</t>
         </is>
       </c>
-      <c r="B37" s="73">
+      <c r="B37" s="74">
         <f>B35*B36</f>
         <v/>
       </c>
@@ -17086,28 +17087,28 @@
           <t>Blended electric rate ($/kWh)</t>
         </is>
       </c>
-      <c r="B38" s="90" t="n">
+      <c r="B38" s="91" t="n">
         <v>0.3</v>
       </c>
-      <c r="C38" s="47" t="inlineStr">
+      <c r="C38" s="48" t="inlineStr">
         <is>
           <t>Used to value net-metering credits from exports.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="44" t="inlineStr">
+      <c r="A40" s="45" t="inlineStr">
         <is>
           <t>④ REINVESTMENT MODEL — accelerate the ROI</t>
         </is>
       </c>
-      <c r="B40" s="45" t="n"/>
-      <c r="C40" s="45" t="n"/>
-      <c r="D40" s="45" t="n"/>
-      <c r="E40" s="45" t="n"/>
-      <c r="F40" s="45" t="n"/>
-      <c r="G40" s="45" t="n"/>
-      <c r="H40" s="45" t="n"/>
+      <c r="B40" s="46" t="n"/>
+      <c r="C40" s="46" t="n"/>
+      <c r="D40" s="46" t="n"/>
+      <c r="E40" s="46" t="n"/>
+      <c r="F40" s="46" t="n"/>
+      <c r="G40" s="46" t="n"/>
+      <c r="H40" s="46" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -17115,10 +17116,10 @@
           <t>Reinvestment return (nominal)</t>
         </is>
       </c>
-      <c r="B41" s="51" t="n">
+      <c r="B41" s="52" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C41" s="47" t="inlineStr">
+      <c r="C41" s="48" t="inlineStr">
         <is>
           <t>Matches the 7% on your Scenarios tab.</t>
         </is>
@@ -17130,7 +17131,7 @@
           <t>Electric rate escalation (%/yr)</t>
         </is>
       </c>
-      <c r="B42" s="51" t="n">
+      <c r="B42" s="52" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -17140,7 +17141,7 @@
           <t>Horizon (years)</t>
         </is>
       </c>
-      <c r="B43" s="49" t="n">
+      <c r="B43" s="50" t="n">
         <v>25</v>
       </c>
     </row>
@@ -17150,923 +17151,923 @@
           <t>First full year</t>
         </is>
       </c>
-      <c r="B44" s="49" t="n">
+      <c r="B44" s="50" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1" s="39">
-      <c r="A46" s="65" t="inlineStr">
+      <c r="A46" s="66" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B46" s="65" t="inlineStr">
+      <c r="B46" s="66" t="inlineStr">
         <is>
           <t>Calendar</t>
         </is>
       </c>
-      <c r="C46" s="65" t="inlineStr">
+      <c r="C46" s="66" t="inlineStr">
         <is>
           <t>Avoided cost</t>
         </is>
       </c>
-      <c r="D46" s="65" t="inlineStr">
+      <c r="D46" s="66" t="inlineStr">
         <is>
           <t>SMART</t>
         </is>
       </c>
-      <c r="E46" s="65" t="inlineStr">
+      <c r="E46" s="66" t="inlineStr">
         <is>
           <t>Reinvested/yr</t>
         </is>
       </c>
-      <c r="F46" s="65" t="inlineStr">
+      <c r="F46" s="66" t="inlineStr">
         <is>
           <t>Reinvested bal.</t>
         </is>
       </c>
-      <c r="G46" s="65" t="inlineStr">
+      <c r="G46" s="66" t="inlineStr">
         <is>
           <t>Simple cum.</t>
         </is>
       </c>
-      <c r="H46" s="65" t="inlineStr">
+      <c r="H46" s="66" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="55" t="n">
+      <c r="A47" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="B47" s="92">
+      <c r="B47" s="93">
         <f>$B$44+(A47-1)</f>
         <v/>
       </c>
-      <c r="C47" s="68">
+      <c r="C47" s="69">
         <f>$B$34*(1+$B$42)^(A47-1)</f>
         <v/>
       </c>
-      <c r="D47" s="68">
+      <c r="D47" s="69">
         <f>IF(A47&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E47" s="68">
+      <c r="E47" s="69">
         <f>C47+D47</f>
         <v/>
       </c>
-      <c r="F47" s="85">
+      <c r="F47" s="86">
         <f>E47</f>
         <v/>
       </c>
-      <c r="G47" s="68">
+      <c r="G47" s="69">
         <f>E47</f>
         <v/>
       </c>
-      <c r="H47" s="83">
+      <c r="H47" s="84">
         <f>IF(F47&gt;=$B$9,"◄ accelerated payback",IF(G47&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="55" t="n">
+      <c r="A48" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="B48" s="92">
+      <c r="B48" s="93">
         <f>$B$44+(A48-1)</f>
         <v/>
       </c>
-      <c r="C48" s="68">
+      <c r="C48" s="69">
         <f>$B$34*(1+$B$42)^(A48-1)</f>
         <v/>
       </c>
-      <c r="D48" s="68">
+      <c r="D48" s="69">
         <f>IF(A48&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E48" s="68">
+      <c r="E48" s="69">
         <f>C48+D48</f>
         <v/>
       </c>
-      <c r="F48" s="85">
+      <c r="F48" s="86">
         <f>F47*(1+$B$41)+E48</f>
         <v/>
       </c>
-      <c r="G48" s="68">
+      <c r="G48" s="69">
         <f>G47+E48</f>
         <v/>
       </c>
-      <c r="H48" s="83">
+      <c r="H48" s="84">
         <f>IF(F48&gt;=$B$9,"◄ accelerated payback",IF(G48&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="55" t="n">
+      <c r="A49" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="B49" s="92">
+      <c r="B49" s="93">
         <f>$B$44+(A49-1)</f>
         <v/>
       </c>
-      <c r="C49" s="68">
+      <c r="C49" s="69">
         <f>$B$34*(1+$B$42)^(A49-1)</f>
         <v/>
       </c>
-      <c r="D49" s="68">
+      <c r="D49" s="69">
         <f>IF(A49&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E49" s="68">
+      <c r="E49" s="69">
         <f>C49+D49</f>
         <v/>
       </c>
-      <c r="F49" s="85">
+      <c r="F49" s="86">
         <f>F48*(1+$B$41)+E49</f>
         <v/>
       </c>
-      <c r="G49" s="68">
+      <c r="G49" s="69">
         <f>G48+E49</f>
         <v/>
       </c>
-      <c r="H49" s="83">
+      <c r="H49" s="84">
         <f>IF(F49&gt;=$B$9,"◄ accelerated payback",IF(G49&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="55" t="n">
+      <c r="A50" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="B50" s="92">
+      <c r="B50" s="93">
         <f>$B$44+(A50-1)</f>
         <v/>
       </c>
-      <c r="C50" s="68">
+      <c r="C50" s="69">
         <f>$B$34*(1+$B$42)^(A50-1)</f>
         <v/>
       </c>
-      <c r="D50" s="68">
+      <c r="D50" s="69">
         <f>IF(A50&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E50" s="68">
+      <c r="E50" s="69">
         <f>C50+D50</f>
         <v/>
       </c>
-      <c r="F50" s="85">
+      <c r="F50" s="86">
         <f>F49*(1+$B$41)+E50</f>
         <v/>
       </c>
-      <c r="G50" s="68">
+      <c r="G50" s="69">
         <f>G49+E50</f>
         <v/>
       </c>
-      <c r="H50" s="83">
+      <c r="H50" s="84">
         <f>IF(F50&gt;=$B$9,"◄ accelerated payback",IF(G50&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="55" t="n">
+      <c r="A51" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="B51" s="92">
+      <c r="B51" s="93">
         <f>$B$44+(A51-1)</f>
         <v/>
       </c>
-      <c r="C51" s="68">
+      <c r="C51" s="69">
         <f>$B$34*(1+$B$42)^(A51-1)</f>
         <v/>
       </c>
-      <c r="D51" s="68">
+      <c r="D51" s="69">
         <f>IF(A51&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E51" s="68">
+      <c r="E51" s="69">
         <f>C51+D51</f>
         <v/>
       </c>
-      <c r="F51" s="85">
+      <c r="F51" s="86">
         <f>F50*(1+$B$41)+E51</f>
         <v/>
       </c>
-      <c r="G51" s="68">
+      <c r="G51" s="69">
         <f>G50+E51</f>
         <v/>
       </c>
-      <c r="H51" s="83">
+      <c r="H51" s="84">
         <f>IF(F51&gt;=$B$9,"◄ accelerated payback",IF(G51&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="55" t="n">
+      <c r="A52" s="56" t="n">
         <v>6</v>
       </c>
-      <c r="B52" s="92">
+      <c r="B52" s="93">
         <f>$B$44+(A52-1)</f>
         <v/>
       </c>
-      <c r="C52" s="68">
+      <c r="C52" s="69">
         <f>$B$34*(1+$B$42)^(A52-1)</f>
         <v/>
       </c>
-      <c r="D52" s="68">
+      <c r="D52" s="69">
         <f>IF(A52&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E52" s="68">
+      <c r="E52" s="69">
         <f>C52+D52</f>
         <v/>
       </c>
-      <c r="F52" s="85">
+      <c r="F52" s="86">
         <f>F51*(1+$B$41)+E52</f>
         <v/>
       </c>
-      <c r="G52" s="68">
+      <c r="G52" s="69">
         <f>G51+E52</f>
         <v/>
       </c>
-      <c r="H52" s="83">
+      <c r="H52" s="84">
         <f>IF(F52&gt;=$B$9,"◄ accelerated payback",IF(G52&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="55" t="n">
+      <c r="A53" s="56" t="n">
         <v>7</v>
       </c>
-      <c r="B53" s="92">
+      <c r="B53" s="93">
         <f>$B$44+(A53-1)</f>
         <v/>
       </c>
-      <c r="C53" s="68">
+      <c r="C53" s="69">
         <f>$B$34*(1+$B$42)^(A53-1)</f>
         <v/>
       </c>
-      <c r="D53" s="68">
+      <c r="D53" s="69">
         <f>IF(A53&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E53" s="68">
+      <c r="E53" s="69">
         <f>C53+D53</f>
         <v/>
       </c>
-      <c r="F53" s="85">
+      <c r="F53" s="86">
         <f>F52*(1+$B$41)+E53</f>
         <v/>
       </c>
-      <c r="G53" s="68">
+      <c r="G53" s="69">
         <f>G52+E53</f>
         <v/>
       </c>
-      <c r="H53" s="83">
+      <c r="H53" s="84">
         <f>IF(F53&gt;=$B$9,"◄ accelerated payback",IF(G53&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="55" t="n">
+      <c r="A54" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="B54" s="92">
+      <c r="B54" s="93">
         <f>$B$44+(A54-1)</f>
         <v/>
       </c>
-      <c r="C54" s="68">
+      <c r="C54" s="69">
         <f>$B$34*(1+$B$42)^(A54-1)</f>
         <v/>
       </c>
-      <c r="D54" s="68">
+      <c r="D54" s="69">
         <f>IF(A54&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E54" s="68">
+      <c r="E54" s="69">
         <f>C54+D54</f>
         <v/>
       </c>
-      <c r="F54" s="85">
+      <c r="F54" s="86">
         <f>F53*(1+$B$41)+E54</f>
         <v/>
       </c>
-      <c r="G54" s="68">
+      <c r="G54" s="69">
         <f>G53+E54</f>
         <v/>
       </c>
-      <c r="H54" s="83">
+      <c r="H54" s="84">
         <f>IF(F54&gt;=$B$9,"◄ accelerated payback",IF(G54&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="55" t="n">
+      <c r="A55" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="B55" s="92">
+      <c r="B55" s="93">
         <f>$B$44+(A55-1)</f>
         <v/>
       </c>
-      <c r="C55" s="68">
+      <c r="C55" s="69">
         <f>$B$34*(1+$B$42)^(A55-1)</f>
         <v/>
       </c>
-      <c r="D55" s="68">
+      <c r="D55" s="69">
         <f>IF(A55&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E55" s="68">
+      <c r="E55" s="69">
         <f>C55+D55</f>
         <v/>
       </c>
-      <c r="F55" s="85">
+      <c r="F55" s="86">
         <f>F54*(1+$B$41)+E55</f>
         <v/>
       </c>
-      <c r="G55" s="68">
+      <c r="G55" s="69">
         <f>G54+E55</f>
         <v/>
       </c>
-      <c r="H55" s="83">
+      <c r="H55" s="84">
         <f>IF(F55&gt;=$B$9,"◄ accelerated payback",IF(G55&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="55" t="n">
+      <c r="A56" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="B56" s="92">
+      <c r="B56" s="93">
         <f>$B$44+(A56-1)</f>
         <v/>
       </c>
-      <c r="C56" s="68">
+      <c r="C56" s="69">
         <f>$B$34*(1+$B$42)^(A56-1)</f>
         <v/>
       </c>
-      <c r="D56" s="68">
+      <c r="D56" s="69">
         <f>IF(A56&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E56" s="68">
+      <c r="E56" s="69">
         <f>C56+D56</f>
         <v/>
       </c>
-      <c r="F56" s="85">
+      <c r="F56" s="86">
         <f>F55*(1+$B$41)+E56</f>
         <v/>
       </c>
-      <c r="G56" s="68">
+      <c r="G56" s="69">
         <f>G55+E56</f>
         <v/>
       </c>
-      <c r="H56" s="83">
+      <c r="H56" s="84">
         <f>IF(F56&gt;=$B$9,"◄ accelerated payback",IF(G56&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="55" t="n">
+      <c r="A57" s="56" t="n">
         <v>11</v>
       </c>
-      <c r="B57" s="92">
+      <c r="B57" s="93">
         <f>$B$44+(A57-1)</f>
         <v/>
       </c>
-      <c r="C57" s="68">
+      <c r="C57" s="69">
         <f>$B$34*(1+$B$42)^(A57-1)</f>
         <v/>
       </c>
-      <c r="D57" s="68">
+      <c r="D57" s="69">
         <f>IF(A57&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E57" s="68">
+      <c r="E57" s="69">
         <f>C57+D57</f>
         <v/>
       </c>
-      <c r="F57" s="85">
+      <c r="F57" s="86">
         <f>F56*(1+$B$41)+E57</f>
         <v/>
       </c>
-      <c r="G57" s="68">
+      <c r="G57" s="69">
         <f>G56+E57</f>
         <v/>
       </c>
-      <c r="H57" s="83">
+      <c r="H57" s="84">
         <f>IF(F57&gt;=$B$9,"◄ accelerated payback",IF(G57&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="55" t="n">
+      <c r="A58" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="B58" s="92">
+      <c r="B58" s="93">
         <f>$B$44+(A58-1)</f>
         <v/>
       </c>
-      <c r="C58" s="68">
+      <c r="C58" s="69">
         <f>$B$34*(1+$B$42)^(A58-1)</f>
         <v/>
       </c>
-      <c r="D58" s="68">
+      <c r="D58" s="69">
         <f>IF(A58&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E58" s="68">
+      <c r="E58" s="69">
         <f>C58+D58</f>
         <v/>
       </c>
-      <c r="F58" s="85">
+      <c r="F58" s="86">
         <f>F57*(1+$B$41)+E58</f>
         <v/>
       </c>
-      <c r="G58" s="68">
+      <c r="G58" s="69">
         <f>G57+E58</f>
         <v/>
       </c>
-      <c r="H58" s="83">
+      <c r="H58" s="84">
         <f>IF(F58&gt;=$B$9,"◄ accelerated payback",IF(G58&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="55" t="n">
+      <c r="A59" s="56" t="n">
         <v>13</v>
       </c>
-      <c r="B59" s="92">
+      <c r="B59" s="93">
         <f>$B$44+(A59-1)</f>
         <v/>
       </c>
-      <c r="C59" s="68">
+      <c r="C59" s="69">
         <f>$B$34*(1+$B$42)^(A59-1)</f>
         <v/>
       </c>
-      <c r="D59" s="68">
+      <c r="D59" s="69">
         <f>IF(A59&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E59" s="68">
+      <c r="E59" s="69">
         <f>C59+D59</f>
         <v/>
       </c>
-      <c r="F59" s="85">
+      <c r="F59" s="86">
         <f>F58*(1+$B$41)+E59</f>
         <v/>
       </c>
-      <c r="G59" s="68">
+      <c r="G59" s="69">
         <f>G58+E59</f>
         <v/>
       </c>
-      <c r="H59" s="83">
+      <c r="H59" s="84">
         <f>IF(F59&gt;=$B$9,"◄ accelerated payback",IF(G59&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="55" t="n">
+      <c r="A60" s="56" t="n">
         <v>14</v>
       </c>
-      <c r="B60" s="92">
+      <c r="B60" s="93">
         <f>$B$44+(A60-1)</f>
         <v/>
       </c>
-      <c r="C60" s="68">
+      <c r="C60" s="69">
         <f>$B$34*(1+$B$42)^(A60-1)</f>
         <v/>
       </c>
-      <c r="D60" s="68">
+      <c r="D60" s="69">
         <f>IF(A60&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E60" s="68">
+      <c r="E60" s="69">
         <f>C60+D60</f>
         <v/>
       </c>
-      <c r="F60" s="85">
+      <c r="F60" s="86">
         <f>F59*(1+$B$41)+E60</f>
         <v/>
       </c>
-      <c r="G60" s="68">
+      <c r="G60" s="69">
         <f>G59+E60</f>
         <v/>
       </c>
-      <c r="H60" s="83">
+      <c r="H60" s="84">
         <f>IF(F60&gt;=$B$9,"◄ accelerated payback",IF(G60&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="55" t="n">
+      <c r="A61" s="56" t="n">
         <v>15</v>
       </c>
-      <c r="B61" s="92">
+      <c r="B61" s="93">
         <f>$B$44+(A61-1)</f>
         <v/>
       </c>
-      <c r="C61" s="68">
+      <c r="C61" s="69">
         <f>$B$34*(1+$B$42)^(A61-1)</f>
         <v/>
       </c>
-      <c r="D61" s="68">
+      <c r="D61" s="69">
         <f>IF(A61&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E61" s="68">
+      <c r="E61" s="69">
         <f>C61+D61</f>
         <v/>
       </c>
-      <c r="F61" s="85">
+      <c r="F61" s="86">
         <f>F60*(1+$B$41)+E61</f>
         <v/>
       </c>
-      <c r="G61" s="68">
+      <c r="G61" s="69">
         <f>G60+E61</f>
         <v/>
       </c>
-      <c r="H61" s="83">
+      <c r="H61" s="84">
         <f>IF(F61&gt;=$B$9,"◄ accelerated payback",IF(G61&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="55" t="n">
+      <c r="A62" s="56" t="n">
         <v>16</v>
       </c>
-      <c r="B62" s="92">
+      <c r="B62" s="93">
         <f>$B$44+(A62-1)</f>
         <v/>
       </c>
-      <c r="C62" s="68">
+      <c r="C62" s="69">
         <f>$B$34*(1+$B$42)^(A62-1)</f>
         <v/>
       </c>
-      <c r="D62" s="68">
+      <c r="D62" s="69">
         <f>IF(A62&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E62" s="68">
+      <c r="E62" s="69">
         <f>C62+D62</f>
         <v/>
       </c>
-      <c r="F62" s="85">
+      <c r="F62" s="86">
         <f>F61*(1+$B$41)+E62</f>
         <v/>
       </c>
-      <c r="G62" s="68">
+      <c r="G62" s="69">
         <f>G61+E62</f>
         <v/>
       </c>
-      <c r="H62" s="83">
+      <c r="H62" s="84">
         <f>IF(F62&gt;=$B$9,"◄ accelerated payback",IF(G62&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="55" t="n">
+      <c r="A63" s="56" t="n">
         <v>17</v>
       </c>
-      <c r="B63" s="92">
+      <c r="B63" s="93">
         <f>$B$44+(A63-1)</f>
         <v/>
       </c>
-      <c r="C63" s="68">
+      <c r="C63" s="69">
         <f>$B$34*(1+$B$42)^(A63-1)</f>
         <v/>
       </c>
-      <c r="D63" s="68">
+      <c r="D63" s="69">
         <f>IF(A63&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E63" s="68">
+      <c r="E63" s="69">
         <f>C63+D63</f>
         <v/>
       </c>
-      <c r="F63" s="85">
+      <c r="F63" s="86">
         <f>F62*(1+$B$41)+E63</f>
         <v/>
       </c>
-      <c r="G63" s="68">
+      <c r="G63" s="69">
         <f>G62+E63</f>
         <v/>
       </c>
-      <c r="H63" s="83">
+      <c r="H63" s="84">
         <f>IF(F63&gt;=$B$9,"◄ accelerated payback",IF(G63&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="55" t="n">
+      <c r="A64" s="56" t="n">
         <v>18</v>
       </c>
-      <c r="B64" s="92">
+      <c r="B64" s="93">
         <f>$B$44+(A64-1)</f>
         <v/>
       </c>
-      <c r="C64" s="68">
+      <c r="C64" s="69">
         <f>$B$34*(1+$B$42)^(A64-1)</f>
         <v/>
       </c>
-      <c r="D64" s="68">
+      <c r="D64" s="69">
         <f>IF(A64&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E64" s="68">
+      <c r="E64" s="69">
         <f>C64+D64</f>
         <v/>
       </c>
-      <c r="F64" s="85">
+      <c r="F64" s="86">
         <f>F63*(1+$B$41)+E64</f>
         <v/>
       </c>
-      <c r="G64" s="68">
+      <c r="G64" s="69">
         <f>G63+E64</f>
         <v/>
       </c>
-      <c r="H64" s="83">
+      <c r="H64" s="84">
         <f>IF(F64&gt;=$B$9,"◄ accelerated payback",IF(G64&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="55" t="n">
+      <c r="A65" s="56" t="n">
         <v>19</v>
       </c>
-      <c r="B65" s="92">
+      <c r="B65" s="93">
         <f>$B$44+(A65-1)</f>
         <v/>
       </c>
-      <c r="C65" s="68">
+      <c r="C65" s="69">
         <f>$B$34*(1+$B$42)^(A65-1)</f>
         <v/>
       </c>
-      <c r="D65" s="68">
+      <c r="D65" s="69">
         <f>IF(A65&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E65" s="68">
+      <c r="E65" s="69">
         <f>C65+D65</f>
         <v/>
       </c>
-      <c r="F65" s="85">
+      <c r="F65" s="86">
         <f>F64*(1+$B$41)+E65</f>
         <v/>
       </c>
-      <c r="G65" s="68">
+      <c r="G65" s="69">
         <f>G64+E65</f>
         <v/>
       </c>
-      <c r="H65" s="83">
+      <c r="H65" s="84">
         <f>IF(F65&gt;=$B$9,"◄ accelerated payback",IF(G65&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="55" t="n">
+      <c r="A66" s="56" t="n">
         <v>20</v>
       </c>
-      <c r="B66" s="92">
+      <c r="B66" s="93">
         <f>$B$44+(A66-1)</f>
         <v/>
       </c>
-      <c r="C66" s="68">
+      <c r="C66" s="69">
         <f>$B$34*(1+$B$42)^(A66-1)</f>
         <v/>
       </c>
-      <c r="D66" s="68">
+      <c r="D66" s="69">
         <f>IF(A66&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E66" s="68">
+      <c r="E66" s="69">
         <f>C66+D66</f>
         <v/>
       </c>
-      <c r="F66" s="85">
+      <c r="F66" s="86">
         <f>F65*(1+$B$41)+E66</f>
         <v/>
       </c>
-      <c r="G66" s="68">
+      <c r="G66" s="69">
         <f>G65+E66</f>
         <v/>
       </c>
-      <c r="H66" s="83">
+      <c r="H66" s="84">
         <f>IF(F66&gt;=$B$9,"◄ accelerated payback",IF(G66&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="55" t="n">
+      <c r="A67" s="56" t="n">
         <v>21</v>
       </c>
-      <c r="B67" s="92">
+      <c r="B67" s="93">
         <f>$B$44+(A67-1)</f>
         <v/>
       </c>
-      <c r="C67" s="68">
+      <c r="C67" s="69">
         <f>$B$34*(1+$B$42)^(A67-1)</f>
         <v/>
       </c>
-      <c r="D67" s="68">
+      <c r="D67" s="69">
         <f>IF(A67&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E67" s="68">
+      <c r="E67" s="69">
         <f>C67+D67</f>
         <v/>
       </c>
-      <c r="F67" s="85">
+      <c r="F67" s="86">
         <f>F66*(1+$B$41)+E67</f>
         <v/>
       </c>
-      <c r="G67" s="68">
+      <c r="G67" s="69">
         <f>G66+E67</f>
         <v/>
       </c>
-      <c r="H67" s="83">
+      <c r="H67" s="84">
         <f>IF(F67&gt;=$B$9,"◄ accelerated payback",IF(G67&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="55" t="n">
+      <c r="A68" s="56" t="n">
         <v>22</v>
       </c>
-      <c r="B68" s="92">
+      <c r="B68" s="93">
         <f>$B$44+(A68-1)</f>
         <v/>
       </c>
-      <c r="C68" s="68">
+      <c r="C68" s="69">
         <f>$B$34*(1+$B$42)^(A68-1)</f>
         <v/>
       </c>
-      <c r="D68" s="68">
+      <c r="D68" s="69">
         <f>IF(A68&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E68" s="68">
+      <c r="E68" s="69">
         <f>C68+D68</f>
         <v/>
       </c>
-      <c r="F68" s="85">
+      <c r="F68" s="86">
         <f>F67*(1+$B$41)+E68</f>
         <v/>
       </c>
-      <c r="G68" s="68">
+      <c r="G68" s="69">
         <f>G67+E68</f>
         <v/>
       </c>
-      <c r="H68" s="83">
+      <c r="H68" s="84">
         <f>IF(F68&gt;=$B$9,"◄ accelerated payback",IF(G68&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="55" t="n">
+      <c r="A69" s="56" t="n">
         <v>23</v>
       </c>
-      <c r="B69" s="92">
+      <c r="B69" s="93">
         <f>$B$44+(A69-1)</f>
         <v/>
       </c>
-      <c r="C69" s="68">
+      <c r="C69" s="69">
         <f>$B$34*(1+$B$42)^(A69-1)</f>
         <v/>
       </c>
-      <c r="D69" s="68">
+      <c r="D69" s="69">
         <f>IF(A69&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E69" s="68">
+      <c r="E69" s="69">
         <f>C69+D69</f>
         <v/>
       </c>
-      <c r="F69" s="85">
+      <c r="F69" s="86">
         <f>F68*(1+$B$41)+E69</f>
         <v/>
       </c>
-      <c r="G69" s="68">
+      <c r="G69" s="69">
         <f>G68+E69</f>
         <v/>
       </c>
-      <c r="H69" s="83">
+      <c r="H69" s="84">
         <f>IF(F69&gt;=$B$9,"◄ accelerated payback",IF(G69&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="55" t="n">
+      <c r="A70" s="56" t="n">
         <v>24</v>
       </c>
-      <c r="B70" s="92">
+      <c r="B70" s="93">
         <f>$B$44+(A70-1)</f>
         <v/>
       </c>
-      <c r="C70" s="68">
+      <c r="C70" s="69">
         <f>$B$34*(1+$B$42)^(A70-1)</f>
         <v/>
       </c>
-      <c r="D70" s="68">
+      <c r="D70" s="69">
         <f>IF(A70&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E70" s="68">
+      <c r="E70" s="69">
         <f>C70+D70</f>
         <v/>
       </c>
-      <c r="F70" s="85">
+      <c r="F70" s="86">
         <f>F69*(1+$B$41)+E70</f>
         <v/>
       </c>
-      <c r="G70" s="68">
+      <c r="G70" s="69">
         <f>G69+E70</f>
         <v/>
       </c>
-      <c r="H70" s="83">
+      <c r="H70" s="84">
         <f>IF(F70&gt;=$B$9,"◄ accelerated payback",IF(G70&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="55" t="n">
+      <c r="A71" s="56" t="n">
         <v>25</v>
       </c>
-      <c r="B71" s="92">
+      <c r="B71" s="93">
         <f>$B$44+(A71-1)</f>
         <v/>
       </c>
-      <c r="C71" s="68">
+      <c r="C71" s="69">
         <f>$B$34*(1+$B$42)^(A71-1)</f>
         <v/>
       </c>
-      <c r="D71" s="68">
+      <c r="D71" s="69">
         <f>IF(A71&lt;=10,$B$37,0)</f>
         <v/>
       </c>
-      <c r="E71" s="68">
+      <c r="E71" s="69">
         <f>C71+D71</f>
         <v/>
       </c>
-      <c r="F71" s="85">
+      <c r="F71" s="86">
         <f>F70*(1+$B$41)+E71</f>
         <v/>
       </c>
-      <c r="G71" s="68">
+      <c r="G71" s="69">
         <f>G70+E71</f>
         <v/>
       </c>
-      <c r="H71" s="83">
+      <c r="H71" s="84">
         <f>IF(F71&gt;=$B$9,"◄ accelerated payback",IF(G71&gt;=$B$9,"simple payback",""))</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="63" t="inlineStr">
+      <c r="A73" s="64" t="inlineStr">
         <is>
           <t>Simple payback (year #):</t>
         </is>
       </c>
-      <c r="C73" s="69">
+      <c r="C73" s="70">
         <f>IFERROR(INDEX(A47:A71,MATCH(TRUE,INDEX(G47:G71&gt;=$B$9,0),0)),"&gt;25")</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="63" t="inlineStr">
+      <c r="A74" s="64" t="inlineStr">
         <is>
           <t>Accelerated payback (year #):</t>
         </is>
       </c>
-      <c r="C74" s="69">
+      <c r="C74" s="70">
         <f>IFERROR(INDEX(A47:A71,MATCH(TRUE,INDEX(F47:F71&gt;=$B$9,0),0)),"&gt;25")</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="63" t="inlineStr">
+      <c r="A75" s="64" t="inlineStr">
         <is>
           <t>Reinvested value at horizon:</t>
         </is>
       </c>
-      <c r="C75" s="64">
+      <c r="C75" s="65">
         <f>INDEX(F47:F71,MATCH($B$43,A47:A71,0))</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="63" t="inlineStr">
+      <c r="A76" s="64" t="inlineStr">
         <is>
           <t>Net gain (value − net capital):</t>
         </is>
       </c>
-      <c r="C76" s="64">
+      <c r="C76" s="65">
         <f>C75-B9</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="41" t="inlineStr">
+      <c r="A78" s="42" t="inlineStr">
         <is>
           <t>Takeaway: 'Simple payback' is when avoided bills alone repay the system. 'Accelerated payback' is when those same dollars — invested at your return — repay it. The gap between them, and the horizon value above, is the compounding you unlock by reinvesting instead of just banking lower bills. Add the monthly avoided cost (B33) to the FIRE Dashboard contributions to fold it into your savings rate.</t>
         </is>
@@ -18107,27 +18108,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>HSA Election Planner — November open enrollment</t>
         </is>
       </c>
     </row>
     <row r="2" ht="34" customHeight="1" s="39">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>Turns your freed-up cash (solar + mobile + old FSA) into a concrete HSA election for the 2027 plan year. ORANGE = inputs. Educational planning, not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>① 2027 HSA LIMIT</t>
         </is>
       </c>
-      <c r="B4" s="45" t="n"/>
-      <c r="C4" s="45" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18135,7 +18136,7 @@
           <t>Coverage type</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
@@ -18147,10 +18148,10 @@
           <t>2027 HSA limit (family)</t>
         </is>
       </c>
-      <c r="B6" s="73" t="n">
+      <c r="B6" s="74" t="n">
         <v>9000</v>
       </c>
-      <c r="C6" s="47" t="inlineStr">
+      <c r="C6" s="48" t="inlineStr">
         <is>
           <t>Self-only 2027 = $4,500. Family = $9,000.</t>
         </is>
@@ -18162,10 +18163,10 @@
           <t>Catch-up (age 55+, each)</t>
         </is>
       </c>
-      <c r="B7" s="73" t="n">
+      <c r="B7" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="47" t="inlineStr">
+      <c r="C7" s="48" t="inlineStr">
         <is>
           <t>You're 45 — the +$1,000 each starts in 2036.</t>
         </is>
@@ -18177,22 +18178,22 @@
           <t>Employer HSA seed/contribution</t>
         </is>
       </c>
-      <c r="B8" s="50" t="n">
+      <c r="B8" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="47" t="inlineStr">
+      <c r="C8" s="48" t="inlineStr">
         <is>
           <t>If MathWorks seeds the HSA, it counts against the limit — enter it.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>Your max employee election</t>
         </is>
       </c>
-      <c r="B9" s="64">
+      <c r="B9" s="65">
         <f>B6+B7-B8</f>
         <v/>
       </c>
@@ -18203,10 +18204,10 @@
           <t>Pay periods / year</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="50" t="n">
         <v>26</v>
       </c>
-      <c r="C10" s="47" t="inlineStr">
+      <c r="C10" s="48" t="inlineStr">
         <is>
           <t>MathWorks is biweekly = 26.</t>
         </is>
@@ -18218,19 +18219,19 @@
           <t>Max per paycheck</t>
         </is>
       </c>
-      <c r="B11" s="73">
+      <c r="B11" s="74">
         <f>B9/B10</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="44" t="inlineStr">
+      <c r="A13" s="45" t="inlineStr">
         <is>
           <t>② FREED-UP CASH TO REDIRECT  (annual)</t>
         </is>
       </c>
-      <c r="B13" s="45" t="n"/>
-      <c r="C13" s="45" t="n"/>
+      <c r="B13" s="46" t="n"/>
+      <c r="C13" s="46" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18238,7 +18239,7 @@
           <t>Solar avoided cost (from Solar tab)</t>
         </is>
       </c>
-      <c r="B14" s="73">
+      <c r="B14" s="74">
         <f>'Solar Reinvestment'!B34</f>
         <v/>
       </c>
@@ -18249,10 +18250,10 @@
           <t>Mobile / phone savings</t>
         </is>
       </c>
-      <c r="B15" s="50" t="n">
+      <c r="B15" s="51" t="n">
         <v>600</v>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="48" t="inlineStr">
         <is>
           <t>From switching to the cheaper carrier.</t>
         </is>
@@ -18264,10 +18265,10 @@
           <t>Former FSA Health Care contribution</t>
         </is>
       </c>
-      <c r="B16" s="50" t="n">
+      <c r="B16" s="51" t="n">
         <v>2500</v>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="48" t="inlineStr">
         <is>
           <t>What you were putting in the FSA (~$96/pay × 26). This moves to the HSA.</t>
         </is>
@@ -18279,29 +18280,29 @@
           <t>Other freed cash</t>
         </is>
       </c>
-      <c r="B17" s="50" t="n">
+      <c r="B17" s="51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="63" t="inlineStr">
+      <c r="A18" s="64" t="inlineStr">
         <is>
           <t>TOTAL new annual money</t>
         </is>
       </c>
-      <c r="B18" s="64">
+      <c r="B18" s="65">
         <f>SUM(B14:B17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="44" t="inlineStr">
+      <c r="A20" s="45" t="inlineStr">
         <is>
           <t>③ ELECTION PLAN</t>
         </is>
       </c>
-      <c r="B20" s="45" t="n"/>
-      <c r="C20" s="45" t="n"/>
+      <c r="B20" s="46" t="n"/>
+      <c r="C20" s="46" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -18309,11 +18310,11 @@
           <t>Suggested election (fund HSA from freed cash)</t>
         </is>
       </c>
-      <c r="B21" s="73">
+      <c r="B21" s="74">
         <f>MIN(B9,B18)</f>
         <v/>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C21" s="48" t="inlineStr">
         <is>
           <t>Fund the more tax-efficient HSA first, up to the limit.</t>
         </is>
@@ -18325,23 +18326,23 @@
           <t>Your chosen HSA election</t>
         </is>
       </c>
-      <c r="B22" s="50">
+      <c r="B22" s="51">
         <f>B21</f>
         <v/>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C22" s="48" t="inlineStr">
         <is>
           <t>Override with the number you actually elect.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="63" t="inlineStr">
+      <c r="A23" s="64" t="inlineStr">
         <is>
           <t>→ Per paycheck</t>
         </is>
       </c>
-      <c r="B23" s="64">
+      <c r="B23" s="65">
         <f>B22/B10</f>
         <v/>
       </c>
@@ -18352,7 +18353,7 @@
           <t>→ % of family limit used</t>
         </is>
       </c>
-      <c r="B24" s="93">
+      <c r="B24" s="94">
         <f>B22/B6</f>
         <v/>
       </c>
@@ -18363,7 +18364,7 @@
           <t>Remaining freed cash → IRAs</t>
         </is>
       </c>
-      <c r="B25" s="73">
+      <c r="B25" s="74">
         <f>MAX(0,B18-B22)</f>
         <v/>
       </c>
@@ -18374,55 +18375,55 @@
           <t>Extra needed to hit $9,000 max</t>
         </is>
       </c>
-      <c r="B26" s="73">
+      <c r="B26" s="74">
         <f>MAX(0,B9-B18)</f>
         <v/>
       </c>
-      <c r="C26" s="47" t="inlineStr">
+      <c r="C26" s="48" t="inlineStr">
         <is>
           <t>Shortfall between freed cash and a full max — pull from elsewhere if you want to top out.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="44" t="inlineStr">
+      <c r="A28" s="45" t="inlineStr">
         <is>
           <t>④ DECISION NOTES  (from our planning)</t>
         </is>
       </c>
-      <c r="B28" s="45" t="n"/>
-      <c r="C28" s="45" t="n"/>
+      <c r="B28" s="46" t="n"/>
+      <c r="C28" s="46" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1" s="39">
-      <c r="A29" s="41" t="inlineStr">
+      <c r="A29" s="42" t="inlineStr">
         <is>
           <t>• HSA is the most tax-efficient bucket (triple advantage + the payroll-tax break) — fund it first from freed cash, then overflow to IRAs.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" s="39">
-      <c r="A30" s="41" t="inlineStr">
+      <c r="A30" s="42" t="inlineStr">
         <is>
           <t>• Orthodontia: pay out of pocket, save every receipt, let the HSA stay invested and reimburse yourself later (the 'shoebox' growth play).</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" s="39">
-      <c r="A31" s="41" t="inlineStr">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>• Open + fund the HSA (even $1) BEFORE the first ortho expense — expenses incurred before the account exists can never be reimbursed.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" s="39">
-      <c r="A32" s="41" t="inlineStr">
+      <c r="A32" s="42" t="inlineStr">
         <is>
           <t>• Confirm your 2026 FSA has no carryover/grace period bleeding into 2027 — it can block HSA eligibility early in the year. Consider a limited-purpose (dental/vision) FSA.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" s="39">
-      <c r="A33" s="41" t="inlineStr">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>• 2027 IRA limit isn't official yet (~$7,500 each expected); confirm in November before finalizing the IRA split.</t>
         </is>
@@ -18457,31 +18458,31 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>Monthly Entry — one place to update everything</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1" s="39">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>Pick the month, fill in what you have (blanks are skipped), then run 📊 Family Finances → Post Monthly Entry. Values fan out to Balances, Solar, Amazon Reconciliation and Comp &amp; Benefits. You can also fill this from your phone via the linked Google Form.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="63" t="inlineStr">
+      <c r="A4" s="64" t="inlineStr">
         <is>
           <t>Month to post</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>Choose the month these figures belong to.</t>
         </is>
@@ -18493,21 +18494,21 @@
           <t>Data as of (date)</t>
         </is>
       </c>
-      <c r="B5" s="94" t="n"/>
-      <c r="C5" s="47" t="inlineStr">
+      <c r="B5" s="95" t="n"/>
+      <c r="C5" s="48" t="inlineStr">
         <is>
           <t>Optional — for your records.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>① ACCOUNT BALANCES  (month-end)</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n"/>
-      <c r="C6" s="45" t="n"/>
+      <c r="B6" s="46" t="n"/>
+      <c r="C6" s="46" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18515,8 +18516,8 @@
           <t>Capital One Checking</t>
         </is>
       </c>
-      <c r="B7" s="50" t="n"/>
-      <c r="C7" s="47" t="inlineStr">
+      <c r="B7" s="51" t="n"/>
+      <c r="C7" s="48" t="inlineStr">
         <is>
           <t>→ Balances</t>
         </is>
@@ -18528,8 +18529,8 @@
           <t>Capital One Savings</t>
         </is>
       </c>
-      <c r="B8" s="50" t="n"/>
-      <c r="C8" s="47" t="inlineStr"/>
+      <c r="B8" s="51" t="n"/>
+      <c r="C8" s="48" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18537,8 +18538,8 @@
           <t>Venmo float</t>
         </is>
       </c>
-      <c r="B9" s="50" t="n"/>
-      <c r="C9" s="47" t="inlineStr"/>
+      <c r="B9" s="51" t="n"/>
+      <c r="C9" s="48" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18546,8 +18547,8 @@
           <t>Fidelity Money Market</t>
         </is>
       </c>
-      <c r="B10" s="50" t="n"/>
-      <c r="C10" s="47" t="inlineStr"/>
+      <c r="B10" s="51" t="n"/>
+      <c r="C10" s="48" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18555,8 +18556,8 @@
           <t>Schwab investment</t>
         </is>
       </c>
-      <c r="B11" s="50" t="n"/>
-      <c r="C11" s="47" t="inlineStr"/>
+      <c r="B11" s="51" t="n"/>
+      <c r="C11" s="48" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18564,8 +18565,8 @@
           <t>529</t>
         </is>
       </c>
-      <c r="B12" s="50" t="n"/>
-      <c r="C12" s="47" t="inlineStr"/>
+      <c r="B12" s="51" t="n"/>
+      <c r="C12" s="48" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18573,8 +18574,8 @@
           <t>FSA Dep Care balance</t>
         </is>
       </c>
-      <c r="B13" s="50" t="n"/>
-      <c r="C13" s="47" t="inlineStr"/>
+      <c r="B13" s="51" t="n"/>
+      <c r="C13" s="48" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18582,8 +18583,8 @@
           <t>FSA Health Care balance</t>
         </is>
       </c>
-      <c r="B14" s="50" t="n"/>
-      <c r="C14" s="47" t="inlineStr"/>
+      <c r="B14" s="51" t="n"/>
+      <c r="C14" s="48" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18591,8 +18592,8 @@
           <t>Matt 401k</t>
         </is>
       </c>
-      <c r="B15" s="50" t="n"/>
-      <c r="C15" s="47" t="inlineStr"/>
+      <c r="B15" s="51" t="n"/>
+      <c r="C15" s="48" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18600,8 +18601,8 @@
           <t>Sue 403b</t>
         </is>
       </c>
-      <c r="B16" s="50" t="n"/>
-      <c r="C16" s="47" t="inlineStr"/>
+      <c r="B16" s="51" t="n"/>
+      <c r="C16" s="48" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18609,8 +18610,8 @@
           <t>Sue pension (est.)</t>
         </is>
       </c>
-      <c r="B17" s="50" t="n"/>
-      <c r="C17" s="47" t="inlineStr"/>
+      <c r="B17" s="51" t="n"/>
+      <c r="C17" s="48" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18618,17 +18619,17 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="B18" s="50" t="n"/>
-      <c r="C18" s="47" t="inlineStr"/>
+      <c r="B18" s="51" t="n"/>
+      <c r="C18" s="48" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="44" t="inlineStr">
+      <c r="A20" s="45" t="inlineStr">
         <is>
           <t>② SOLAR — ENERGY  (Enphase, kWh)</t>
         </is>
       </c>
-      <c r="B20" s="45" t="n"/>
-      <c r="C20" s="45" t="n"/>
+      <c r="B20" s="46" t="n"/>
+      <c r="C20" s="46" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -18636,8 +18637,8 @@
           <t>Produced (kWh)</t>
         </is>
       </c>
-      <c r="B21" s="91" t="n"/>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="B21" s="92" t="n"/>
+      <c r="C21" s="48" t="inlineStr">
         <is>
           <t>→ Solar Reinvestment log</t>
         </is>
@@ -18649,8 +18650,8 @@
           <t>Consumed (kWh)</t>
         </is>
       </c>
-      <c r="B22" s="91" t="n"/>
-      <c r="C22" s="47" t="inlineStr"/>
+      <c r="B22" s="92" t="n"/>
+      <c r="C22" s="48" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18658,8 +18659,8 @@
           <t>Imported (kWh)</t>
         </is>
       </c>
-      <c r="B23" s="91" t="n"/>
-      <c r="C23" s="47" t="inlineStr"/>
+      <c r="B23" s="92" t="n"/>
+      <c r="C23" s="48" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -18667,17 +18668,17 @@
           <t>Exported (kWh)</t>
         </is>
       </c>
-      <c r="B24" s="91" t="n"/>
-      <c r="C24" s="47" t="inlineStr"/>
+      <c r="B24" s="92" t="n"/>
+      <c r="C24" s="48" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="44" t="inlineStr">
+      <c r="A25" s="45" t="inlineStr">
         <is>
           <t>③ SOLAR — ELECTRIC BILL</t>
         </is>
       </c>
-      <c r="B25" s="45" t="n"/>
-      <c r="C25" s="45" t="n"/>
+      <c r="B25" s="46" t="n"/>
+      <c r="C25" s="46" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -18685,8 +18686,8 @@
           <t>Baseline electric (would-have-paid)</t>
         </is>
       </c>
-      <c r="B26" s="50" t="n"/>
-      <c r="C26" s="47" t="inlineStr">
+      <c r="B26" s="51" t="n"/>
+      <c r="C26" s="48" t="inlineStr">
         <is>
           <t>→ Solar ROI row 9</t>
         </is>
@@ -18698,21 +18699,21 @@
           <t>Actual electric bill</t>
         </is>
       </c>
-      <c r="B27" s="50" t="n"/>
-      <c r="C27" s="47" t="inlineStr">
+      <c r="B27" s="51" t="n"/>
+      <c r="C27" s="48" t="inlineStr">
         <is>
           <t>→ Solar ROI row 10</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="44" t="inlineStr">
+      <c r="A29" s="45" t="inlineStr">
         <is>
           <t>④ AMAZON — split this month's total into buckets</t>
         </is>
       </c>
-      <c r="B29" s="45" t="n"/>
-      <c r="C29" s="45" t="n"/>
+      <c r="B29" s="46" t="n"/>
+      <c r="C29" s="46" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -18720,11 +18721,11 @@
           <t>Amazon total to split (auto)</t>
         </is>
       </c>
-      <c r="B30" s="73">
+      <c r="B30" s="74">
         <f>IFERROR(INDEX('CC Detail'!B14:M14,MATCH($B$4,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0)),"")</f>
         <v/>
       </c>
-      <c r="C30" s="47" t="inlineStr">
+      <c r="C30" s="48" t="inlineStr">
         <is>
           <t>Pulled from CC Detail for the chosen month — split it below.</t>
         </is>
@@ -18736,8 +18737,8 @@
           <t>Groceries</t>
         </is>
       </c>
-      <c r="B31" s="50" t="n"/>
-      <c r="C31" s="47" t="inlineStr">
+      <c r="B31" s="51" t="n"/>
+      <c r="C31" s="48" t="inlineStr">
         <is>
           <t>→ Amazon Reconciliation</t>
         </is>
@@ -18749,8 +18750,8 @@
           <t>Kids / Activities</t>
         </is>
       </c>
-      <c r="B32" s="50" t="n"/>
-      <c r="C32" s="47" t="inlineStr"/>
+      <c r="B32" s="51" t="n"/>
+      <c r="C32" s="48" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -18758,8 +18759,8 @@
           <t>Personal Care</t>
         </is>
       </c>
-      <c r="B33" s="50" t="n"/>
-      <c r="C33" s="47" t="inlineStr"/>
+      <c r="B33" s="51" t="n"/>
+      <c r="C33" s="48" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -18767,8 +18768,8 @@
           <t>Pharmacy / Health</t>
         </is>
       </c>
-      <c r="B34" s="50" t="n"/>
-      <c r="C34" s="47" t="inlineStr"/>
+      <c r="B34" s="51" t="n"/>
+      <c r="C34" s="48" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -18776,8 +18777,8 @@
           <t>Home / Hardware</t>
         </is>
       </c>
-      <c r="B35" s="50" t="n"/>
-      <c r="C35" s="47" t="inlineStr"/>
+      <c r="B35" s="51" t="n"/>
+      <c r="C35" s="48" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -18785,8 +18786,8 @@
           <t>Subscriptions</t>
         </is>
       </c>
-      <c r="B36" s="50" t="n"/>
-      <c r="C36" s="47" t="inlineStr"/>
+      <c r="B36" s="51" t="n"/>
+      <c r="C36" s="48" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -18794,8 +18795,8 @@
           <t>Other / gifts</t>
         </is>
       </c>
-      <c r="B37" s="50" t="n"/>
-      <c r="C37" s="47" t="inlineStr"/>
+      <c r="B37" s="51" t="n"/>
+      <c r="C37" s="48" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -18803,24 +18804,24 @@
           <t>Split check (should match total)</t>
         </is>
       </c>
-      <c r="B38" s="73">
+      <c r="B38" s="74">
         <f>SUM(B31:B37)</f>
         <v/>
       </c>
-      <c r="C38" s="47" t="inlineStr">
+      <c r="C38" s="48" t="inlineStr">
         <is>
           <t>Compare to Amazon total above.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="44" t="inlineStr">
+      <c r="A40" s="45" t="inlineStr">
         <is>
           <t>⑤ COMP &amp; BENEFITS  (YTD, from paystub)</t>
         </is>
       </c>
-      <c r="B40" s="45" t="n"/>
-      <c r="C40" s="45" t="n"/>
+      <c r="B40" s="46" t="n"/>
+      <c r="C40" s="46" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -18828,8 +18829,8 @@
           <t>Matt gross earnings YTD</t>
         </is>
       </c>
-      <c r="B41" s="50" t="n"/>
-      <c r="C41" s="47" t="inlineStr">
+      <c r="B41" s="51" t="n"/>
+      <c r="C41" s="48" t="inlineStr">
         <is>
           <t>→ Comp &amp; Benefits</t>
         </is>
@@ -18841,8 +18842,8 @@
           <t>Matt 401k contribution YTD</t>
         </is>
       </c>
-      <c r="B42" s="50" t="n"/>
-      <c r="C42" s="47" t="inlineStr"/>
+      <c r="B42" s="51" t="n"/>
+      <c r="C42" s="48" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -18850,8 +18851,8 @@
           <t>Matt 401k match YTD</t>
         </is>
       </c>
-      <c r="B43" s="50" t="n"/>
-      <c r="C43" s="47" t="inlineStr"/>
+      <c r="B43" s="51" t="n"/>
+      <c r="C43" s="48" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -18859,8 +18860,8 @@
           <t>FSA Dep Care YTD</t>
         </is>
       </c>
-      <c r="B44" s="50" t="n"/>
-      <c r="C44" s="47" t="inlineStr"/>
+      <c r="B44" s="51" t="n"/>
+      <c r="C44" s="48" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -18868,8 +18869,8 @@
           <t>FSA Health Care YTD</t>
         </is>
       </c>
-      <c r="B45" s="50" t="n"/>
-      <c r="C45" s="47" t="inlineStr"/>
+      <c r="B45" s="51" t="n"/>
+      <c r="C45" s="48" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -18877,8 +18878,8 @@
           <t>Tuition reimbursement YTD</t>
         </is>
       </c>
-      <c r="B46" s="50" t="n"/>
-      <c r="C46" s="47" t="inlineStr"/>
+      <c r="B46" s="51" t="n"/>
+      <c r="C46" s="48" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -18886,8 +18887,8 @@
           <t>Stakeholder earnings YTD</t>
         </is>
       </c>
-      <c r="B47" s="50" t="n"/>
-      <c r="C47" s="47" t="inlineStr"/>
+      <c r="B47" s="51" t="n"/>
+      <c r="C47" s="48" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -18895,8 +18896,8 @@
           <t>Sue 403b YTD</t>
         </is>
       </c>
-      <c r="B48" s="50" t="n"/>
-      <c r="C48" s="47" t="inlineStr"/>
+      <c r="B48" s="51" t="n"/>
+      <c r="C48" s="48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -18904,17 +18905,17 @@
           <t>529 contributions YTD</t>
         </is>
       </c>
-      <c r="B49" s="50" t="n"/>
-      <c r="C49" s="47" t="inlineStr"/>
+      <c r="B49" s="51" t="n"/>
+      <c r="C49" s="48" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="44" t="inlineStr">
+      <c r="A51" s="45" t="inlineStr">
         <is>
           <t>⑥ DISCRETIONARY SPENT  (this month)</t>
         </is>
       </c>
-      <c r="B51" s="45" t="n"/>
-      <c r="C51" s="45" t="n"/>
+      <c r="B51" s="46" t="n"/>
+      <c r="C51" s="46" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -18922,8 +18923,8 @@
           <t>Matt discretionary spent</t>
         </is>
       </c>
-      <c r="B52" s="50" t="n"/>
-      <c r="C52" s="47" t="inlineStr">
+      <c r="B52" s="51" t="n"/>
+      <c r="C52" s="48" t="inlineStr">
         <is>
           <t>→ Spending Guardrail</t>
         </is>
@@ -18935,8 +18936,8 @@
           <t>Sue discretionary spent</t>
         </is>
       </c>
-      <c r="B53" s="50" t="n"/>
-      <c r="C53" s="47" t="inlineStr"/>
+      <c r="B53" s="51" t="n"/>
+      <c r="C53" s="48" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -18944,11 +18945,11 @@
           <t>Household discretionary spent</t>
         </is>
       </c>
-      <c r="B54" s="50" t="n"/>
-      <c r="C54" s="47" t="inlineStr"/>
+      <c r="B54" s="51" t="n"/>
+      <c r="C54" s="48" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="41" t="inlineStr">
+      <c r="A56" s="42" t="inlineStr">
         <is>
           <t>After posting, blank the input cells for next month (or use the Form). The script only writes fields you filled, into the month you chose above.</t>
         </is>
@@ -18996,38 +18997,38 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>Discretionary Spending Guardrail</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1" s="39">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>Three lanes — Matt, Sue, Household — for dinners, drinks, coffee, entertainment, convenience &amp; vices. Unused budget ROLLS OVER, so a high 'available' balance = green light to splurge; a negative one = pause. ORANGE = inputs (actuals arrive via Monthly Entry). Educational tool, not advice.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>① BUDGET CONFIG  (per month)</t>
         </is>
       </c>
-      <c r="B4" s="45" t="n"/>
-      <c r="C4" s="45" t="n"/>
-      <c r="D4" s="45" t="n"/>
-      <c r="E4" s="45" t="n"/>
-      <c r="F4" s="45" t="n"/>
-      <c r="G4" s="45" t="n"/>
-      <c r="H4" s="45" t="n"/>
-      <c r="I4" s="45" t="n"/>
-      <c r="J4" s="45" t="n"/>
-      <c r="K4" s="45" t="n"/>
-      <c r="L4" s="45" t="n"/>
-      <c r="M4" s="45" t="n"/>
-      <c r="N4" s="45" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="46" t="n"/>
+      <c r="L4" s="46" t="n"/>
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19035,7 +19036,7 @@
           <t>Matt monthly budget</t>
         </is>
       </c>
-      <c r="B5" s="50" t="n">
+      <c r="B5" s="51" t="n">
         <v>200</v>
       </c>
     </row>
@@ -19045,7 +19046,7 @@
           <t>Sue monthly budget</t>
         </is>
       </c>
-      <c r="B6" s="50" t="n">
+      <c r="B6" s="51" t="n">
         <v>200</v>
       </c>
     </row>
@@ -19055,22 +19056,22 @@
           <t>Household monthly budget</t>
         </is>
       </c>
-      <c r="B7" s="50" t="n">
+      <c r="B7" s="51" t="n">
         <v>300</v>
       </c>
-      <c r="C7" s="47" t="inlineStr">
+      <c r="C7" s="48" t="inlineStr">
         <is>
           <t>Shared dinners/entertainment together — set to taste.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="63" t="inlineStr">
+      <c r="A8" s="64" t="inlineStr">
         <is>
           <t>Combined monthly budget</t>
         </is>
       </c>
-      <c r="B8" s="95">
+      <c r="B8" s="96">
         <f>B5+B6+B7</f>
         <v/>
       </c>
@@ -19081,10 +19082,10 @@
           <t>Splurge-room threshold ($)</t>
         </is>
       </c>
-      <c r="B9" s="50" t="n">
+      <c r="B9" s="51" t="n">
         <v>150</v>
       </c>
-      <c r="C9" s="47" t="inlineStr">
+      <c r="C9" s="48" t="inlineStr">
         <is>
           <t>When a lane's rollover balance clears this, it's green to splurge.</t>
         </is>
@@ -19096,863 +19097,863 @@
           <t>Reporting month</t>
         </is>
       </c>
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="50" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="C10" s="47" t="inlineStr">
+      <c r="C10" s="48" t="inlineStr">
         <is>
           <t>Drives the standings panel below.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="44" t="inlineStr">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t>② WHERE YOU STAND  (reporting month)</t>
         </is>
       </c>
-      <c r="B12" s="45" t="n"/>
-      <c r="C12" s="45" t="n"/>
-      <c r="D12" s="45" t="n"/>
-      <c r="E12" s="45" t="n"/>
-      <c r="F12" s="45" t="n"/>
-      <c r="G12" s="45" t="n"/>
-      <c r="H12" s="45" t="n"/>
-      <c r="I12" s="45" t="n"/>
-      <c r="J12" s="45" t="n"/>
-      <c r="K12" s="45" t="n"/>
-      <c r="L12" s="45" t="n"/>
-      <c r="M12" s="45" t="n"/>
-      <c r="N12" s="45" t="n"/>
+      <c r="B12" s="46" t="n"/>
+      <c r="C12" s="46" t="n"/>
+      <c r="D12" s="46" t="n"/>
+      <c r="E12" s="46" t="n"/>
+      <c r="F12" s="46" t="n"/>
+      <c r="G12" s="46" t="n"/>
+      <c r="H12" s="46" t="n"/>
+      <c r="I12" s="46" t="n"/>
+      <c r="J12" s="46" t="n"/>
+      <c r="K12" s="46" t="n"/>
+      <c r="L12" s="46" t="n"/>
+      <c r="M12" s="46" t="n"/>
+      <c r="N12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="53" t="inlineStr">
+      <c r="A13" s="54" t="inlineStr">
         <is>
           <t>Lane</t>
         </is>
       </c>
-      <c r="B13" s="53" t="inlineStr">
+      <c r="B13" s="54" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C13" s="53" t="inlineStr">
+      <c r="C13" s="54" t="inlineStr">
         <is>
           <t>Spent (mo)</t>
         </is>
       </c>
-      <c r="D13" s="53" t="inlineStr">
+      <c r="D13" s="54" t="inlineStr">
         <is>
           <t>Rollover avail.</t>
         </is>
       </c>
-      <c r="E13" s="53" t="inlineStr">
+      <c r="E13" s="54" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="83" t="inlineStr">
+      <c r="A14" s="84" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="B14" s="68">
+      <c r="B14" s="69">
         <f>B5</f>
         <v/>
       </c>
-      <c r="C14" s="68">
+      <c r="C14" s="69">
         <f>INDEX(B22:M22,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
         <v/>
       </c>
-      <c r="D14" s="82">
+      <c r="D14" s="83">
         <f>INDEX(B23:M23,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
         <v/>
       </c>
-      <c r="E14" s="83">
+      <c r="E14" s="84">
         <f>IF(D14="","",IF(D14&lt;0,"🔴 over — pause",IF(D14&gt;=$B$9,"🟢 splurge OK","🟡 on track")))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="83" t="inlineStr">
+      <c r="A15" s="84" t="inlineStr">
         <is>
           <t>Sue</t>
         </is>
       </c>
-      <c r="B15" s="68">
+      <c r="B15" s="69">
         <f>B6</f>
         <v/>
       </c>
-      <c r="C15" s="68">
+      <c r="C15" s="69">
         <f>INDEX(B25:M25,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
         <v/>
       </c>
-      <c r="D15" s="82">
+      <c r="D15" s="83">
         <f>INDEX(B26:M26,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
         <v/>
       </c>
-      <c r="E15" s="83">
+      <c r="E15" s="84">
         <f>IF(D15="","",IF(D15&lt;0,"🔴 over — pause",IF(D15&gt;=$B$9,"🟢 splurge OK","🟡 on track")))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="83" t="inlineStr">
+      <c r="A16" s="84" t="inlineStr">
         <is>
           <t>Household</t>
         </is>
       </c>
-      <c r="B16" s="68">
+      <c r="B16" s="69">
         <f>B7</f>
         <v/>
       </c>
-      <c r="C16" s="68">
+      <c r="C16" s="69">
         <f>INDEX(B28:M28,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
         <v/>
       </c>
-      <c r="D16" s="82">
+      <c r="D16" s="83">
         <f>INDEX(B29:M29,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
         <v/>
       </c>
-      <c r="E16" s="83">
+      <c r="E16" s="84">
         <f>IF(D16="","",IF(D16&lt;0,"🔴 over — pause",IF(D16&gt;=$B$9,"🟢 splurge OK","🟡 on track")))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="80" t="inlineStr">
+      <c r="A17" s="81" t="inlineStr">
         <is>
           <t>Combined</t>
         </is>
       </c>
-      <c r="B17" s="68">
+      <c r="B17" s="69">
         <f>B8</f>
         <v/>
       </c>
-      <c r="C17" s="68">
+      <c r="C17" s="69">
         <f>INDEX(B30:M30,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
         <v/>
       </c>
-      <c r="D17" s="82">
+      <c r="D17" s="83">
         <f>INDEX(B32:M32,MATCH($B$10,{"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},0))</f>
         <v/>
       </c>
-      <c r="E17" s="83">
+      <c r="E17" s="84">
         <f>IF(D17="","",IF(D17&lt;0,"🔴 over — pause",IF(D17&gt;=$B$9,"🟢 splurge OK","🟡 on track")))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="44" t="inlineStr">
+      <c r="A19" s="45" t="inlineStr">
         <is>
           <t>③ MONTHLY TRACKER  (rollover carries forward)</t>
         </is>
       </c>
-      <c r="B19" s="45" t="n"/>
-      <c r="C19" s="45" t="n"/>
-      <c r="D19" s="45" t="n"/>
-      <c r="E19" s="45" t="n"/>
-      <c r="F19" s="45" t="n"/>
-      <c r="G19" s="45" t="n"/>
-      <c r="H19" s="45" t="n"/>
-      <c r="I19" s="45" t="n"/>
-      <c r="J19" s="45" t="n"/>
-      <c r="K19" s="45" t="n"/>
-      <c r="L19" s="45" t="n"/>
-      <c r="M19" s="45" t="n"/>
-      <c r="N19" s="45" t="n"/>
+      <c r="B19" s="46" t="n"/>
+      <c r="C19" s="46" t="n"/>
+      <c r="D19" s="46" t="n"/>
+      <c r="E19" s="46" t="n"/>
+      <c r="F19" s="46" t="n"/>
+      <c r="G19" s="46" t="n"/>
+      <c r="H19" s="46" t="n"/>
+      <c r="I19" s="46" t="n"/>
+      <c r="J19" s="46" t="n"/>
+      <c r="K19" s="46" t="n"/>
+      <c r="L19" s="46" t="n"/>
+      <c r="M19" s="46" t="n"/>
+      <c r="N19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="96" t="inlineStr"/>
-      <c r="B20" s="53" t="inlineStr">
+      <c r="A20" s="97" t="inlineStr"/>
+      <c r="B20" s="54" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C20" s="53" t="inlineStr">
+      <c r="C20" s="54" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D20" s="53" t="inlineStr">
+      <c r="D20" s="54" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E20" s="53" t="inlineStr">
+      <c r="E20" s="54" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F20" s="53" t="inlineStr">
+      <c r="F20" s="54" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G20" s="53" t="inlineStr">
+      <c r="G20" s="54" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H20" s="53" t="inlineStr">
+      <c r="H20" s="54" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I20" s="53" t="inlineStr">
+      <c r="I20" s="54" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J20" s="53" t="inlineStr">
+      <c r="J20" s="54" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K20" s="53" t="inlineStr">
+      <c r="K20" s="54" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L20" s="53" t="inlineStr">
+      <c r="L20" s="54" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M20" s="53" t="inlineStr">
+      <c r="M20" s="54" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="N20" s="53" t="inlineStr">
+      <c r="N20" s="54" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="83" t="inlineStr">
+      <c r="A21" s="84" t="inlineStr">
         <is>
           <t>Matt — Budget</t>
         </is>
       </c>
-      <c r="B21" s="68">
+      <c r="B21" s="69">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="C21" s="68">
+      <c r="C21" s="69">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="D21" s="68">
+      <c r="D21" s="69">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E21" s="68">
+      <c r="E21" s="69">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="F21" s="68">
+      <c r="F21" s="69">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="G21" s="68">
+      <c r="G21" s="69">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="H21" s="68">
+      <c r="H21" s="69">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="I21" s="68">
+      <c r="I21" s="69">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="J21" s="68">
+      <c r="J21" s="69">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="K21" s="68">
+      <c r="K21" s="69">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="L21" s="68">
+      <c r="L21" s="69">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="M21" s="68">
+      <c r="M21" s="69">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="N21" s="68">
+      <c r="N21" s="69">
         <f>SUM(B21:M21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="83" t="inlineStr">
+      <c r="A22" s="84" t="inlineStr">
         <is>
           <t>Matt — Actual (spent)</t>
         </is>
       </c>
-      <c r="B22" s="84" t="n"/>
-      <c r="C22" s="84" t="n"/>
-      <c r="D22" s="84" t="n"/>
-      <c r="E22" s="84" t="n"/>
-      <c r="F22" s="84" t="n"/>
-      <c r="G22" s="84" t="n"/>
-      <c r="H22" s="84" t="n"/>
-      <c r="I22" s="84" t="n"/>
-      <c r="J22" s="84" t="n"/>
-      <c r="K22" s="84" t="n"/>
-      <c r="L22" s="84" t="n"/>
-      <c r="M22" s="84" t="n"/>
-      <c r="N22" s="68">
+      <c r="B22" s="85" t="n"/>
+      <c r="C22" s="85" t="n"/>
+      <c r="D22" s="85" t="n"/>
+      <c r="E22" s="85" t="n"/>
+      <c r="F22" s="85" t="n"/>
+      <c r="G22" s="85" t="n"/>
+      <c r="H22" s="85" t="n"/>
+      <c r="I22" s="85" t="n"/>
+      <c r="J22" s="85" t="n"/>
+      <c r="K22" s="85" t="n"/>
+      <c r="L22" s="85" t="n"/>
+      <c r="M22" s="85" t="n"/>
+      <c r="N22" s="69">
         <f>SUM(B22:M22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="80" t="inlineStr">
+      <c r="A23" s="81" t="inlineStr">
         <is>
           <t>Matt — Rollover available</t>
         </is>
       </c>
-      <c r="B23" s="85">
+      <c r="B23" s="86">
         <f>B21-B22</f>
         <v/>
       </c>
-      <c r="C23" s="85">
+      <c r="C23" s="86">
         <f>B23+C21-C22</f>
         <v/>
       </c>
-      <c r="D23" s="85">
+      <c r="D23" s="86">
         <f>C23+D21-D22</f>
         <v/>
       </c>
-      <c r="E23" s="85">
+      <c r="E23" s="86">
         <f>D23+E21-E22</f>
         <v/>
       </c>
-      <c r="F23" s="85">
+      <c r="F23" s="86">
         <f>E23+F21-F22</f>
         <v/>
       </c>
-      <c r="G23" s="85">
+      <c r="G23" s="86">
         <f>F23+G21-G22</f>
         <v/>
       </c>
-      <c r="H23" s="85">
+      <c r="H23" s="86">
         <f>G23+H21-H22</f>
         <v/>
       </c>
-      <c r="I23" s="85">
+      <c r="I23" s="86">
         <f>H23+I21-I22</f>
         <v/>
       </c>
-      <c r="J23" s="85">
+      <c r="J23" s="86">
         <f>I23+J21-J22</f>
         <v/>
       </c>
-      <c r="K23" s="85">
+      <c r="K23" s="86">
         <f>J23+K21-K22</f>
         <v/>
       </c>
-      <c r="L23" s="85">
+      <c r="L23" s="86">
         <f>K23+L21-L22</f>
         <v/>
       </c>
-      <c r="M23" s="85">
+      <c r="M23" s="86">
         <f>L23+M21-M22</f>
         <v/>
       </c>
-      <c r="N23" s="85">
+      <c r="N23" s="86">
         <f>M23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="83" t="inlineStr">
+      <c r="A24" s="84" t="inlineStr">
         <is>
           <t>Sue — Budget</t>
         </is>
       </c>
-      <c r="B24" s="68">
+      <c r="B24" s="69">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="C24" s="68">
+      <c r="C24" s="69">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="D24" s="68">
+      <c r="D24" s="69">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="E24" s="68">
+      <c r="E24" s="69">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="F24" s="68">
+      <c r="F24" s="69">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="G24" s="68">
+      <c r="G24" s="69">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="H24" s="68">
+      <c r="H24" s="69">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="I24" s="68">
+      <c r="I24" s="69">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="J24" s="68">
+      <c r="J24" s="69">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="K24" s="68">
+      <c r="K24" s="69">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="L24" s="68">
+      <c r="L24" s="69">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="M24" s="68">
+      <c r="M24" s="69">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="N24" s="68">
+      <c r="N24" s="69">
         <f>SUM(B24:M24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="83" t="inlineStr">
+      <c r="A25" s="84" t="inlineStr">
         <is>
           <t>Sue — Actual (spent)</t>
         </is>
       </c>
-      <c r="B25" s="84" t="n"/>
-      <c r="C25" s="84" t="n"/>
-      <c r="D25" s="84" t="n"/>
-      <c r="E25" s="84" t="n"/>
-      <c r="F25" s="84" t="n"/>
-      <c r="G25" s="84" t="n"/>
-      <c r="H25" s="84" t="n"/>
-      <c r="I25" s="84" t="n"/>
-      <c r="J25" s="84" t="n"/>
-      <c r="K25" s="84" t="n"/>
-      <c r="L25" s="84" t="n"/>
-      <c r="M25" s="84" t="n"/>
-      <c r="N25" s="68">
+      <c r="B25" s="85" t="n"/>
+      <c r="C25" s="85" t="n"/>
+      <c r="D25" s="85" t="n"/>
+      <c r="E25" s="85" t="n"/>
+      <c r="F25" s="85" t="n"/>
+      <c r="G25" s="85" t="n"/>
+      <c r="H25" s="85" t="n"/>
+      <c r="I25" s="85" t="n"/>
+      <c r="J25" s="85" t="n"/>
+      <c r="K25" s="85" t="n"/>
+      <c r="L25" s="85" t="n"/>
+      <c r="M25" s="85" t="n"/>
+      <c r="N25" s="69">
         <f>SUM(B25:M25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="80" t="inlineStr">
+      <c r="A26" s="81" t="inlineStr">
         <is>
           <t>Sue — Rollover available</t>
         </is>
       </c>
-      <c r="B26" s="85">
+      <c r="B26" s="86">
         <f>B24-B25</f>
         <v/>
       </c>
-      <c r="C26" s="85">
+      <c r="C26" s="86">
         <f>B26+C24-C25</f>
         <v/>
       </c>
-      <c r="D26" s="85">
+      <c r="D26" s="86">
         <f>C26+D24-D25</f>
         <v/>
       </c>
-      <c r="E26" s="85">
+      <c r="E26" s="86">
         <f>D26+E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="85">
+      <c r="F26" s="86">
         <f>E26+F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="85">
+      <c r="G26" s="86">
         <f>F26+G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="85">
+      <c r="H26" s="86">
         <f>G26+H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="85">
+      <c r="I26" s="86">
         <f>H26+I24-I25</f>
         <v/>
       </c>
-      <c r="J26" s="85">
+      <c r="J26" s="86">
         <f>I26+J24-J25</f>
         <v/>
       </c>
-      <c r="K26" s="85">
+      <c r="K26" s="86">
         <f>J26+K24-K25</f>
         <v/>
       </c>
-      <c r="L26" s="85">
+      <c r="L26" s="86">
         <f>K26+L24-L25</f>
         <v/>
       </c>
-      <c r="M26" s="85">
+      <c r="M26" s="86">
         <f>L26+M24-M25</f>
         <v/>
       </c>
-      <c r="N26" s="85">
+      <c r="N26" s="86">
         <f>M26</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="83" t="inlineStr">
+      <c r="A27" s="84" t="inlineStr">
         <is>
           <t>Household — Budget</t>
         </is>
       </c>
-      <c r="B27" s="68">
+      <c r="B27" s="69">
         <f>$B$7</f>
         <v/>
       </c>
-      <c r="C27" s="68">
+      <c r="C27" s="69">
         <f>$B$7</f>
         <v/>
       </c>
-      <c r="D27" s="68">
+      <c r="D27" s="69">
         <f>$B$7</f>
         <v/>
       </c>
-      <c r="E27" s="68">
+      <c r="E27" s="69">
         <f>$B$7</f>
         <v/>
       </c>
-      <c r="F27" s="68">
+      <c r="F27" s="69">
         <f>$B$7</f>
         <v/>
       </c>
-      <c r="G27" s="68">
+      <c r="G27" s="69">
         <f>$B$7</f>
         <v/>
       </c>
-      <c r="H27" s="68">
+      <c r="H27" s="69">
         <f>$B$7</f>
         <v/>
       </c>
-      <c r="I27" s="68">
+      <c r="I27" s="69">
         <f>$B$7</f>
         <v/>
       </c>
-      <c r="J27" s="68">
+      <c r="J27" s="69">
         <f>$B$7</f>
         <v/>
       </c>
-      <c r="K27" s="68">
+      <c r="K27" s="69">
         <f>$B$7</f>
         <v/>
       </c>
-      <c r="L27" s="68">
+      <c r="L27" s="69">
         <f>$B$7</f>
         <v/>
       </c>
-      <c r="M27" s="68">
+      <c r="M27" s="69">
         <f>$B$7</f>
         <v/>
       </c>
-      <c r="N27" s="68">
+      <c r="N27" s="69">
         <f>SUM(B27:M27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="83" t="inlineStr">
+      <c r="A28" s="84" t="inlineStr">
         <is>
           <t>Household — Actual (spent)</t>
         </is>
       </c>
-      <c r="B28" s="84" t="n"/>
-      <c r="C28" s="84" t="n"/>
-      <c r="D28" s="84" t="n"/>
-      <c r="E28" s="84" t="n"/>
-      <c r="F28" s="84" t="n"/>
-      <c r="G28" s="84" t="n"/>
-      <c r="H28" s="84" t="n"/>
-      <c r="I28" s="84" t="n"/>
-      <c r="J28" s="84" t="n"/>
-      <c r="K28" s="84" t="n"/>
-      <c r="L28" s="84" t="n"/>
-      <c r="M28" s="84" t="n"/>
-      <c r="N28" s="68">
+      <c r="B28" s="85" t="n"/>
+      <c r="C28" s="85" t="n"/>
+      <c r="D28" s="85" t="n"/>
+      <c r="E28" s="85" t="n"/>
+      <c r="F28" s="85" t="n"/>
+      <c r="G28" s="85" t="n"/>
+      <c r="H28" s="85" t="n"/>
+      <c r="I28" s="85" t="n"/>
+      <c r="J28" s="85" t="n"/>
+      <c r="K28" s="85" t="n"/>
+      <c r="L28" s="85" t="n"/>
+      <c r="M28" s="85" t="n"/>
+      <c r="N28" s="69">
         <f>SUM(B28:M28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="80" t="inlineStr">
+      <c r="A29" s="81" t="inlineStr">
         <is>
           <t>Household — Rollover available</t>
         </is>
       </c>
-      <c r="B29" s="85">
+      <c r="B29" s="86">
         <f>B27-B28</f>
         <v/>
       </c>
-      <c r="C29" s="85">
+      <c r="C29" s="86">
         <f>B29+C27-C28</f>
         <v/>
       </c>
-      <c r="D29" s="85">
+      <c r="D29" s="86">
         <f>C29+D27-D28</f>
         <v/>
       </c>
-      <c r="E29" s="85">
+      <c r="E29" s="86">
         <f>D29+E27-E28</f>
         <v/>
       </c>
-      <c r="F29" s="85">
+      <c r="F29" s="86">
         <f>E29+F27-F28</f>
         <v/>
       </c>
-      <c r="G29" s="85">
+      <c r="G29" s="86">
         <f>F29+G27-G28</f>
         <v/>
       </c>
-      <c r="H29" s="85">
+      <c r="H29" s="86">
         <f>G29+H27-H28</f>
         <v/>
       </c>
-      <c r="I29" s="85">
+      <c r="I29" s="86">
         <f>H29+I27-I28</f>
         <v/>
       </c>
-      <c r="J29" s="85">
+      <c r="J29" s="86">
         <f>I29+J27-J28</f>
         <v/>
       </c>
-      <c r="K29" s="85">
+      <c r="K29" s="86">
         <f>J29+K27-K28</f>
         <v/>
       </c>
-      <c r="L29" s="85">
+      <c r="L29" s="86">
         <f>K29+L27-L28</f>
         <v/>
       </c>
-      <c r="M29" s="85">
+      <c r="M29" s="86">
         <f>L29+M27-M28</f>
         <v/>
       </c>
-      <c r="N29" s="85">
+      <c r="N29" s="86">
         <f>M29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="83" t="inlineStr">
+      <c r="A30" s="84" t="inlineStr">
         <is>
           <t>Combined — Actual</t>
         </is>
       </c>
-      <c r="B30" s="68">
+      <c r="B30" s="69">
         <f>B22+B25+B28</f>
         <v/>
       </c>
-      <c r="C30" s="68">
+      <c r="C30" s="69">
         <f>C22+C25+C28</f>
         <v/>
       </c>
-      <c r="D30" s="68">
+      <c r="D30" s="69">
         <f>D22+D25+D28</f>
         <v/>
       </c>
-      <c r="E30" s="68">
+      <c r="E30" s="69">
         <f>E22+E25+E28</f>
         <v/>
       </c>
-      <c r="F30" s="68">
+      <c r="F30" s="69">
         <f>F22+F25+F28</f>
         <v/>
       </c>
-      <c r="G30" s="68">
+      <c r="G30" s="69">
         <f>G22+G25+G28</f>
         <v/>
       </c>
-      <c r="H30" s="68">
+      <c r="H30" s="69">
         <f>H22+H25+H28</f>
         <v/>
       </c>
-      <c r="I30" s="68">
+      <c r="I30" s="69">
         <f>I22+I25+I28</f>
         <v/>
       </c>
-      <c r="J30" s="68">
+      <c r="J30" s="69">
         <f>J22+J25+J28</f>
         <v/>
       </c>
-      <c r="K30" s="68">
+      <c r="K30" s="69">
         <f>K22+K25+K28</f>
         <v/>
       </c>
-      <c r="L30" s="68">
+      <c r="L30" s="69">
         <f>L22+L25+L28</f>
         <v/>
       </c>
-      <c r="M30" s="68">
+      <c r="M30" s="69">
         <f>M22+M25+M28</f>
         <v/>
       </c>
-      <c r="N30" s="68">
+      <c r="N30" s="69">
         <f>SUM(B30:M30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="83" t="inlineStr">
+      <c r="A31" s="84" t="inlineStr">
         <is>
           <t>Combined — Budget</t>
         </is>
       </c>
-      <c r="B31" s="68">
+      <c r="B31" s="69">
         <f>B21+B24+B27</f>
         <v/>
       </c>
-      <c r="C31" s="68">
+      <c r="C31" s="69">
         <f>C21+C24+C27</f>
         <v/>
       </c>
-      <c r="D31" s="68">
+      <c r="D31" s="69">
         <f>D21+D24+D27</f>
         <v/>
       </c>
-      <c r="E31" s="68">
+      <c r="E31" s="69">
         <f>E21+E24+E27</f>
         <v/>
       </c>
-      <c r="F31" s="68">
+      <c r="F31" s="69">
         <f>F21+F24+F27</f>
         <v/>
       </c>
-      <c r="G31" s="68">
+      <c r="G31" s="69">
         <f>G21+G24+G27</f>
         <v/>
       </c>
-      <c r="H31" s="68">
+      <c r="H31" s="69">
         <f>H21+H24+H27</f>
         <v/>
       </c>
-      <c r="I31" s="68">
+      <c r="I31" s="69">
         <f>I21+I24+I27</f>
         <v/>
       </c>
-      <c r="J31" s="68">
+      <c r="J31" s="69">
         <f>J21+J24+J27</f>
         <v/>
       </c>
-      <c r="K31" s="68">
+      <c r="K31" s="69">
         <f>K21+K24+K27</f>
         <v/>
       </c>
-      <c r="L31" s="68">
+      <c r="L31" s="69">
         <f>L21+L24+L27</f>
         <v/>
       </c>
-      <c r="M31" s="68">
+      <c r="M31" s="69">
         <f>M21+M24+M27</f>
         <v/>
       </c>
-      <c r="N31" s="68">
+      <c r="N31" s="69">
         <f>SUM(B31:M31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="80" t="inlineStr">
+      <c r="A32" s="81" t="inlineStr">
         <is>
           <t>Combined — Rollover available</t>
         </is>
       </c>
-      <c r="B32" s="85">
+      <c r="B32" s="86">
         <f>B23+B26+B29</f>
         <v/>
       </c>
-      <c r="C32" s="85">
+      <c r="C32" s="86">
         <f>C23+C26+C29</f>
         <v/>
       </c>
-      <c r="D32" s="85">
+      <c r="D32" s="86">
         <f>D23+D26+D29</f>
         <v/>
       </c>
-      <c r="E32" s="85">
+      <c r="E32" s="86">
         <f>E23+E26+E29</f>
         <v/>
       </c>
-      <c r="F32" s="85">
+      <c r="F32" s="86">
         <f>F23+F26+F29</f>
         <v/>
       </c>
-      <c r="G32" s="85">
+      <c r="G32" s="86">
         <f>G23+G26+G29</f>
         <v/>
       </c>
-      <c r="H32" s="85">
+      <c r="H32" s="86">
         <f>H23+H26+H29</f>
         <v/>
       </c>
-      <c r="I32" s="85">
+      <c r="I32" s="86">
         <f>I23+I26+I29</f>
         <v/>
       </c>
-      <c r="J32" s="85">
+      <c r="J32" s="86">
         <f>J23+J26+J29</f>
         <v/>
       </c>
-      <c r="K32" s="85">
+      <c r="K32" s="86">
         <f>K23+K26+K29</f>
         <v/>
       </c>
-      <c r="L32" s="85">
+      <c r="L32" s="86">
         <f>L23+L26+L29</f>
         <v/>
       </c>
-      <c r="M32" s="85">
+      <c r="M32" s="86">
         <f>M23+M26+M29</f>
         <v/>
       </c>
-      <c r="N32" s="85">
+      <c r="N32" s="86">
         <f>M32</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="44" t="inlineStr">
+      <c r="A34" s="45" t="inlineStr">
         <is>
           <t>④ IMPACT ON YOUR SAVINGS / FIRE</t>
         </is>
       </c>
-      <c r="B34" s="45" t="n"/>
-      <c r="C34" s="45" t="n"/>
-      <c r="D34" s="45" t="n"/>
-      <c r="E34" s="45" t="n"/>
-      <c r="F34" s="45" t="n"/>
-      <c r="G34" s="45" t="n"/>
-      <c r="H34" s="45" t="n"/>
-      <c r="I34" s="45" t="n"/>
-      <c r="J34" s="45" t="n"/>
-      <c r="K34" s="45" t="n"/>
-      <c r="L34" s="45" t="n"/>
-      <c r="M34" s="45" t="n"/>
-      <c r="N34" s="45" t="n"/>
+      <c r="B34" s="46" t="n"/>
+      <c r="C34" s="46" t="n"/>
+      <c r="D34" s="46" t="n"/>
+      <c r="E34" s="46" t="n"/>
+      <c r="F34" s="46" t="n"/>
+      <c r="G34" s="46" t="n"/>
+      <c r="H34" s="46" t="n"/>
+      <c r="I34" s="46" t="n"/>
+      <c r="J34" s="46" t="n"/>
+      <c r="K34" s="46" t="n"/>
+      <c r="L34" s="46" t="n"/>
+      <c r="M34" s="46" t="n"/>
+      <c r="N34" s="46" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -19960,7 +19961,7 @@
           <t>YTD combined budget</t>
         </is>
       </c>
-      <c r="B35" s="73">
+      <c r="B35" s="74">
         <f>N31</f>
         <v/>
       </c>
@@ -19971,22 +19972,22 @@
           <t>YTD combined actual</t>
         </is>
       </c>
-      <c r="B36" s="73">
+      <c r="B36" s="74">
         <f>N30</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="63" t="inlineStr">
+      <c r="A37" s="64" t="inlineStr">
         <is>
           <t>YTD over / (under)</t>
         </is>
       </c>
-      <c r="B37" s="64">
+      <c r="B37" s="65">
         <f>N30-N31</f>
         <v/>
       </c>
-      <c r="C37" s="47" t="inlineStr">
+      <c r="C37" s="48" t="inlineStr">
         <is>
           <t>Positive = overspent (money that didn't get invested).</t>
         </is>
@@ -19998,29 +19999,29 @@
           <t>Growth factor (real, 20 yrs)</t>
         </is>
       </c>
-      <c r="B38" s="97">
+      <c r="B38" s="98">
         <f>(1+'FIRE Dashboard'!B12)^20</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="63" t="inlineStr">
+      <c r="A39" s="64" t="inlineStr">
         <is>
           <t>Compounded cost of overspend</t>
         </is>
       </c>
-      <c r="B39" s="64">
+      <c r="B39" s="65">
         <f>MAX(0,B37)*B38</f>
         <v/>
       </c>
-      <c r="C39" s="47" t="inlineStr">
+      <c r="C39" s="48" t="inlineStr">
         <is>
           <t>What this year's overspend would be worth in 20 yrs if invested instead.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="41" t="inlineStr">
+      <c r="A41" s="42" t="inlineStr">
         <is>
           <t>How rollover works: each month adds the lane's budget and subtracts what you spent. Underspend and the balance grows (bank it for a guilt-free splurge later); overspend and it goes negative until you claw it back. Actuals post automatically from the Monthly Entry tab.</t>
         </is>
@@ -24903,7 +24904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="40" customWidth="1" style="39" min="1" max="1"/>
@@ -25083,9 +25084,15 @@
       <c r="D9" s="40" t="n"/>
       <c r="E9" s="40" t="n"/>
       <c r="F9" s="40" t="n"/>
-      <c r="G9" s="40" t="n"/>
-      <c r="H9" s="40" t="n"/>
-      <c r="I9" s="40" t="n"/>
+      <c r="G9" s="41" t="n">
+        <v>143</v>
+      </c>
+      <c r="H9" s="41" t="n">
+        <v>206.98</v>
+      </c>
+      <c r="I9" s="41" t="n">
+        <v>308.95</v>
+      </c>
       <c r="J9" s="40" t="n"/>
       <c r="K9" s="40" t="n"/>
       <c r="L9" s="40" t="n"/>
@@ -25101,20 +25108,24 @@
           <t>Actual electric bill</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n">
+      <c r="B10" s="40" t="n"/>
+      <c r="C10" s="40" t="n"/>
+      <c r="D10" s="40" t="n"/>
+      <c r="E10" s="40" t="n"/>
+      <c r="F10" s="40" t="n"/>
+      <c r="G10" s="41" t="n">
         <v>87</v>
       </c>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="n"/>
-      <c r="M10" s="8" t="n"/>
+      <c r="H10" s="41" t="n">
+        <v>105.09</v>
+      </c>
+      <c r="I10" s="41" t="n">
+        <v>122.29</v>
+      </c>
+      <c r="J10" s="40" t="n"/>
+      <c r="K10" s="40" t="n"/>
+      <c r="L10" s="40" t="n"/>
+      <c r="M10" s="40" t="n"/>
       <c r="N10" s="15">
         <f>SUM(B10:M10)</f>
         <v/>
@@ -25298,15 +25309,21 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="39">
-      <c r="A21" s="41" t="inlineStr">
-        <is>
-          <t>⚠ To make payback compute: (1) enter pre-solar baseline monthly bills in row 9 (orange). (2) Enter incentives in row 6 — NOTE: the 30% federal solar credit (25D) ended for systems placed in service after 12/31/2025 (OBBB, 7/4/2025); if yours went live in 2026 the federal credit is $0. MA still gives a 15% state credit up to $1,000. Full reinvestment model on the 'Solar Reinvestment' tab →</t>
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>⚠ Incentives (row 6): the 30% federal solar credit (25D) ended for systems placed in service after 12/31/2025 (OBBB, 7/4/2025); yours went live ~Apr 2026, so federal = $0. MA still gives a 15% state credit up to $1,000. Full reinvestment model on the 'Solar Reinvestment' tab →</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="39"/>
     <row r="23" ht="15.75" customHeight="1" s="39"/>
-    <row r="24" ht="15.75" customHeight="1" s="39"/>
+    <row r="24" ht="15.75" customHeight="1" s="39">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>Real data entered for the first clean post-solar months (Jun–Aug): baseline = 2025 same-month bills, actual = 2026 bills → saved ~$56 / $102 / $187. 2026 winter bills spiked on rates &amp; cold, so earlier months aren't a clean solar comparison — add post-solar winter data (Nov 2026+) for a full-year payback.</t>
+        </is>
+      </c>
+    </row>
     <row r="25" ht="15.75" customHeight="1" s="39"/>
     <row r="26" ht="15.75" customHeight="1" s="39"/>
     <row r="27" ht="15.75" customHeight="1" s="39"/>
@@ -26284,7 +26301,8 @@
     <row r="999" ht="15.75" customHeight="1" s="39"/>
     <row r="1000" ht="15.75" customHeight="1" s="39"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A24:N26"/>
     <mergeCell ref="A21:N23"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
